--- a/dataset/DSLIB_Analysis_Scheet.xlsx
+++ b/dataset/DSLIB_Analysis_Scheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/jisantos_ubu_es/Documents/CodeDrive/GitHub/counterEVM-1/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{397A7FD8-BC23-430C-B2C6-E98CFB6549D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DDE3AFD-37A0-413F-9159-865035E2D196}"/>
+  <xr:revisionPtr revIDLastSave="185" documentId="13_ncr:1_{397A7FD8-BC23-430C-B2C6-E98CFB6549D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92B32219-D8E5-4F52-B320-1AED125380EF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3184,7 +3184,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3311,12 +3311,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC66"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -3365,7 +3359,7 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3693,50 +3687,6 @@
     <xf numFmtId="0" fontId="26" fillId="19" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3773,9 +3723,6 @@
     <xf numFmtId="0" fontId="33" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3794,6 +3741,47 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Bueno" xfId="4" builtinId="26"/>
@@ -4920,6 +4908,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6218,13 +6210,13 @@
   <cols>
     <col min="2" max="2" width="33.1640625" customWidth="1"/>
     <col min="3" max="3" width="23.1640625" customWidth="1"/>
-    <col min="4" max="4" width="30.1640625" customWidth="1"/>
-    <col min="5" max="5" width="33.83203125" customWidth="1"/>
-    <col min="6" max="6" width="17.5" style="159" customWidth="1"/>
-    <col min="7" max="7" width="17" style="159" customWidth="1"/>
+    <col min="4" max="4" width="14.9140625" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.5" style="143" customWidth="1"/>
+    <col min="7" max="7" width="17" style="143" customWidth="1"/>
     <col min="8" max="8" width="17.6640625" customWidth="1"/>
     <col min="9" max="9" width="17.5" customWidth="1"/>
-    <col min="10" max="10" width="18.5" style="159" customWidth="1"/>
+    <col min="10" max="10" width="18.5" style="143" customWidth="1"/>
     <col min="13" max="14" width="17" customWidth="1"/>
     <col min="15" max="15" width="18.6640625" customWidth="1"/>
     <col min="16" max="18" width="19.6640625" customWidth="1"/>
@@ -6241,232 +6233,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:84" ht="16" customHeight="1">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="150" t="s">
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="159" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="150"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="146" t="s">
+      <c r="G1" s="159"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="163"/>
-      <c r="K1" s="147" t="s">
+      <c r="J1" s="161"/>
+      <c r="K1" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="146" t="s">
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="148" t="s">
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="R1" s="148"/>
-      <c r="S1" s="146" t="s">
+      <c r="R1" s="162"/>
+      <c r="S1" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="146"/>
-      <c r="X1" s="146"/>
-      <c r="Y1" s="141" t="s">
+      <c r="T1" s="158"/>
+      <c r="U1" s="158"/>
+      <c r="V1" s="158"/>
+      <c r="W1" s="158"/>
+      <c r="X1" s="158"/>
+      <c r="Y1" s="153" t="s">
         <v>71</v>
       </c>
-      <c r="Z1" s="141"/>
-      <c r="AA1" s="141"/>
-      <c r="AB1" s="141"/>
-      <c r="AC1" s="141"/>
-      <c r="AD1" s="141"/>
-      <c r="AE1" s="141"/>
-      <c r="AF1" s="141"/>
-      <c r="AG1" s="141"/>
-      <c r="AH1" s="141"/>
-      <c r="AI1" s="141"/>
-      <c r="AJ1" s="141"/>
-      <c r="AK1" s="141"/>
-      <c r="AL1" s="141"/>
-      <c r="AM1" s="141"/>
-      <c r="AN1" s="141"/>
-      <c r="AO1" s="141"/>
-      <c r="AP1" s="141"/>
-      <c r="AQ1" s="149" t="s">
+      <c r="Z1" s="153"/>
+      <c r="AA1" s="153"/>
+      <c r="AB1" s="153"/>
+      <c r="AC1" s="153"/>
+      <c r="AD1" s="153"/>
+      <c r="AE1" s="153"/>
+      <c r="AF1" s="153"/>
+      <c r="AG1" s="153"/>
+      <c r="AH1" s="153"/>
+      <c r="AI1" s="153"/>
+      <c r="AJ1" s="153"/>
+      <c r="AK1" s="153"/>
+      <c r="AL1" s="153"/>
+      <c r="AM1" s="153"/>
+      <c r="AN1" s="153"/>
+      <c r="AO1" s="153"/>
+      <c r="AP1" s="153"/>
+      <c r="AQ1" s="154" t="s">
         <v>86</v>
       </c>
-      <c r="AR1" s="149"/>
-      <c r="AS1" s="149"/>
-      <c r="AT1" s="149"/>
-      <c r="AU1" s="149"/>
-      <c r="AV1" s="149"/>
-      <c r="AW1" s="149"/>
-      <c r="AX1" s="149"/>
-      <c r="AY1" s="149"/>
-      <c r="AZ1" s="141" t="s">
+      <c r="AR1" s="154"/>
+      <c r="AS1" s="154"/>
+      <c r="AT1" s="154"/>
+      <c r="AU1" s="154"/>
+      <c r="AV1" s="154"/>
+      <c r="AW1" s="154"/>
+      <c r="AX1" s="154"/>
+      <c r="AY1" s="154"/>
+      <c r="AZ1" s="153" t="s">
         <v>89</v>
       </c>
-      <c r="BA1" s="141"/>
-      <c r="BB1" s="141"/>
-      <c r="BC1" s="141"/>
-      <c r="BD1" s="141"/>
-      <c r="BE1" s="141"/>
-      <c r="BF1" s="141"/>
-      <c r="BG1" s="141"/>
-      <c r="BH1" s="141"/>
-      <c r="BI1" s="142" t="s">
+      <c r="BA1" s="153"/>
+      <c r="BB1" s="153"/>
+      <c r="BC1" s="153"/>
+      <c r="BD1" s="153"/>
+      <c r="BE1" s="153"/>
+      <c r="BF1" s="153"/>
+      <c r="BG1" s="153"/>
+      <c r="BH1" s="153"/>
+      <c r="BI1" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="BJ1" s="142"/>
-      <c r="BK1" s="142"/>
-      <c r="BL1" s="142"/>
-      <c r="BM1" s="142"/>
-      <c r="BN1" s="142"/>
-      <c r="BO1" s="142"/>
-      <c r="BP1" s="142"/>
-      <c r="BQ1" s="142"/>
-      <c r="BR1" s="142"/>
-      <c r="BS1" s="142"/>
-      <c r="BT1" s="142"/>
-      <c r="BU1" s="142"/>
-      <c r="BV1" s="142"/>
-      <c r="BW1" s="142"/>
-      <c r="BX1" s="142"/>
-      <c r="BY1" s="142"/>
-      <c r="BZ1" s="142"/>
-      <c r="CA1" s="142"/>
-      <c r="CB1" s="142"/>
-      <c r="CC1" s="142"/>
-      <c r="CD1" s="142"/>
-      <c r="CE1" s="142"/>
+      <c r="BJ1" s="163"/>
+      <c r="BK1" s="163"/>
+      <c r="BL1" s="163"/>
+      <c r="BM1" s="163"/>
+      <c r="BN1" s="163"/>
+      <c r="BO1" s="163"/>
+      <c r="BP1" s="163"/>
+      <c r="BQ1" s="163"/>
+      <c r="BR1" s="163"/>
+      <c r="BS1" s="163"/>
+      <c r="BT1" s="163"/>
+      <c r="BU1" s="163"/>
+      <c r="BV1" s="163"/>
+      <c r="BW1" s="163"/>
+      <c r="BX1" s="163"/>
+      <c r="BY1" s="163"/>
+      <c r="BZ1" s="163"/>
+      <c r="CA1" s="163"/>
+      <c r="CB1" s="163"/>
+      <c r="CC1" s="163"/>
+      <c r="CD1" s="163"/>
+      <c r="CE1" s="163"/>
     </row>
     <row r="2" spans="1:84" ht="16" customHeight="1">
-      <c r="A2" s="145"/>
-      <c r="B2" s="145"/>
-      <c r="C2" s="145"/>
-      <c r="D2" s="145"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="150"/>
-      <c r="G2" s="150"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="148"/>
-      <c r="R2" s="148"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="146"/>
-      <c r="V2" s="146"/>
-      <c r="W2" s="146"/>
-      <c r="X2" s="146"/>
-      <c r="Y2" s="143" t="s">
+      <c r="A2" s="157"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="162"/>
+      <c r="R2" s="162"/>
+      <c r="S2" s="158"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="158"/>
+      <c r="V2" s="158"/>
+      <c r="W2" s="158"/>
+      <c r="X2" s="158"/>
+      <c r="Y2" s="155" t="s">
         <v>132</v>
       </c>
-      <c r="Z2" s="143"/>
-      <c r="AA2" s="143"/>
-      <c r="AB2" s="144" t="s">
+      <c r="Z2" s="155"/>
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="156" t="s">
         <v>75</v>
       </c>
-      <c r="AC2" s="144"/>
-      <c r="AD2" s="144"/>
-      <c r="AE2" s="143" t="s">
+      <c r="AC2" s="156"/>
+      <c r="AD2" s="156"/>
+      <c r="AE2" s="155" t="s">
         <v>77</v>
       </c>
-      <c r="AF2" s="143"/>
-      <c r="AG2" s="143"/>
-      <c r="AH2" s="144" t="s">
+      <c r="AF2" s="155"/>
+      <c r="AG2" s="155"/>
+      <c r="AH2" s="156" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" s="144"/>
-      <c r="AJ2" s="144"/>
-      <c r="AK2" s="143" t="s">
+      <c r="AI2" s="156"/>
+      <c r="AJ2" s="156"/>
+      <c r="AK2" s="155" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" s="143"/>
-      <c r="AM2" s="143"/>
-      <c r="AN2" s="144" t="s">
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="156" t="s">
         <v>83</v>
       </c>
-      <c r="AO2" s="144"/>
-      <c r="AP2" s="144"/>
-      <c r="AQ2" s="143" t="s">
+      <c r="AO2" s="156"/>
+      <c r="AP2" s="156"/>
+      <c r="AQ2" s="155" t="s">
         <v>79</v>
       </c>
-      <c r="AR2" s="143"/>
-      <c r="AS2" s="143"/>
-      <c r="AT2" s="144" t="s">
+      <c r="AR2" s="155"/>
+      <c r="AS2" s="155"/>
+      <c r="AT2" s="156" t="s">
         <v>81</v>
       </c>
-      <c r="AU2" s="144"/>
-      <c r="AV2" s="144"/>
-      <c r="AW2" s="143" t="s">
+      <c r="AU2" s="156"/>
+      <c r="AV2" s="156"/>
+      <c r="AW2" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="AX2" s="143"/>
-      <c r="AY2" s="143"/>
-      <c r="AZ2" s="144" t="s">
+      <c r="AX2" s="155"/>
+      <c r="AY2" s="155"/>
+      <c r="AZ2" s="156" t="s">
         <v>79</v>
       </c>
-      <c r="BA2" s="144"/>
-      <c r="BB2" s="144"/>
-      <c r="BC2" s="143" t="s">
+      <c r="BA2" s="156"/>
+      <c r="BB2" s="156"/>
+      <c r="BC2" s="155" t="s">
         <v>81</v>
       </c>
-      <c r="BD2" s="143"/>
-      <c r="BE2" s="143"/>
-      <c r="BF2" s="144" t="s">
+      <c r="BD2" s="155"/>
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="156" t="s">
         <v>83</v>
       </c>
-      <c r="BG2" s="144"/>
-      <c r="BH2" s="144"/>
-      <c r="BI2" s="143" t="s">
+      <c r="BG2" s="156"/>
+      <c r="BH2" s="156"/>
+      <c r="BI2" s="155" t="s">
         <v>93</v>
       </c>
-      <c r="BJ2" s="143"/>
-      <c r="BK2" s="143"/>
-      <c r="BL2" s="144" t="s">
+      <c r="BJ2" s="155"/>
+      <c r="BK2" s="155"/>
+      <c r="BL2" s="156" t="s">
         <v>95</v>
       </c>
-      <c r="BM2" s="144"/>
-      <c r="BN2" s="144"/>
-      <c r="BO2" s="143" t="s">
+      <c r="BM2" s="156"/>
+      <c r="BN2" s="156"/>
+      <c r="BO2" s="155" t="s">
         <v>97</v>
       </c>
-      <c r="BP2" s="143"/>
-      <c r="BQ2" s="143"/>
-      <c r="BR2" s="144" t="s">
+      <c r="BP2" s="155"/>
+      <c r="BQ2" s="155"/>
+      <c r="BR2" s="156" t="s">
         <v>99</v>
       </c>
-      <c r="BS2" s="144"/>
-      <c r="BT2" s="144"/>
-      <c r="BU2" s="143" t="s">
+      <c r="BS2" s="156"/>
+      <c r="BT2" s="156"/>
+      <c r="BU2" s="155" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="143"/>
-      <c r="BW2" s="143"/>
-      <c r="BX2" s="144" t="s">
+      <c r="BV2" s="155"/>
+      <c r="BW2" s="155"/>
+      <c r="BX2" s="156" t="s">
         <v>103</v>
       </c>
-      <c r="BY2" s="144"/>
-      <c r="BZ2" s="144"/>
-      <c r="CA2" s="143" t="s">
+      <c r="BY2" s="156"/>
+      <c r="BZ2" s="156"/>
+      <c r="CA2" s="155" t="s">
         <v>105</v>
       </c>
-      <c r="CB2" s="143"/>
-      <c r="CC2" s="143"/>
+      <c r="CB2" s="155"/>
+      <c r="CC2" s="155"/>
       <c r="CD2" s="41" t="s">
         <v>133</v>
       </c>
@@ -6490,10 +6482,10 @@
       <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="151" t="s">
+      <c r="F3" s="135" t="s">
         <v>135</v>
       </c>
-      <c r="G3" s="151" t="s">
+      <c r="G3" s="135" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -6502,7 +6494,7 @@
       <c r="I3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="J3" s="151" t="s">
+      <c r="J3" s="135" t="s">
         <v>131</v>
       </c>
       <c r="K3" s="8" t="s">
@@ -6741,17 +6733,17 @@
       <c r="E4" t="s">
         <v>148</v>
       </c>
-      <c r="F4" s="152">
-        <v>1</v>
-      </c>
-      <c r="G4" s="153">
+      <c r="F4" s="136">
+        <v>1</v>
+      </c>
+      <c r="G4" s="137">
         <v>2</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J4" s="164" t="s">
+      <c r="J4" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K4" s="6">
@@ -6948,17 +6940,17 @@
       <c r="E5" t="s">
         <v>158</v>
       </c>
-      <c r="F5" s="152">
-        <v>1</v>
-      </c>
-      <c r="G5" s="153">
+      <c r="F5" s="136">
+        <v>1</v>
+      </c>
+      <c r="G5" s="137">
         <v>2</v>
       </c>
       <c r="H5" s="11"/>
       <c r="I5" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J5" s="164" t="s">
+      <c r="J5" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K5" s="6">
@@ -7149,17 +7141,17 @@
       <c r="E6" t="s">
         <v>163</v>
       </c>
-      <c r="F6" s="152">
-        <v>1</v>
-      </c>
-      <c r="G6" s="153">
+      <c r="F6" s="136">
+        <v>1</v>
+      </c>
+      <c r="G6" s="137">
         <v>2</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J6" s="164" t="s">
+      <c r="J6" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K6" s="6">
@@ -7350,17 +7342,17 @@
       <c r="E7" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="152">
-        <v>1</v>
-      </c>
-      <c r="G7" s="153">
+      <c r="F7" s="136">
+        <v>1</v>
+      </c>
+      <c r="G7" s="137">
         <v>2</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J7" s="164" t="s">
+      <c r="J7" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K7" s="6">
@@ -7551,17 +7543,17 @@
       <c r="E8" t="s">
         <v>175</v>
       </c>
-      <c r="F8" s="152">
-        <v>1</v>
-      </c>
-      <c r="G8" s="153">
+      <c r="F8" s="136">
+        <v>1</v>
+      </c>
+      <c r="G8" s="137">
         <v>2</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J8" s="154">
+      <c r="J8" s="138">
         <v>3</v>
       </c>
       <c r="K8" s="6">
@@ -7801,17 +7793,17 @@
       <c r="E9" t="s">
         <v>177</v>
       </c>
-      <c r="F9" s="152">
-        <v>1</v>
-      </c>
-      <c r="G9" s="152">
+      <c r="F9" s="136">
+        <v>1</v>
+      </c>
+      <c r="G9" s="136">
         <v>1</v>
       </c>
       <c r="H9" s="11"/>
       <c r="I9" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J9" s="164" t="s">
+      <c r="J9" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K9" s="6">
@@ -7997,17 +7989,17 @@
       <c r="E10" t="s">
         <v>182</v>
       </c>
-      <c r="F10" s="152">
-        <v>1</v>
-      </c>
-      <c r="G10" s="153">
+      <c r="F10" s="136">
+        <v>1</v>
+      </c>
+      <c r="G10" s="137">
         <v>2</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J10" s="153">
+      <c r="J10" s="137">
         <v>2</v>
       </c>
       <c r="K10" s="6">
@@ -8247,17 +8239,17 @@
       <c r="E11" t="s">
         <v>186</v>
       </c>
-      <c r="F11" s="152">
-        <v>1</v>
-      </c>
-      <c r="G11" s="153">
+      <c r="F11" s="136">
+        <v>1</v>
+      </c>
+      <c r="G11" s="137">
         <v>2</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J11" s="164" t="s">
+      <c r="J11" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K11" s="6">
@@ -8449,17 +8441,17 @@
       <c r="E12" t="s">
         <v>190</v>
       </c>
-      <c r="F12" s="152">
-        <v>1</v>
-      </c>
-      <c r="G12" s="153">
+      <c r="F12" s="136">
+        <v>1</v>
+      </c>
+      <c r="G12" s="137">
         <v>2</v>
       </c>
       <c r="H12" s="11"/>
       <c r="I12" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J12" s="164" t="s">
+      <c r="J12" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K12" s="6">
@@ -8657,17 +8649,17 @@
       <c r="E13" t="s">
         <v>194</v>
       </c>
-      <c r="F13" s="152">
-        <v>1</v>
-      </c>
-      <c r="G13" s="152">
+      <c r="F13" s="136">
+        <v>1</v>
+      </c>
+      <c r="G13" s="136">
         <v>1</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J13" s="164" t="s">
+      <c r="J13" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K13" s="6">
@@ -8901,17 +8893,17 @@
       <c r="E14" t="s">
         <v>163</v>
       </c>
-      <c r="F14" s="152">
-        <v>1</v>
-      </c>
-      <c r="G14" s="153">
+      <c r="F14" s="136">
+        <v>1</v>
+      </c>
+      <c r="G14" s="137">
         <v>2</v>
       </c>
       <c r="H14" s="11"/>
       <c r="I14" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J14" s="164" t="s">
+      <c r="J14" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K14" s="6">
@@ -9103,17 +9095,17 @@
       <c r="E15" t="s">
         <v>201</v>
       </c>
-      <c r="F15" s="152">
-        <v>1</v>
-      </c>
-      <c r="G15" s="152">
+      <c r="F15" s="136">
+        <v>1</v>
+      </c>
+      <c r="G15" s="136">
         <v>1</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J15" s="153">
+      <c r="J15" s="137">
         <v>2</v>
       </c>
       <c r="K15" s="6">
@@ -9353,17 +9345,17 @@
       <c r="E16" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="153">
+      <c r="F16" s="137">
         <v>2</v>
       </c>
-      <c r="G16" s="153">
+      <c r="G16" s="137">
         <v>2</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="16" t="s">
         <v>760</v>
       </c>
-      <c r="J16" s="165">
+      <c r="J16" s="148">
         <v>1</v>
       </c>
       <c r="K16" s="6">
@@ -9585,17 +9577,17 @@
       <c r="E17" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="154">
+      <c r="F17" s="138">
         <v>3</v>
       </c>
-      <c r="G17" s="153">
+      <c r="G17" s="137">
         <v>2</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J17" s="164" t="s">
+      <c r="J17" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K17" s="6">
@@ -9757,17 +9749,17 @@
       <c r="E18" t="s">
         <v>215</v>
       </c>
-      <c r="F18" s="152">
-        <v>1</v>
-      </c>
-      <c r="G18" s="153">
+      <c r="F18" s="136">
+        <v>1</v>
+      </c>
+      <c r="G18" s="137">
         <v>2</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="164" t="s">
+      <c r="J18" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K18" s="6">
@@ -9953,17 +9945,17 @@
       <c r="E19" t="s">
         <v>219</v>
       </c>
-      <c r="F19" s="152">
-        <v>1</v>
-      </c>
-      <c r="G19" s="153">
+      <c r="F19" s="136">
+        <v>1</v>
+      </c>
+      <c r="G19" s="137">
         <v>2</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J19" s="164" t="s">
+      <c r="J19" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K19" s="6">
@@ -10161,17 +10153,17 @@
       <c r="E20" t="s">
         <v>224</v>
       </c>
-      <c r="F20" s="154">
+      <c r="F20" s="138">
         <v>3</v>
       </c>
-      <c r="G20" s="152">
+      <c r="G20" s="136">
         <v>1</v>
       </c>
       <c r="H20" s="11"/>
       <c r="I20" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J20" s="164" t="s">
+      <c r="J20" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K20" s="6">
@@ -10333,17 +10325,17 @@
       <c r="E21" t="s">
         <v>228</v>
       </c>
-      <c r="F21" s="152">
-        <v>1</v>
-      </c>
-      <c r="G21" s="153">
+      <c r="F21" s="136">
+        <v>1</v>
+      </c>
+      <c r="G21" s="137">
         <v>2</v>
       </c>
       <c r="H21" s="11"/>
       <c r="I21" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J21" s="164" t="s">
+      <c r="J21" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K21" s="6">
@@ -10541,17 +10533,17 @@
       <c r="E22" t="s">
         <v>232</v>
       </c>
-      <c r="F22" s="152">
-        <v>1</v>
-      </c>
-      <c r="G22" s="153">
+      <c r="F22" s="136">
+        <v>1</v>
+      </c>
+      <c r="G22" s="137">
         <v>2</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J22" s="164" t="s">
+      <c r="J22" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K22" s="6">
@@ -10749,17 +10741,17 @@
       <c r="E23" t="s">
         <v>236</v>
       </c>
-      <c r="F23" s="153">
+      <c r="F23" s="137">
         <v>2</v>
       </c>
-      <c r="G23" s="152">
+      <c r="G23" s="136">
         <v>1</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J23" s="164" t="s">
+      <c r="J23" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K23" s="6">
@@ -10921,17 +10913,17 @@
       <c r="E24" t="s">
         <v>240</v>
       </c>
-      <c r="F24" s="154">
+      <c r="F24" s="138">
         <v>3</v>
       </c>
-      <c r="G24" s="153">
+      <c r="G24" s="137">
         <v>2</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J24" s="164" t="s">
+      <c r="J24" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K24" s="6">
@@ -11093,17 +11085,17 @@
       <c r="E25" t="s">
         <v>244</v>
       </c>
-      <c r="F25" s="152">
-        <v>1</v>
-      </c>
-      <c r="G25" s="152">
+      <c r="F25" s="136">
+        <v>1</v>
+      </c>
+      <c r="G25" s="136">
         <v>1</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J25" s="164" t="s">
+      <c r="J25" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K25" s="6">
@@ -11301,17 +11293,17 @@
       <c r="E26" t="s">
         <v>248</v>
       </c>
-      <c r="F26" s="152">
-        <v>1</v>
-      </c>
-      <c r="G26" s="153">
+      <c r="F26" s="136">
+        <v>1</v>
+      </c>
+      <c r="G26" s="137">
         <v>2</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J26" s="164" t="s">
+      <c r="J26" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K26" s="6">
@@ -11503,17 +11495,17 @@
       <c r="E27" t="s">
         <v>252</v>
       </c>
-      <c r="F27" s="152">
-        <v>1</v>
-      </c>
-      <c r="G27" s="153">
+      <c r="F27" s="136">
+        <v>1</v>
+      </c>
+      <c r="G27" s="137">
         <v>2</v>
       </c>
       <c r="H27" s="11"/>
       <c r="I27" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J27" s="164" t="s">
+      <c r="J27" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K27" s="6">
@@ -11711,17 +11703,17 @@
       <c r="E28" t="s">
         <v>256</v>
       </c>
-      <c r="F28" s="152">
-        <v>1</v>
-      </c>
-      <c r="G28" s="152">
+      <c r="F28" s="136">
+        <v>1</v>
+      </c>
+      <c r="G28" s="136">
         <v>1</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J28" s="164" t="s">
+      <c r="J28" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K28" s="6">
@@ -11913,17 +11905,17 @@
       <c r="E29" t="s">
         <v>260</v>
       </c>
-      <c r="F29" s="154">
+      <c r="F29" s="138">
         <v>3</v>
       </c>
-      <c r="G29" s="152">
+      <c r="G29" s="136">
         <v>1</v>
       </c>
       <c r="H29" s="11"/>
       <c r="I29" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J29" s="164" t="s">
+      <c r="J29" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K29" s="6">
@@ -12070,10 +12062,10 @@
       <c r="CF29" s="33"/>
     </row>
     <row r="30" spans="1:84">
-      <c r="A30" s="139" t="s">
+      <c r="A30" s="166" t="s">
         <v>261</v>
       </c>
-      <c r="B30" s="140" t="s">
+      <c r="B30" s="167" t="s">
         <v>262</v>
       </c>
       <c r="C30" t="s">
@@ -12085,17 +12077,17 @@
       <c r="E30" t="s">
         <v>264</v>
       </c>
-      <c r="F30" s="152">
-        <v>1</v>
-      </c>
-      <c r="G30" s="153">
+      <c r="F30" s="136">
+        <v>1</v>
+      </c>
+      <c r="G30" s="137">
         <v>2</v>
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J30" s="165">
+      <c r="J30" s="148">
         <v>1</v>
       </c>
       <c r="K30" s="6">
@@ -12329,17 +12321,17 @@
       <c r="E31" t="s">
         <v>268</v>
       </c>
-      <c r="F31" s="152">
-        <v>1</v>
-      </c>
-      <c r="G31" s="153">
+      <c r="F31" s="136">
+        <v>1</v>
+      </c>
+      <c r="G31" s="137">
         <v>2</v>
       </c>
       <c r="H31" s="11"/>
       <c r="I31" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J31" s="164" t="s">
+      <c r="J31" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K31" s="6">
@@ -12537,17 +12529,17 @@
       <c r="E32" t="s">
         <v>272</v>
       </c>
-      <c r="F32" s="152">
-        <v>1</v>
-      </c>
-      <c r="G32" s="152">
+      <c r="F32" s="136">
+        <v>1</v>
+      </c>
+      <c r="G32" s="136">
         <v>1</v>
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J32" s="164" t="s">
+      <c r="J32" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K32" s="6">
@@ -12767,17 +12759,17 @@
       <c r="E33" t="s">
         <v>275</v>
       </c>
-      <c r="F33" s="153">
+      <c r="F33" s="137">
         <v>2</v>
       </c>
-      <c r="G33" s="153">
+      <c r="G33" s="137">
         <v>2</v>
       </c>
       <c r="H33" s="11"/>
       <c r="I33" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J33" s="164" t="s">
+      <c r="J33" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K33" s="6">
@@ -12939,17 +12931,17 @@
       <c r="E34" t="s">
         <v>194</v>
       </c>
-      <c r="F34" s="152">
-        <v>1</v>
-      </c>
-      <c r="G34" s="153">
+      <c r="F34" s="136">
+        <v>1</v>
+      </c>
+      <c r="G34" s="137">
         <v>2</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="J34" s="164" t="s">
+      <c r="J34" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K34" s="6">
@@ -13189,17 +13181,17 @@
       <c r="E35" t="s">
         <v>282</v>
       </c>
-      <c r="F35" s="153">
+      <c r="F35" s="137">
         <v>2</v>
       </c>
-      <c r="G35" s="153">
+      <c r="G35" s="137">
         <v>2</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J35" s="165">
+      <c r="J35" s="148">
         <v>1</v>
       </c>
       <c r="K35" s="6">
@@ -13421,17 +13413,17 @@
       <c r="E36" t="s">
         <v>286</v>
       </c>
-      <c r="F36" s="153">
+      <c r="F36" s="137">
         <v>2</v>
       </c>
-      <c r="G36" s="153">
+      <c r="G36" s="137">
         <v>2</v>
       </c>
       <c r="H36" s="9"/>
       <c r="I36" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J36" s="165">
+      <c r="J36" s="148">
         <v>1</v>
       </c>
       <c r="K36" s="6">
@@ -13653,17 +13645,17 @@
       <c r="E37" t="s">
         <v>289</v>
       </c>
-      <c r="F37" s="153">
+      <c r="F37" s="137">
         <v>2</v>
       </c>
-      <c r="G37" s="153">
+      <c r="G37" s="137">
         <v>2</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J37" s="165">
+      <c r="J37" s="148">
         <v>1</v>
       </c>
       <c r="K37" s="6">
@@ -13885,17 +13877,17 @@
       <c r="E38" t="s">
         <v>292</v>
       </c>
-      <c r="F38" s="153">
+      <c r="F38" s="137">
         <v>2</v>
       </c>
-      <c r="G38" s="153">
+      <c r="G38" s="137">
         <v>2</v>
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J38" s="165">
+      <c r="J38" s="148">
         <v>1</v>
       </c>
       <c r="K38" s="6">
@@ -14117,17 +14109,17 @@
       <c r="E39" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="F39" s="153">
+      <c r="F39" s="137">
         <v>2</v>
       </c>
-      <c r="G39" s="153">
+      <c r="G39" s="137">
         <v>2</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J39" s="153">
+      <c r="J39" s="137">
         <v>2</v>
       </c>
       <c r="K39" s="6">
@@ -14343,17 +14335,17 @@
       <c r="E40" t="s">
         <v>300</v>
       </c>
-      <c r="F40" s="153">
+      <c r="F40" s="137">
         <v>2</v>
       </c>
-      <c r="G40" s="153">
+      <c r="G40" s="137">
         <v>2</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J40" s="165">
+      <c r="J40" s="148">
         <v>1</v>
       </c>
       <c r="K40" s="6">
@@ -14571,17 +14563,17 @@
       <c r="E41" t="s">
         <v>194</v>
       </c>
-      <c r="F41" s="153">
+      <c r="F41" s="137">
         <v>2</v>
       </c>
-      <c r="G41" s="153">
+      <c r="G41" s="137">
         <v>2</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J41" s="165">
+      <c r="J41" s="148">
         <v>1</v>
       </c>
       <c r="K41" s="6">
@@ -14797,17 +14789,17 @@
       <c r="E42" t="s">
         <v>194</v>
       </c>
-      <c r="F42" s="153">
+      <c r="F42" s="137">
         <v>2</v>
       </c>
-      <c r="G42" s="153">
+      <c r="G42" s="137">
         <v>2</v>
       </c>
       <c r="H42" s="9"/>
       <c r="I42" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J42" s="165">
+      <c r="J42" s="148">
         <v>1</v>
       </c>
       <c r="K42" s="6">
@@ -15023,17 +15015,17 @@
       <c r="E43" t="s">
         <v>307</v>
       </c>
-      <c r="F43" s="153">
+      <c r="F43" s="137">
         <v>2</v>
       </c>
-      <c r="G43" s="153">
+      <c r="G43" s="137">
         <v>2</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J43" s="165">
+      <c r="J43" s="148">
         <v>1</v>
       </c>
       <c r="K43" s="6">
@@ -15249,17 +15241,17 @@
       <c r="E44" t="s">
         <v>310</v>
       </c>
-      <c r="F44" s="153">
+      <c r="F44" s="137">
         <v>2</v>
       </c>
-      <c r="G44" s="153">
+      <c r="G44" s="137">
         <v>2</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J44" s="165">
+      <c r="J44" s="148">
         <v>1</v>
       </c>
       <c r="K44" s="6">
@@ -15477,17 +15469,17 @@
       <c r="E45" t="s">
         <v>186</v>
       </c>
-      <c r="F45" s="153">
+      <c r="F45" s="137">
         <v>2</v>
       </c>
-      <c r="G45" s="153">
+      <c r="G45" s="137">
         <v>2</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J45" s="165">
+      <c r="J45" s="148">
         <v>1</v>
       </c>
       <c r="K45" s="6">
@@ -15705,17 +15697,17 @@
       <c r="E46" t="s">
         <v>315</v>
       </c>
-      <c r="F46" s="153">
+      <c r="F46" s="137">
         <v>2</v>
       </c>
-      <c r="G46" s="153">
+      <c r="G46" s="137">
         <v>2</v>
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J46" s="165">
+      <c r="J46" s="148">
         <v>1</v>
       </c>
       <c r="K46" s="6">
@@ -15931,17 +15923,17 @@
       <c r="E47" t="s">
         <v>318</v>
       </c>
-      <c r="F47" s="153">
+      <c r="F47" s="137">
         <v>2</v>
       </c>
-      <c r="G47" s="153">
+      <c r="G47" s="137">
         <v>2</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J47" s="165">
+      <c r="J47" s="148">
         <v>1</v>
       </c>
       <c r="K47" s="6">
@@ -16163,17 +16155,17 @@
       <c r="E48" t="s">
         <v>318</v>
       </c>
-      <c r="F48" s="153">
+      <c r="F48" s="137">
         <v>2</v>
       </c>
-      <c r="G48" s="153">
+      <c r="G48" s="137">
         <v>2</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J48" s="165">
+      <c r="J48" s="148">
         <v>1</v>
       </c>
       <c r="K48" s="6">
@@ -16389,17 +16381,17 @@
       <c r="E49" t="s">
         <v>318</v>
       </c>
-      <c r="F49" s="153">
+      <c r="F49" s="137">
         <v>2</v>
       </c>
-      <c r="G49" s="153">
+      <c r="G49" s="137">
         <v>2</v>
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J49" s="165">
+      <c r="J49" s="148">
         <v>1</v>
       </c>
       <c r="K49" s="6">
@@ -16621,17 +16613,17 @@
       <c r="E50" t="s">
         <v>318</v>
       </c>
-      <c r="F50" s="153">
+      <c r="F50" s="137">
         <v>2</v>
       </c>
-      <c r="G50" s="153">
+      <c r="G50" s="137">
         <v>2</v>
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J50" s="165">
+      <c r="J50" s="148">
         <v>1</v>
       </c>
       <c r="K50" s="6">
@@ -16853,17 +16845,17 @@
       <c r="E51" t="s">
         <v>318</v>
       </c>
-      <c r="F51" s="153">
+      <c r="F51" s="137">
         <v>2</v>
       </c>
-      <c r="G51" s="153">
+      <c r="G51" s="137">
         <v>2</v>
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J51" s="165">
+      <c r="J51" s="148">
         <v>1</v>
       </c>
       <c r="K51" s="6">
@@ -17085,17 +17077,17 @@
       <c r="E52" t="s">
         <v>329</v>
       </c>
-      <c r="F52" s="153">
+      <c r="F52" s="137">
         <v>2</v>
       </c>
-      <c r="G52" s="153">
+      <c r="G52" s="137">
         <v>2</v>
       </c>
       <c r="H52" s="9"/>
       <c r="I52" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J52" s="165">
+      <c r="J52" s="148">
         <v>1</v>
       </c>
       <c r="K52" s="6">
@@ -17313,17 +17305,17 @@
       <c r="E53" t="s">
         <v>332</v>
       </c>
-      <c r="F53" s="153">
+      <c r="F53" s="137">
         <v>2</v>
       </c>
-      <c r="G53" s="153">
+      <c r="G53" s="137">
         <v>2</v>
       </c>
       <c r="H53" s="9"/>
       <c r="I53" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J53" s="165">
+      <c r="J53" s="148">
         <v>1</v>
       </c>
       <c r="K53" s="6">
@@ -17539,17 +17531,17 @@
       <c r="E54" t="s">
         <v>334</v>
       </c>
-      <c r="F54" s="152">
-        <v>1</v>
-      </c>
-      <c r="G54" s="153">
+      <c r="F54" s="136">
+        <v>1</v>
+      </c>
+      <c r="G54" s="137">
         <v>2</v>
       </c>
       <c r="H54" s="9"/>
       <c r="I54" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J54" s="165">
+      <c r="J54" s="148">
         <v>1</v>
       </c>
       <c r="K54" s="6">
@@ -17783,17 +17775,17 @@
       <c r="E55" t="s">
         <v>337</v>
       </c>
-      <c r="F55" s="153">
+      <c r="F55" s="137">
         <v>2</v>
       </c>
-      <c r="G55" s="153">
+      <c r="G55" s="137">
         <v>2</v>
       </c>
       <c r="H55" s="9"/>
       <c r="I55" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="J55" s="165">
+      <c r="J55" s="148">
         <v>1</v>
       </c>
       <c r="K55" s="6">
@@ -17961,17 +17953,17 @@
       <c r="E56" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F56" s="153">
+      <c r="F56" s="137">
         <v>2</v>
       </c>
-      <c r="G56" s="153">
+      <c r="G56" s="137">
         <v>2</v>
       </c>
       <c r="H56" s="9"/>
       <c r="I56" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J56" s="165">
+      <c r="J56" s="148">
         <v>1</v>
       </c>
       <c r="K56" s="6">
@@ -18193,17 +18185,17 @@
       <c r="E57" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F57" s="153">
+      <c r="F57" s="137">
         <v>2</v>
       </c>
-      <c r="G57" s="153">
+      <c r="G57" s="137">
         <v>2</v>
       </c>
       <c r="H57" s="9"/>
       <c r="I57" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J57" s="165">
+      <c r="J57" s="148">
         <v>1</v>
       </c>
       <c r="K57" s="6">
@@ -18425,17 +18417,17 @@
       <c r="E58" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F58" s="153">
+      <c r="F58" s="137">
         <v>2</v>
       </c>
-      <c r="G58" s="153">
+      <c r="G58" s="137">
         <v>2</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J58" s="165">
+      <c r="J58" s="148">
         <v>1</v>
       </c>
       <c r="K58" s="6">
@@ -18657,17 +18649,17 @@
       <c r="E59" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="F59" s="153">
+      <c r="F59" s="137">
         <v>2</v>
       </c>
-      <c r="G59" s="153">
+      <c r="G59" s="137">
         <v>2</v>
       </c>
       <c r="H59" s="9"/>
       <c r="I59" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J59" s="165">
+      <c r="J59" s="148">
         <v>1</v>
       </c>
       <c r="K59" s="7">
@@ -18889,17 +18881,17 @@
       <c r="E60" t="s">
         <v>315</v>
       </c>
-      <c r="F60" s="153">
+      <c r="F60" s="137">
         <v>2</v>
       </c>
-      <c r="G60" s="153">
+      <c r="G60" s="137">
         <v>2</v>
       </c>
       <c r="H60" s="9"/>
       <c r="I60" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J60" s="165">
+      <c r="J60" s="148">
         <v>1</v>
       </c>
       <c r="K60" s="6">
@@ -19025,17 +19017,17 @@
       <c r="E61" t="s">
         <v>260</v>
       </c>
-      <c r="F61" s="153">
+      <c r="F61" s="137">
         <v>2</v>
       </c>
-      <c r="G61" s="153">
+      <c r="G61" s="137">
         <v>2</v>
       </c>
       <c r="H61" s="9"/>
       <c r="I61" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J61" s="165">
+      <c r="J61" s="148">
         <v>1</v>
       </c>
       <c r="K61" s="6">
@@ -19161,17 +19153,17 @@
       <c r="E62" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="F62" s="153">
+      <c r="F62" s="137">
         <v>2</v>
       </c>
-      <c r="G62" s="153">
+      <c r="G62" s="137">
         <v>2</v>
       </c>
       <c r="H62" s="9"/>
       <c r="I62" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J62" s="165">
+      <c r="J62" s="148">
         <v>1</v>
       </c>
       <c r="K62" s="6">
@@ -19297,17 +19289,17 @@
       <c r="E63" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="F63" s="153">
+      <c r="F63" s="137">
         <v>2</v>
       </c>
-      <c r="G63" s="153">
+      <c r="G63" s="137">
         <v>2</v>
       </c>
       <c r="H63" s="9"/>
       <c r="I63" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J63" s="165">
+      <c r="J63" s="148">
         <v>1</v>
       </c>
       <c r="K63" s="6">
@@ -19433,17 +19425,17 @@
       <c r="E64" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="F64" s="153">
+      <c r="F64" s="137">
         <v>2</v>
       </c>
-      <c r="G64" s="153">
+      <c r="G64" s="137">
         <v>2</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J64" s="165">
+      <c r="J64" s="148">
         <v>1</v>
       </c>
       <c r="K64" s="6">
@@ -19569,17 +19561,17 @@
       <c r="E65" t="s">
         <v>194</v>
       </c>
-      <c r="F65" s="153">
+      <c r="F65" s="137">
         <v>2</v>
       </c>
-      <c r="G65" s="153">
+      <c r="G65" s="137">
         <v>2</v>
       </c>
       <c r="H65" s="9"/>
       <c r="I65" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J65" s="165">
+      <c r="J65" s="148">
         <v>1</v>
       </c>
       <c r="K65" s="6">
@@ -19705,17 +19697,17 @@
       <c r="E66" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="F66" s="153">
+      <c r="F66" s="137">
         <v>2</v>
       </c>
-      <c r="G66" s="153">
+      <c r="G66" s="137">
         <v>2</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J66" s="165">
+      <c r="J66" s="148">
         <v>1</v>
       </c>
       <c r="K66" s="6">
@@ -19841,17 +19833,17 @@
       <c r="E67" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="F67" s="153">
+      <c r="F67" s="137">
         <v>2</v>
       </c>
-      <c r="G67" s="153">
+      <c r="G67" s="137">
         <v>2</v>
       </c>
       <c r="H67" s="9"/>
       <c r="I67" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J67" s="165">
+      <c r="J67" s="148">
         <v>1</v>
       </c>
       <c r="K67" s="6">
@@ -19977,17 +19969,17 @@
       <c r="E68" t="s">
         <v>260</v>
       </c>
-      <c r="F68" s="153">
+      <c r="F68" s="137">
         <v>2</v>
       </c>
-      <c r="G68" s="153">
+      <c r="G68" s="137">
         <v>2</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J68" s="165">
+      <c r="J68" s="148">
         <v>1</v>
       </c>
       <c r="K68" s="6">
@@ -20097,7 +20089,7 @@
       </c>
       <c r="CF68" s="33"/>
     </row>
-    <row r="69" spans="1:84">
+    <row r="69" spans="1:84" hidden="1">
       <c r="A69" s="6" t="s">
         <v>372</v>
       </c>
@@ -20113,17 +20105,15 @@
       <c r="E69" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F69" s="152">
-        <v>1</v>
-      </c>
-      <c r="G69" s="153">
+      <c r="F69" s="136"/>
+      <c r="G69" s="137">
         <v>2</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J69" s="165">
+      <c r="J69" s="148">
         <v>1</v>
       </c>
       <c r="K69" s="6">
@@ -20233,7 +20223,7 @@
       </c>
       <c r="CF69" s="33"/>
     </row>
-    <row r="70" spans="1:84">
+    <row r="70" spans="1:84" hidden="1">
       <c r="A70" s="6" t="s">
         <v>376</v>
       </c>
@@ -20249,17 +20239,15 @@
       <c r="E70" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F70" s="152">
-        <v>1</v>
-      </c>
-      <c r="G70" s="153">
+      <c r="F70" s="136"/>
+      <c r="G70" s="137">
         <v>2</v>
       </c>
       <c r="H70" s="9"/>
       <c r="I70" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J70" s="165">
+      <c r="J70" s="148">
         <v>1</v>
       </c>
       <c r="K70" s="6">
@@ -20385,17 +20373,17 @@
       <c r="E71" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F71" s="152">
-        <v>1</v>
-      </c>
-      <c r="G71" s="153">
+      <c r="F71" s="136">
+        <v>1</v>
+      </c>
+      <c r="G71" s="137">
         <v>2</v>
       </c>
       <c r="H71" s="9"/>
       <c r="I71" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J71" s="165">
+      <c r="J71" s="148">
         <v>1</v>
       </c>
       <c r="K71" s="6">
@@ -20505,7 +20493,7 @@
       </c>
       <c r="CF71" s="33"/>
     </row>
-    <row r="72" spans="1:84">
+    <row r="72" spans="1:84" hidden="1">
       <c r="A72" s="6" t="s">
         <v>380</v>
       </c>
@@ -20521,17 +20509,15 @@
       <c r="E72" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F72" s="152">
-        <v>1</v>
-      </c>
-      <c r="G72" s="153">
+      <c r="F72" s="136"/>
+      <c r="G72" s="137">
         <v>2</v>
       </c>
       <c r="H72" s="9"/>
       <c r="I72" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J72" s="165">
+      <c r="J72" s="148">
         <v>1</v>
       </c>
       <c r="K72" s="6">
@@ -20641,7 +20627,7 @@
       </c>
       <c r="CF72" s="33"/>
     </row>
-    <row r="73" spans="1:84">
+    <row r="73" spans="1:84" hidden="1">
       <c r="A73" s="6" t="s">
         <v>382</v>
       </c>
@@ -20657,17 +20643,15 @@
       <c r="E73" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F73" s="152">
-        <v>1</v>
-      </c>
-      <c r="G73" s="153">
+      <c r="F73" s="136"/>
+      <c r="G73" s="137">
         <v>2</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J73" s="165">
+      <c r="J73" s="148">
         <v>1</v>
       </c>
       <c r="K73" s="6">
@@ -20793,17 +20777,17 @@
       <c r="E74" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F74" s="152">
-        <v>1</v>
-      </c>
-      <c r="G74" s="153">
+      <c r="F74" s="136">
+        <v>1</v>
+      </c>
+      <c r="G74" s="137">
         <v>2</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J74" s="165">
+      <c r="J74" s="148">
         <v>1</v>
       </c>
       <c r="K74" s="6">
@@ -20929,17 +20913,17 @@
       <c r="E75" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F75" s="152">
-        <v>1</v>
-      </c>
-      <c r="G75" s="153">
+      <c r="F75" s="136">
+        <v>1</v>
+      </c>
+      <c r="G75" s="137">
         <v>2</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J75" s="165">
+      <c r="J75" s="148">
         <v>1</v>
       </c>
       <c r="K75" s="6">
@@ -21065,17 +21049,17 @@
       <c r="E76" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F76" s="152">
-        <v>1</v>
-      </c>
-      <c r="G76" s="153">
+      <c r="F76" s="136">
+        <v>1</v>
+      </c>
+      <c r="G76" s="137">
         <v>2</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J76" s="165">
+      <c r="J76" s="148">
         <v>1</v>
       </c>
       <c r="K76" s="6">
@@ -21201,17 +21185,17 @@
       <c r="E77" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F77" s="152">
-        <v>1</v>
-      </c>
-      <c r="G77" s="153">
+      <c r="F77" s="136">
+        <v>1</v>
+      </c>
+      <c r="G77" s="137">
         <v>2</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J77" s="165">
+      <c r="J77" s="148">
         <v>1</v>
       </c>
       <c r="K77" s="6">
@@ -21337,17 +21321,17 @@
       <c r="E78" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F78" s="152">
-        <v>1</v>
-      </c>
-      <c r="G78" s="153">
+      <c r="F78" s="136">
+        <v>1</v>
+      </c>
+      <c r="G78" s="137">
         <v>2</v>
       </c>
       <c r="H78" s="9"/>
       <c r="I78" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J78" s="165">
+      <c r="J78" s="148">
         <v>1</v>
       </c>
       <c r="K78" s="6">
@@ -21457,7 +21441,7 @@
       </c>
       <c r="CF78" s="33"/>
     </row>
-    <row r="79" spans="1:84">
+    <row r="79" spans="1:84" hidden="1">
       <c r="A79" s="6" t="s">
         <v>394</v>
       </c>
@@ -21473,17 +21457,15 @@
       <c r="E79" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F79" s="152">
-        <v>1</v>
-      </c>
-      <c r="G79" s="153">
+      <c r="F79" s="136"/>
+      <c r="G79" s="137">
         <v>2</v>
       </c>
       <c r="H79" s="9"/>
       <c r="I79" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J79" s="165">
+      <c r="J79" s="148">
         <v>1</v>
       </c>
       <c r="K79" s="6">
@@ -21609,17 +21591,17 @@
       <c r="E80" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F80" s="152">
-        <v>1</v>
-      </c>
-      <c r="G80" s="153">
+      <c r="F80" s="136">
+        <v>1</v>
+      </c>
+      <c r="G80" s="137">
         <v>2</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J80" s="165">
+      <c r="J80" s="148">
         <v>1</v>
       </c>
       <c r="K80" s="6">
@@ -21745,17 +21727,17 @@
       <c r="E81" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F81" s="152">
-        <v>1</v>
-      </c>
-      <c r="G81" s="153">
+      <c r="F81" s="136">
+        <v>1</v>
+      </c>
+      <c r="G81" s="137">
         <v>2</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J81" s="165">
+      <c r="J81" s="148">
         <v>1</v>
       </c>
       <c r="K81" s="6">
@@ -21881,17 +21863,17 @@
       <c r="E82" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F82" s="152">
-        <v>1</v>
-      </c>
-      <c r="G82" s="153">
+      <c r="F82" s="136">
+        <v>1</v>
+      </c>
+      <c r="G82" s="137">
         <v>2</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J82" s="165">
+      <c r="J82" s="148">
         <v>1</v>
       </c>
       <c r="K82" s="6">
@@ -22001,7 +21983,7 @@
       </c>
       <c r="CF82" s="33"/>
     </row>
-    <row r="83" spans="1:84">
+    <row r="83" spans="1:84" hidden="1">
       <c r="A83" s="6" t="s">
         <v>402</v>
       </c>
@@ -22017,17 +21999,15 @@
       <c r="E83" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F83" s="152">
-        <v>1</v>
-      </c>
-      <c r="G83" s="153">
+      <c r="F83" s="136"/>
+      <c r="G83" s="137">
         <v>2</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J83" s="165">
+      <c r="J83" s="148">
         <v>1</v>
       </c>
       <c r="K83" s="6">
@@ -22153,17 +22133,17 @@
       <c r="E84" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="F84" s="152">
-        <v>1</v>
-      </c>
-      <c r="G84" s="153">
+      <c r="F84" s="136">
+        <v>1</v>
+      </c>
+      <c r="G84" s="137">
         <v>2</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J84" s="165">
+      <c r="J84" s="148">
         <v>1</v>
       </c>
       <c r="K84" s="6">
@@ -22289,17 +22269,17 @@
       <c r="E85" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="F85" s="152">
-        <v>1</v>
-      </c>
-      <c r="G85" s="153">
+      <c r="F85" s="136">
+        <v>1</v>
+      </c>
+      <c r="G85" s="137">
         <v>2</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J85" s="165">
+      <c r="J85" s="148">
         <v>1</v>
       </c>
       <c r="K85" s="6">
@@ -22409,7 +22389,7 @@
       </c>
       <c r="CF85" s="33"/>
     </row>
-    <row r="86" spans="1:84">
+    <row r="86" spans="1:84" hidden="1">
       <c r="A86" s="6" t="s">
         <v>410</v>
       </c>
@@ -22425,17 +22405,15 @@
       <c r="E86" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="F86" s="152">
-        <v>1</v>
-      </c>
-      <c r="G86" s="153">
+      <c r="F86" s="136"/>
+      <c r="G86" s="137">
         <v>2</v>
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J86" s="165">
+      <c r="J86" s="148">
         <v>1</v>
       </c>
       <c r="K86" s="6">
@@ -22545,7 +22523,7 @@
       </c>
       <c r="CF86" s="33"/>
     </row>
-    <row r="87" spans="1:84">
+    <row r="87" spans="1:84" hidden="1">
       <c r="A87" s="6" t="s">
         <v>413</v>
       </c>
@@ -22561,17 +22539,15 @@
       <c r="E87" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="F87" s="152">
-        <v>1</v>
-      </c>
-      <c r="G87" s="153">
+      <c r="F87" s="136"/>
+      <c r="G87" s="137">
         <v>2</v>
       </c>
       <c r="H87" s="9"/>
       <c r="I87" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J87" s="165">
+      <c r="J87" s="148">
         <v>1</v>
       </c>
       <c r="K87" s="6">
@@ -22697,17 +22673,17 @@
       <c r="E88" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="F88" s="153">
+      <c r="F88" s="137">
         <v>2</v>
       </c>
-      <c r="G88" s="153">
+      <c r="G88" s="137">
         <v>2</v>
       </c>
       <c r="H88" s="9"/>
       <c r="I88" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J88" s="165">
+      <c r="J88" s="148">
         <v>1</v>
       </c>
       <c r="K88" s="6">
@@ -22833,17 +22809,17 @@
       <c r="E89" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="F89" s="153">
+      <c r="F89" s="137">
         <v>2</v>
       </c>
-      <c r="G89" s="153">
+      <c r="G89" s="137">
         <v>2</v>
       </c>
       <c r="H89" s="9"/>
       <c r="I89" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J89" s="165">
+      <c r="J89" s="148">
         <v>1</v>
       </c>
       <c r="K89" s="6">
@@ -22969,17 +22945,17 @@
       <c r="E90" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="F90" s="153">
+      <c r="F90" s="137">
         <v>2</v>
       </c>
-      <c r="G90" s="153">
+      <c r="G90" s="137">
         <v>2</v>
       </c>
       <c r="H90" s="9"/>
       <c r="I90" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J90" s="165">
+      <c r="J90" s="148">
         <v>1</v>
       </c>
       <c r="K90" s="6">
@@ -23105,17 +23081,17 @@
       <c r="E91" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="F91" s="153">
+      <c r="F91" s="137">
         <v>2</v>
       </c>
-      <c r="G91" s="153">
+      <c r="G91" s="137">
         <v>2</v>
       </c>
       <c r="H91" s="9"/>
       <c r="I91" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J91" s="165">
+      <c r="J91" s="148">
         <v>1</v>
       </c>
       <c r="K91" s="6">
@@ -23241,17 +23217,17 @@
       <c r="E92" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="F92" s="153">
+      <c r="F92" s="137">
         <v>2</v>
       </c>
-      <c r="G92" s="153">
+      <c r="G92" s="137">
         <v>2</v>
       </c>
       <c r="H92" s="9"/>
       <c r="I92" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J92" s="165">
+      <c r="J92" s="148">
         <v>1</v>
       </c>
       <c r="K92" s="6">
@@ -23377,17 +23353,17 @@
       <c r="E93" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="F93" s="153">
+      <c r="F93" s="137">
         <v>2</v>
       </c>
-      <c r="G93" s="153">
+      <c r="G93" s="137">
         <v>2</v>
       </c>
       <c r="H93" s="9"/>
       <c r="I93" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J93" s="165">
+      <c r="J93" s="148">
         <v>1</v>
       </c>
       <c r="K93" s="6">
@@ -23513,17 +23489,17 @@
       <c r="E94" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="F94" s="153">
+      <c r="F94" s="137">
         <v>2</v>
       </c>
-      <c r="G94" s="153">
+      <c r="G94" s="137">
         <v>2</v>
       </c>
       <c r="H94" s="9"/>
       <c r="I94" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J94" s="165">
+      <c r="J94" s="148">
         <v>1</v>
       </c>
       <c r="K94" s="6">
@@ -23649,17 +23625,17 @@
       <c r="E95" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="F95" s="153">
+      <c r="F95" s="137">
         <v>2</v>
       </c>
-      <c r="G95" s="152">
+      <c r="G95" s="136">
         <v>1</v>
       </c>
       <c r="H95" s="9"/>
       <c r="I95" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J95" s="165">
+      <c r="J95" s="148">
         <v>1</v>
       </c>
       <c r="K95" s="7">
@@ -23785,17 +23761,17 @@
       <c r="E96" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="F96" s="153">
+      <c r="F96" s="137">
         <v>2</v>
       </c>
-      <c r="G96" s="152">
+      <c r="G96" s="136">
         <v>1</v>
       </c>
       <c r="H96" s="9"/>
       <c r="I96" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J96" s="165">
+      <c r="J96" s="148">
         <v>1</v>
       </c>
       <c r="K96" s="7">
@@ -23921,17 +23897,17 @@
       <c r="E97" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="F97" s="153">
+      <c r="F97" s="137">
         <v>2</v>
       </c>
-      <c r="G97" s="152">
+      <c r="G97" s="136">
         <v>1</v>
       </c>
       <c r="H97" s="9"/>
       <c r="I97" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J97" s="165">
+      <c r="J97" s="148">
         <v>1</v>
       </c>
       <c r="K97" s="7">
@@ -24057,17 +24033,17 @@
       <c r="E98" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="F98" s="153">
+      <c r="F98" s="137">
         <v>2</v>
       </c>
-      <c r="G98" s="152">
+      <c r="G98" s="136">
         <v>1</v>
       </c>
       <c r="H98" s="9"/>
       <c r="I98" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J98" s="165">
+      <c r="J98" s="148">
         <v>1</v>
       </c>
       <c r="K98" s="7">
@@ -24193,17 +24169,17 @@
       <c r="E99" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="F99" s="153">
+      <c r="F99" s="137">
         <v>2</v>
       </c>
-      <c r="G99" s="152">
+      <c r="G99" s="136">
         <v>1</v>
       </c>
       <c r="H99" s="9"/>
       <c r="I99" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J99" s="165">
+      <c r="J99" s="148">
         <v>1</v>
       </c>
       <c r="K99" s="7">
@@ -24329,17 +24305,17 @@
       <c r="E100" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="F100" s="153">
+      <c r="F100" s="137">
         <v>2</v>
       </c>
-      <c r="G100" s="152">
+      <c r="G100" s="136">
         <v>1</v>
       </c>
       <c r="H100" s="9"/>
       <c r="I100" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J100" s="165">
+      <c r="J100" s="148">
         <v>1</v>
       </c>
       <c r="K100" s="7">
@@ -24465,17 +24441,17 @@
       <c r="E101" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="F101" s="153">
+      <c r="F101" s="137">
         <v>2</v>
       </c>
-      <c r="G101" s="153">
+      <c r="G101" s="137">
         <v>2</v>
       </c>
       <c r="H101" s="9"/>
       <c r="I101" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J101" s="165">
+      <c r="J101" s="148">
         <v>1</v>
       </c>
       <c r="K101" s="7">
@@ -24601,17 +24577,17 @@
       <c r="E102" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="F102" s="153">
+      <c r="F102" s="137">
         <v>2</v>
       </c>
-      <c r="G102" s="152">
+      <c r="G102" s="136">
         <v>1</v>
       </c>
       <c r="H102" s="9"/>
       <c r="I102" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J102" s="165">
+      <c r="J102" s="148">
         <v>1</v>
       </c>
       <c r="K102" s="7">
@@ -24737,17 +24713,17 @@
       <c r="E103" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="F103" s="153">
+      <c r="F103" s="137">
         <v>2</v>
       </c>
-      <c r="G103" s="152">
+      <c r="G103" s="136">
         <v>1</v>
       </c>
       <c r="H103" s="9"/>
       <c r="I103" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J103" s="165">
+      <c r="J103" s="148">
         <v>1</v>
       </c>
       <c r="K103" s="7">
@@ -24873,17 +24849,17 @@
       <c r="E104" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="F104" s="153">
+      <c r="F104" s="137">
         <v>2</v>
       </c>
-      <c r="G104" s="152">
+      <c r="G104" s="136">
         <v>1</v>
       </c>
       <c r="H104" s="10"/>
       <c r="I104" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J104" s="164" t="s">
+      <c r="J104" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K104" s="7">
@@ -25009,17 +24985,17 @@
       <c r="E105" t="s">
         <v>194</v>
       </c>
-      <c r="F105" s="153">
+      <c r="F105" s="137">
         <v>2</v>
       </c>
-      <c r="G105" s="152">
+      <c r="G105" s="136">
         <v>1</v>
       </c>
       <c r="H105" s="9"/>
       <c r="I105" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J105" s="165">
+      <c r="J105" s="148">
         <v>1</v>
       </c>
       <c r="K105" s="7">
@@ -25148,17 +25124,17 @@
       <c r="E106" t="s">
         <v>194</v>
       </c>
-      <c r="F106" s="153">
+      <c r="F106" s="137">
         <v>2</v>
       </c>
-      <c r="G106" s="152">
+      <c r="G106" s="136">
         <v>1</v>
       </c>
       <c r="H106" s="9"/>
       <c r="I106" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J106" s="165">
+      <c r="J106" s="148">
         <v>1</v>
       </c>
       <c r="K106" s="7">
@@ -25287,17 +25263,17 @@
       <c r="E107" t="s">
         <v>194</v>
       </c>
-      <c r="F107" s="153">
+      <c r="F107" s="137">
         <v>2</v>
       </c>
-      <c r="G107" s="152">
+      <c r="G107" s="136">
         <v>1</v>
       </c>
       <c r="H107" s="9"/>
       <c r="I107" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J107" s="165">
+      <c r="J107" s="148">
         <v>1</v>
       </c>
       <c r="K107" s="7">
@@ -25426,17 +25402,17 @@
       <c r="E108" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="F108" s="153">
+      <c r="F108" s="137">
         <v>2</v>
       </c>
-      <c r="G108" s="152">
+      <c r="G108" s="136">
         <v>1</v>
       </c>
       <c r="H108" s="9"/>
       <c r="I108" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J108" s="165">
+      <c r="J108" s="148">
         <v>1</v>
       </c>
       <c r="K108" s="7">
@@ -25565,17 +25541,17 @@
       <c r="E109" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="F109" s="153">
+      <c r="F109" s="137">
         <v>2</v>
       </c>
-      <c r="G109" s="152">
+      <c r="G109" s="136">
         <v>1</v>
       </c>
       <c r="H109" s="9"/>
       <c r="I109" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J109" s="165">
+      <c r="J109" s="148">
         <v>1</v>
       </c>
       <c r="K109" s="7">
@@ -25704,17 +25680,17 @@
       <c r="E110" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F110" s="153">
+      <c r="F110" s="137">
         <v>2</v>
       </c>
-      <c r="G110" s="152">
+      <c r="G110" s="136">
         <v>1</v>
       </c>
       <c r="H110" s="9"/>
       <c r="I110" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J110" s="165">
+      <c r="J110" s="148">
         <v>1</v>
       </c>
       <c r="K110" s="7">
@@ -25843,17 +25819,17 @@
       <c r="E111" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F111" s="153">
+      <c r="F111" s="137">
         <v>2</v>
       </c>
-      <c r="G111" s="152">
+      <c r="G111" s="136">
         <v>1</v>
       </c>
       <c r="H111" s="9"/>
       <c r="I111" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J111" s="165">
+      <c r="J111" s="148">
         <v>1</v>
       </c>
       <c r="K111" s="7">
@@ -25982,17 +25958,17 @@
       <c r="E112" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F112" s="153">
+      <c r="F112" s="137">
         <v>2</v>
       </c>
-      <c r="G112" s="152">
+      <c r="G112" s="136">
         <v>1</v>
       </c>
       <c r="H112" s="9"/>
       <c r="I112" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J112" s="165">
+      <c r="J112" s="148">
         <v>1</v>
       </c>
       <c r="K112" s="7">
@@ -26121,17 +26097,17 @@
       <c r="E113" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F113" s="153">
+      <c r="F113" s="137">
         <v>2</v>
       </c>
-      <c r="G113" s="152">
+      <c r="G113" s="136">
         <v>1</v>
       </c>
       <c r="H113" s="9"/>
       <c r="I113" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J113" s="165">
+      <c r="J113" s="148">
         <v>1</v>
       </c>
       <c r="K113" s="7">
@@ -26260,17 +26236,17 @@
       <c r="E114" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F114" s="153">
+      <c r="F114" s="137">
         <v>2</v>
       </c>
-      <c r="G114" s="152">
+      <c r="G114" s="136">
         <v>1</v>
       </c>
       <c r="H114" s="9"/>
       <c r="I114" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J114" s="165">
+      <c r="J114" s="148">
         <v>1</v>
       </c>
       <c r="K114" s="7">
@@ -26399,17 +26375,17 @@
       <c r="E115" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F115" s="153">
+      <c r="F115" s="137">
         <v>2</v>
       </c>
-      <c r="G115" s="152">
+      <c r="G115" s="136">
         <v>1</v>
       </c>
       <c r="H115" s="9"/>
       <c r="I115" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J115" s="165">
+      <c r="J115" s="148">
         <v>1</v>
       </c>
       <c r="K115" s="7">
@@ -26538,17 +26514,17 @@
       <c r="E116" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F116" s="153">
+      <c r="F116" s="137">
         <v>2</v>
       </c>
-      <c r="G116" s="152">
+      <c r="G116" s="136">
         <v>1</v>
       </c>
       <c r="H116" s="9"/>
       <c r="I116" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J116" s="165">
+      <c r="J116" s="148">
         <v>1</v>
       </c>
       <c r="K116" s="7">
@@ -26677,17 +26653,17 @@
       <c r="E117" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F117" s="153">
+      <c r="F117" s="137">
         <v>2</v>
       </c>
-      <c r="G117" s="152">
+      <c r="G117" s="136">
         <v>1</v>
       </c>
       <c r="H117" s="9"/>
       <c r="I117" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J117" s="165">
+      <c r="J117" s="148">
         <v>1</v>
       </c>
       <c r="K117" s="7">
@@ -26816,17 +26792,17 @@
       <c r="E118" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F118" s="153">
+      <c r="F118" s="137">
         <v>2</v>
       </c>
-      <c r="G118" s="152">
+      <c r="G118" s="136">
         <v>1</v>
       </c>
       <c r="H118" s="9"/>
       <c r="I118" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J118" s="165">
+      <c r="J118" s="148">
         <v>1</v>
       </c>
       <c r="K118" s="7">
@@ -26955,17 +26931,17 @@
       <c r="E119" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F119" s="153">
+      <c r="F119" s="137">
         <v>2</v>
       </c>
-      <c r="G119" s="152">
+      <c r="G119" s="136">
         <v>1</v>
       </c>
       <c r="H119" s="9"/>
       <c r="I119" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J119" s="165">
+      <c r="J119" s="148">
         <v>1</v>
       </c>
       <c r="K119" s="7">
@@ -27094,17 +27070,17 @@
       <c r="E120" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="F120" s="153">
+      <c r="F120" s="137">
         <v>2</v>
       </c>
-      <c r="G120" s="152">
+      <c r="G120" s="136">
         <v>1</v>
       </c>
       <c r="H120" s="9"/>
       <c r="I120" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J120" s="165">
+      <c r="J120" s="148">
         <v>1</v>
       </c>
       <c r="K120" s="7">
@@ -27233,17 +27209,17 @@
       <c r="E121" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F121" s="153">
+      <c r="F121" s="137">
         <v>2</v>
       </c>
-      <c r="G121" s="152">
+      <c r="G121" s="136">
         <v>1</v>
       </c>
       <c r="H121" s="9"/>
       <c r="I121" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J121" s="165">
+      <c r="J121" s="148">
         <v>1</v>
       </c>
       <c r="K121" s="7">
@@ -27372,17 +27348,17 @@
       <c r="E122" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F122" s="153">
+      <c r="F122" s="137">
         <v>2</v>
       </c>
-      <c r="G122" s="152">
+      <c r="G122" s="136">
         <v>1</v>
       </c>
       <c r="H122" s="9"/>
       <c r="I122" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J122" s="165">
+      <c r="J122" s="148">
         <v>1</v>
       </c>
       <c r="K122" s="7">
@@ -27511,17 +27487,17 @@
       <c r="E123" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F123" s="153">
+      <c r="F123" s="137">
         <v>2</v>
       </c>
-      <c r="G123" s="152">
+      <c r="G123" s="136">
         <v>1</v>
       </c>
       <c r="H123" s="9"/>
       <c r="I123" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J123" s="165">
+      <c r="J123" s="148">
         <v>1</v>
       </c>
       <c r="K123" s="7">
@@ -27650,17 +27626,17 @@
       <c r="E124" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F124" s="153">
+      <c r="F124" s="137">
         <v>2</v>
       </c>
-      <c r="G124" s="152">
+      <c r="G124" s="136">
         <v>1</v>
       </c>
       <c r="H124" s="9"/>
       <c r="I124" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J124" s="165">
+      <c r="J124" s="148">
         <v>1</v>
       </c>
       <c r="K124" s="7">
@@ -27789,17 +27765,17 @@
       <c r="E125" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F125" s="153">
+      <c r="F125" s="137">
         <v>2</v>
       </c>
-      <c r="G125" s="152">
+      <c r="G125" s="136">
         <v>1</v>
       </c>
       <c r="H125" s="9"/>
       <c r="I125" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J125" s="165">
+      <c r="J125" s="148">
         <v>1</v>
       </c>
       <c r="K125" s="7">
@@ -27928,17 +27904,17 @@
       <c r="E126" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F126" s="153">
+      <c r="F126" s="137">
         <v>2</v>
       </c>
-      <c r="G126" s="152">
+      <c r="G126" s="136">
         <v>1</v>
       </c>
       <c r="H126" s="9"/>
       <c r="I126" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J126" s="165">
+      <c r="J126" s="148">
         <v>1</v>
       </c>
       <c r="K126" s="7">
@@ -28067,17 +28043,17 @@
       <c r="E127" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F127" s="153">
+      <c r="F127" s="137">
         <v>2</v>
       </c>
-      <c r="G127" s="152">
+      <c r="G127" s="136">
         <v>1</v>
       </c>
       <c r="H127" s="9"/>
       <c r="I127" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J127" s="165">
+      <c r="J127" s="148">
         <v>1</v>
       </c>
       <c r="K127" s="7">
@@ -28206,17 +28182,17 @@
       <c r="E128" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="F128" s="153">
+      <c r="F128" s="137">
         <v>2</v>
       </c>
-      <c r="G128" s="152">
+      <c r="G128" s="136">
         <v>1</v>
       </c>
       <c r="H128" s="9"/>
       <c r="I128" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="J128" s="165">
+      <c r="J128" s="148">
         <v>1</v>
       </c>
       <c r="K128" s="7">
@@ -28345,17 +28321,17 @@
       <c r="E129" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F129" s="154">
+      <c r="F129" s="138">
         <v>3</v>
       </c>
-      <c r="G129" s="153">
+      <c r="G129" s="137">
         <v>2</v>
       </c>
       <c r="H129" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I129" s="9"/>
-      <c r="J129" s="164" t="s">
+      <c r="J129" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K129" s="18">
@@ -28517,17 +28493,17 @@
       <c r="E130" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F130" s="154">
+      <c r="F130" s="138">
         <v>3</v>
       </c>
-      <c r="G130" s="152">
+      <c r="G130" s="136">
         <v>1</v>
       </c>
       <c r="H130" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I130" s="9"/>
-      <c r="J130" s="164" t="s">
+      <c r="J130" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K130" s="18">
@@ -28688,17 +28664,17 @@
       <c r="E131" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F131" s="153">
+      <c r="F131" s="137">
         <v>2</v>
       </c>
-      <c r="G131" s="153">
+      <c r="G131" s="137">
         <v>2</v>
       </c>
       <c r="H131" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I131" s="9"/>
-      <c r="J131" s="164" t="s">
+      <c r="J131" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K131" s="18">
@@ -28872,17 +28848,17 @@
       <c r="E132" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F132" s="152">
-        <v>1</v>
-      </c>
-      <c r="G132" s="153">
+      <c r="F132" s="136">
+        <v>1</v>
+      </c>
+      <c r="G132" s="137">
         <v>2</v>
       </c>
       <c r="H132" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I132" s="9"/>
-      <c r="J132" s="164" t="s">
+      <c r="J132" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K132" s="18">
@@ -29062,17 +29038,17 @@
       <c r="E133" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F133" s="153">
+      <c r="F133" s="137">
         <v>2</v>
       </c>
-      <c r="G133" s="153">
+      <c r="G133" s="137">
         <v>2</v>
       </c>
       <c r="H133" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I133" s="9"/>
-      <c r="J133" s="164" t="s">
+      <c r="J133" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K133" s="18">
@@ -29246,17 +29222,17 @@
       <c r="E134" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F134" s="153">
+      <c r="F134" s="137">
         <v>2</v>
       </c>
-      <c r="G134" s="153">
+      <c r="G134" s="137">
         <v>2</v>
       </c>
       <c r="H134" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I134" s="9"/>
-      <c r="J134" s="164" t="s">
+      <c r="J134" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K134" s="18">
@@ -29412,17 +29388,17 @@
       <c r="E135" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F135" s="154">
+      <c r="F135" s="138">
         <v>3</v>
       </c>
-      <c r="G135" s="153">
+      <c r="G135" s="137">
         <v>2</v>
       </c>
       <c r="H135" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I135" s="9"/>
-      <c r="J135" s="164" t="s">
+      <c r="J135" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K135" s="18">
@@ -29584,15 +29560,15 @@
       <c r="E136" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F136" s="152">
-        <v>1</v>
-      </c>
-      <c r="G136" s="153">
+      <c r="F136" s="136">
+        <v>1</v>
+      </c>
+      <c r="G136" s="137">
         <v>2</v>
       </c>
       <c r="H136" s="58"/>
       <c r="I136" s="9"/>
-      <c r="J136" s="152">
+      <c r="J136" s="136">
         <v>1</v>
       </c>
       <c r="K136" s="18">
@@ -29832,17 +29808,17 @@
       <c r="E137" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F137" s="154">
+      <c r="F137" s="138">
         <v>3</v>
       </c>
-      <c r="G137" s="152">
+      <c r="G137" s="136">
         <v>1</v>
       </c>
       <c r="H137" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I137" s="9"/>
-      <c r="J137" s="164" t="s">
+      <c r="J137" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K137" s="18">
@@ -30004,17 +29980,17 @@
       <c r="E138" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F138" s="153">
+      <c r="F138" s="137">
         <v>2</v>
       </c>
-      <c r="G138" s="153">
+      <c r="G138" s="137">
         <v>2</v>
       </c>
       <c r="H138" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I138" s="9"/>
-      <c r="J138" s="164" t="s">
+      <c r="J138" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K138" s="18">
@@ -30190,17 +30166,17 @@
       <c r="E139" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F139" s="154">
+      <c r="F139" s="138">
         <v>3</v>
       </c>
-      <c r="G139" s="153">
+      <c r="G139" s="137">
         <v>2</v>
       </c>
       <c r="H139" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I139" s="9"/>
-      <c r="J139" s="164" t="s">
+      <c r="J139" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K139" s="18">
@@ -30362,17 +30338,17 @@
       <c r="E140" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F140" s="154">
+      <c r="F140" s="138">
         <v>3</v>
       </c>
-      <c r="G140" s="153">
+      <c r="G140" s="137">
         <v>2</v>
       </c>
       <c r="H140" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I140" s="9"/>
-      <c r="J140" s="164" t="s">
+      <c r="J140" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K140" s="18">
@@ -30534,17 +30510,17 @@
       <c r="E141" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F141" s="152">
-        <v>1</v>
-      </c>
-      <c r="G141" s="152">
+      <c r="F141" s="136">
+        <v>1</v>
+      </c>
+      <c r="G141" s="136">
         <v>1</v>
       </c>
       <c r="H141" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I141" s="9"/>
-      <c r="J141" s="164" t="s">
+      <c r="J141" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K141" s="18">
@@ -30730,17 +30706,17 @@
       <c r="E142" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F142" s="152">
-        <v>1</v>
-      </c>
-      <c r="G142" s="153">
+      <c r="F142" s="136">
+        <v>1</v>
+      </c>
+      <c r="G142" s="137">
         <v>2</v>
       </c>
       <c r="H142" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I142" s="9"/>
-      <c r="J142" s="164" t="s">
+      <c r="J142" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K142" s="1">
@@ -30931,17 +30907,17 @@
       <c r="E143" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F143" s="152">
-        <v>1</v>
-      </c>
-      <c r="G143" s="153">
+      <c r="F143" s="136">
+        <v>1</v>
+      </c>
+      <c r="G143" s="137">
         <v>2</v>
       </c>
       <c r="H143" s="57" t="s">
         <v>164</v>
       </c>
       <c r="I143" s="9"/>
-      <c r="J143" s="152">
+      <c r="J143" s="136">
         <v>1</v>
       </c>
       <c r="K143" s="18">
@@ -31181,15 +31157,15 @@
       <c r="E144" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F144" s="154">
+      <c r="F144" s="138">
         <v>3</v>
       </c>
-      <c r="G144" s="153">
+      <c r="G144" s="137">
         <v>2</v>
       </c>
       <c r="H144" s="57"/>
       <c r="I144" s="9"/>
-      <c r="J144" s="164" t="s">
+      <c r="J144" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K144" s="18">
@@ -31351,15 +31327,15 @@
       <c r="E145" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F145" s="152">
-        <v>1</v>
-      </c>
-      <c r="G145" s="153">
+      <c r="F145" s="136">
+        <v>1</v>
+      </c>
+      <c r="G145" s="137">
         <v>2</v>
       </c>
       <c r="H145" s="58"/>
       <c r="I145" s="9"/>
-      <c r="J145" s="164" t="s">
+      <c r="J145" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K145" s="18">
@@ -31557,15 +31533,15 @@
       <c r="E146" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F146" s="152">
-        <v>1</v>
-      </c>
-      <c r="G146" s="152">
+      <c r="F146" s="136">
+        <v>1</v>
+      </c>
+      <c r="G146" s="136">
         <v>1</v>
       </c>
       <c r="H146" s="57"/>
       <c r="I146" s="9"/>
-      <c r="J146" s="164" t="s">
+      <c r="J146" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K146" s="18">
@@ -31761,15 +31737,15 @@
       <c r="E147" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F147" s="153">
+      <c r="F147" s="137">
         <v>2</v>
       </c>
-      <c r="G147" s="152">
+      <c r="G147" s="136">
         <v>1</v>
       </c>
       <c r="H147" s="57"/>
       <c r="I147" s="9"/>
-      <c r="J147" s="164" t="s">
+      <c r="J147" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K147" s="18">
@@ -31943,15 +31919,15 @@
       <c r="E148" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F148" s="153">
+      <c r="F148" s="137">
         <v>2</v>
       </c>
-      <c r="G148" s="152">
+      <c r="G148" s="136">
         <v>1</v>
       </c>
       <c r="H148" s="57"/>
       <c r="I148" s="9"/>
-      <c r="J148" s="164" t="s">
+      <c r="J148" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K148" s="18">
@@ -32131,15 +32107,15 @@
       <c r="E149" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F149" s="152">
-        <v>1</v>
-      </c>
-      <c r="G149" s="153">
+      <c r="F149" s="136">
+        <v>1</v>
+      </c>
+      <c r="G149" s="137">
         <v>2</v>
       </c>
       <c r="H149" s="57"/>
       <c r="I149" s="9"/>
-      <c r="J149" s="164" t="s">
+      <c r="J149" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K149" s="18">
@@ -32325,15 +32301,15 @@
       <c r="E150" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F150" s="152">
-        <v>1</v>
-      </c>
-      <c r="G150" s="153">
+      <c r="F150" s="136">
+        <v>1</v>
+      </c>
+      <c r="G150" s="137">
         <v>2</v>
       </c>
       <c r="H150" s="58"/>
       <c r="I150" s="9"/>
-      <c r="J150" s="164" t="s">
+      <c r="J150" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K150" s="18">
@@ -32509,11 +32485,11 @@
       </c>
       <c r="CF150" s="18"/>
     </row>
-    <row r="151" spans="1:84">
-      <c r="A151" s="137" t="s">
+    <row r="151" spans="1:84" hidden="1">
+      <c r="A151" s="164" t="s">
         <v>568</v>
       </c>
-      <c r="B151" s="138" t="s">
+      <c r="B151" s="165" t="s">
         <v>569</v>
       </c>
       <c r="C151" s="53" t="s">
@@ -32525,15 +32501,13 @@
       <c r="E151" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F151" s="152">
-        <v>1</v>
-      </c>
-      <c r="G151" s="153">
+      <c r="F151" s="136"/>
+      <c r="G151" s="137">
         <v>2</v>
       </c>
       <c r="H151" s="58"/>
       <c r="I151" s="9"/>
-      <c r="J151" s="152">
+      <c r="J151" s="136">
         <v>1</v>
       </c>
       <c r="K151" s="18">
@@ -32758,10 +32732,10 @@
       <c r="CF151" s="18"/>
     </row>
     <row r="152" spans="1:84" hidden="1">
-      <c r="A152" s="53" t="s">
+      <c r="A152" s="164" t="s">
         <v>570</v>
       </c>
-      <c r="B152" s="54" t="s">
+      <c r="B152" s="165" t="s">
         <v>571</v>
       </c>
       <c r="C152" s="53" t="s">
@@ -32773,15 +32747,15 @@
       <c r="E152" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F152" s="152">
-        <v>1</v>
-      </c>
-      <c r="G152" s="153">
+      <c r="F152" s="136">
+        <v>1</v>
+      </c>
+      <c r="G152" s="137">
         <v>2</v>
       </c>
       <c r="H152" s="57"/>
       <c r="I152" s="9"/>
-      <c r="J152" s="164" t="s">
+      <c r="J152" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K152" s="18">
@@ -32964,10 +32938,10 @@
       <c r="CF152" s="18"/>
     </row>
     <row r="153" spans="1:84">
-      <c r="A153" s="53" t="s">
+      <c r="A153" s="164" t="s">
         <v>572</v>
       </c>
-      <c r="B153" s="54" t="s">
+      <c r="B153" s="165" t="s">
         <v>573</v>
       </c>
       <c r="C153" s="53" t="s">
@@ -32979,15 +32953,15 @@
       <c r="E153" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F153" s="152">
-        <v>1</v>
-      </c>
-      <c r="G153" s="153">
+      <c r="F153" s="136">
+        <v>1</v>
+      </c>
+      <c r="G153" s="137">
         <v>2</v>
       </c>
       <c r="H153" s="58"/>
       <c r="I153" s="9"/>
-      <c r="J153" s="152">
+      <c r="J153" s="136">
         <v>1</v>
       </c>
       <c r="K153" s="18">
@@ -33206,10 +33180,10 @@
       <c r="CF153" s="18"/>
     </row>
     <row r="154" spans="1:84" hidden="1">
-      <c r="A154" s="53" t="s">
+      <c r="A154" s="164" t="s">
         <v>574</v>
       </c>
-      <c r="B154" s="54" t="s">
+      <c r="B154" s="165" t="s">
         <v>575</v>
       </c>
       <c r="C154" s="53" t="s">
@@ -33221,15 +33195,15 @@
       <c r="E154" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F154" s="154">
+      <c r="F154" s="138">
         <v>3</v>
       </c>
-      <c r="G154" s="153">
+      <c r="G154" s="137">
         <v>2</v>
       </c>
       <c r="H154" s="57"/>
       <c r="I154" s="9"/>
-      <c r="J154" s="164" t="s">
+      <c r="J154" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K154" s="18">
@@ -33376,10 +33350,10 @@
       <c r="CF154" s="18"/>
     </row>
     <row r="155" spans="1:84" hidden="1">
-      <c r="A155" s="53" t="s">
+      <c r="A155" s="164" t="s">
         <v>576</v>
       </c>
-      <c r="B155" s="54" t="s">
+      <c r="B155" s="165" t="s">
         <v>577</v>
       </c>
       <c r="C155" s="53" t="s">
@@ -33391,15 +33365,15 @@
       <c r="E155" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F155" s="152">
-        <v>1</v>
-      </c>
-      <c r="G155" s="153">
+      <c r="F155" s="136">
+        <v>1</v>
+      </c>
+      <c r="G155" s="137">
         <v>2</v>
       </c>
       <c r="H155" s="57"/>
       <c r="I155" s="9"/>
-      <c r="J155" s="164" t="s">
+      <c r="J155" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K155" s="18">
@@ -33576,10 +33550,10 @@
       <c r="CF155" s="18"/>
     </row>
     <row r="156" spans="1:84">
-      <c r="A156" s="135" t="s">
+      <c r="A156" s="164" t="s">
         <v>578</v>
       </c>
-      <c r="B156" s="136" t="s">
+      <c r="B156" s="165" t="s">
         <v>579</v>
       </c>
       <c r="C156" s="53" t="s">
@@ -33591,15 +33565,15 @@
       <c r="E156" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F156" s="152">
-        <v>1</v>
-      </c>
-      <c r="G156" s="152">
+      <c r="F156" s="136">
+        <v>1</v>
+      </c>
+      <c r="G156" s="136">
         <v>1</v>
       </c>
       <c r="H156" s="58"/>
       <c r="I156" s="9"/>
-      <c r="J156" s="152">
+      <c r="J156" s="136">
         <v>1</v>
       </c>
       <c r="K156" s="18">
@@ -33817,11 +33791,11 @@
       </c>
       <c r="CF156" s="18"/>
     </row>
-    <row r="157" spans="1:84">
-      <c r="A157" s="54" t="s">
+    <row r="157" spans="1:84" hidden="1">
+      <c r="A157" s="165" t="s">
         <v>580</v>
       </c>
-      <c r="B157" s="54" t="s">
+      <c r="B157" s="165" t="s">
         <v>581</v>
       </c>
       <c r="C157" s="53" t="s">
@@ -33831,15 +33805,13 @@
         <v>157</v>
       </c>
       <c r="E157" s="56"/>
-      <c r="F157" s="152">
-        <v>1</v>
-      </c>
-      <c r="G157" s="153">
+      <c r="F157" s="136"/>
+      <c r="G157" s="137">
         <v>2</v>
       </c>
       <c r="H157" s="58"/>
       <c r="I157" s="9"/>
-      <c r="J157" s="152">
+      <c r="J157" s="136">
         <v>1</v>
       </c>
       <c r="K157" s="18">
@@ -33983,11 +33955,11 @@
       <c r="CE157" s="61"/>
       <c r="CF157" s="18"/>
     </row>
-    <row r="158" spans="1:84">
-      <c r="A158" s="138" t="s">
+    <row r="158" spans="1:84" hidden="1">
+      <c r="A158" s="165" t="s">
         <v>583</v>
       </c>
-      <c r="B158" s="138" t="s">
+      <c r="B158" s="165" t="s">
         <v>423</v>
       </c>
       <c r="C158" s="53" t="s">
@@ -33997,15 +33969,13 @@
         <v>157</v>
       </c>
       <c r="E158" s="56"/>
-      <c r="F158" s="152">
-        <v>1</v>
-      </c>
-      <c r="G158" s="153">
+      <c r="F158" s="136"/>
+      <c r="G158" s="137">
         <v>2</v>
       </c>
       <c r="H158" s="58"/>
       <c r="I158" s="9"/>
-      <c r="J158" s="152">
+      <c r="J158" s="136">
         <v>1</v>
       </c>
       <c r="K158" s="18">
@@ -34110,10 +34080,10 @@
       <c r="CF158" s="18"/>
     </row>
     <row r="159" spans="1:84">
-      <c r="A159" s="138" t="s">
+      <c r="A159" s="165" t="s">
         <v>584</v>
       </c>
-      <c r="B159" s="138" t="s">
+      <c r="B159" s="165" t="s">
         <v>585</v>
       </c>
       <c r="C159" s="53" t="s">
@@ -34123,15 +34093,15 @@
         <v>169</v>
       </c>
       <c r="E159" s="56"/>
-      <c r="F159" s="152">
-        <v>1</v>
-      </c>
-      <c r="G159" s="153">
+      <c r="F159" s="136">
+        <v>1</v>
+      </c>
+      <c r="G159" s="137">
         <v>2</v>
       </c>
       <c r="H159" s="58"/>
       <c r="I159" s="9"/>
-      <c r="J159" s="152">
+      <c r="J159" s="136">
         <v>1</v>
       </c>
       <c r="K159" s="18">
@@ -34236,10 +34206,10 @@
       <c r="CF159" s="18"/>
     </row>
     <row r="160" spans="1:84">
-      <c r="A160" s="54" t="s">
+      <c r="A160" s="165" t="s">
         <v>586</v>
       </c>
-      <c r="B160" s="54" t="s">
+      <c r="B160" s="165" t="s">
         <v>587</v>
       </c>
       <c r="C160" s="53" t="s">
@@ -34249,15 +34219,15 @@
         <v>169</v>
       </c>
       <c r="E160" s="56"/>
-      <c r="F160" s="152">
-        <v>1</v>
-      </c>
-      <c r="G160" s="153">
+      <c r="F160" s="136">
+        <v>1</v>
+      </c>
+      <c r="G160" s="137">
         <v>2</v>
       </c>
       <c r="H160" s="58"/>
       <c r="I160" s="9"/>
-      <c r="J160" s="152">
+      <c r="J160" s="136">
         <v>1</v>
       </c>
       <c r="K160" s="18">
@@ -34362,10 +34332,10 @@
       <c r="CF160" s="18"/>
     </row>
     <row r="161" spans="1:84">
-      <c r="A161" s="138" t="s">
+      <c r="A161" s="165" t="s">
         <v>588</v>
       </c>
-      <c r="B161" s="138" t="s">
+      <c r="B161" s="165" t="s">
         <v>589</v>
       </c>
       <c r="C161" s="53" t="s">
@@ -34375,15 +34345,15 @@
         <v>295</v>
       </c>
       <c r="E161" s="56"/>
-      <c r="F161" s="152">
-        <v>1</v>
-      </c>
-      <c r="G161" s="153">
+      <c r="F161" s="136">
+        <v>1</v>
+      </c>
+      <c r="G161" s="137">
         <v>2</v>
       </c>
       <c r="H161" s="58"/>
       <c r="I161" s="9"/>
-      <c r="J161" s="152">
+      <c r="J161" s="136">
         <v>1</v>
       </c>
       <c r="K161" s="18">
@@ -34488,10 +34458,10 @@
       <c r="CF161" s="18"/>
     </row>
     <row r="162" spans="1:84">
-      <c r="A162" s="138" t="s">
+      <c r="A162" s="165" t="s">
         <v>590</v>
       </c>
-      <c r="B162" s="138" t="s">
+      <c r="B162" s="165" t="s">
         <v>591</v>
       </c>
       <c r="C162" s="53" t="s">
@@ -34501,15 +34471,15 @@
         <v>295</v>
       </c>
       <c r="E162" s="56"/>
-      <c r="F162" s="152">
-        <v>1</v>
-      </c>
-      <c r="G162" s="153">
+      <c r="F162" s="136">
+        <v>1</v>
+      </c>
+      <c r="G162" s="137">
         <v>2</v>
       </c>
       <c r="H162" s="58"/>
       <c r="I162" s="9"/>
-      <c r="J162" s="152">
+      <c r="J162" s="136">
         <v>1</v>
       </c>
       <c r="K162" s="18">
@@ -34613,11 +34583,11 @@
       <c r="CE162" s="61"/>
       <c r="CF162" s="18"/>
     </row>
-    <row r="163" spans="1:84">
-      <c r="A163" s="138" t="s">
+    <row r="163" spans="1:84" hidden="1">
+      <c r="A163" s="165" t="s">
         <v>592</v>
       </c>
-      <c r="B163" s="138" t="s">
+      <c r="B163" s="165" t="s">
         <v>593</v>
       </c>
       <c r="C163" s="53" t="s">
@@ -34627,15 +34597,13 @@
         <v>295</v>
       </c>
       <c r="E163" s="56"/>
-      <c r="F163" s="152">
-        <v>1</v>
-      </c>
-      <c r="G163" s="153">
+      <c r="F163" s="136"/>
+      <c r="G163" s="137">
         <v>2</v>
       </c>
       <c r="H163" s="58"/>
       <c r="I163" s="9"/>
-      <c r="J163" s="152">
+      <c r="J163" s="136">
         <v>1</v>
       </c>
       <c r="K163" s="18">
@@ -34739,11 +34707,11 @@
       <c r="CE163" s="61"/>
       <c r="CF163" s="18"/>
     </row>
-    <row r="164" spans="1:84">
-      <c r="A164" s="138" t="s">
+    <row r="164" spans="1:84" hidden="1">
+      <c r="A164" s="165" t="s">
         <v>594</v>
       </c>
-      <c r="B164" s="138" t="s">
+      <c r="B164" s="165" t="s">
         <v>595</v>
       </c>
       <c r="C164" s="53" t="s">
@@ -34753,15 +34721,13 @@
         <v>295</v>
       </c>
       <c r="E164" s="56"/>
-      <c r="F164" s="152">
-        <v>1</v>
-      </c>
-      <c r="G164" s="153">
+      <c r="F164" s="136"/>
+      <c r="G164" s="137">
         <v>2</v>
       </c>
       <c r="H164" s="58"/>
       <c r="I164" s="9"/>
-      <c r="J164" s="152">
+      <c r="J164" s="136">
         <v>1</v>
       </c>
       <c r="K164" s="18">
@@ -34866,10 +34832,10 @@
       <c r="CF164" s="18"/>
     </row>
     <row r="165" spans="1:84" hidden="1">
-      <c r="A165" s="53" t="s">
+      <c r="A165" s="164" t="s">
         <v>596</v>
       </c>
-      <c r="B165" s="54" t="s">
+      <c r="B165" s="165" t="s">
         <v>597</v>
       </c>
       <c r="C165" s="53" t="s">
@@ -34881,15 +34847,15 @@
       <c r="E165" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F165" s="153">
+      <c r="F165" s="137">
         <v>2</v>
       </c>
-      <c r="G165" s="153">
+      <c r="G165" s="137">
         <v>2</v>
       </c>
       <c r="H165" s="58"/>
       <c r="I165" s="9"/>
-      <c r="J165" s="152">
+      <c r="J165" s="136">
         <v>1</v>
       </c>
       <c r="K165" s="18">
@@ -35106,15 +35072,15 @@
       <c r="E166" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F166" s="153">
+      <c r="F166" s="137">
         <v>2</v>
       </c>
-      <c r="G166" s="153">
+      <c r="G166" s="137">
         <v>2</v>
       </c>
       <c r="H166" s="57"/>
       <c r="I166" s="9"/>
-      <c r="J166" s="164" t="s">
+      <c r="J166" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K166" s="18">
@@ -35282,15 +35248,15 @@
       <c r="E167" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F167" s="152">
-        <v>1</v>
-      </c>
-      <c r="G167" s="152">
+      <c r="F167" s="136">
+        <v>1</v>
+      </c>
+      <c r="G167" s="136">
         <v>1</v>
       </c>
       <c r="H167" s="58"/>
       <c r="I167" s="9"/>
-      <c r="J167" s="152">
+      <c r="J167" s="136">
         <v>1</v>
       </c>
       <c r="K167" s="18">
@@ -35524,15 +35490,15 @@
       <c r="E168" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F168" s="153">
+      <c r="F168" s="137">
         <v>2</v>
       </c>
-      <c r="G168" s="152">
+      <c r="G168" s="136">
         <v>1</v>
       </c>
       <c r="H168" s="57"/>
       <c r="I168" s="9"/>
-      <c r="J168" s="164" t="s">
+      <c r="J168" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K168" s="18">
@@ -35702,15 +35668,15 @@
       <c r="E169" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F169" s="152">
-        <v>1</v>
-      </c>
-      <c r="G169" s="152">
+      <c r="F169" s="136">
+        <v>1</v>
+      </c>
+      <c r="G169" s="136">
         <v>1</v>
       </c>
       <c r="H169" s="57"/>
       <c r="I169" s="9"/>
-      <c r="J169" s="164" t="s">
+      <c r="J169" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K169" s="18">
@@ -35888,15 +35854,15 @@
       <c r="E170" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F170" s="152">
-        <v>1</v>
-      </c>
-      <c r="G170" s="152">
+      <c r="F170" s="136">
+        <v>1</v>
+      </c>
+      <c r="G170" s="136">
         <v>1</v>
       </c>
       <c r="H170" s="57"/>
       <c r="I170" s="9"/>
-      <c r="J170" s="164" t="s">
+      <c r="J170" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K170" s="18">
@@ -36082,15 +36048,15 @@
       <c r="E171" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F171" s="153">
+      <c r="F171" s="137">
         <v>2</v>
       </c>
-      <c r="G171" s="153">
+      <c r="G171" s="137">
         <v>2</v>
       </c>
       <c r="H171" s="57"/>
       <c r="I171" s="9"/>
-      <c r="J171" s="164" t="s">
+      <c r="J171" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K171" s="18">
@@ -36264,15 +36230,15 @@
       <c r="E172" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F172" s="152">
-        <v>1</v>
-      </c>
-      <c r="G172" s="152">
+      <c r="F172" s="136">
+        <v>1</v>
+      </c>
+      <c r="G172" s="136">
         <v>1</v>
       </c>
       <c r="H172" s="57"/>
       <c r="I172" s="9"/>
-      <c r="J172" s="164" t="s">
+      <c r="J172" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K172" s="18">
@@ -36464,15 +36430,15 @@
       <c r="E173" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F173" s="154">
+      <c r="F173" s="138">
         <v>3</v>
       </c>
-      <c r="G173" s="152">
+      <c r="G173" s="136">
         <v>1</v>
       </c>
       <c r="H173" s="57"/>
       <c r="I173" s="9"/>
-      <c r="J173" s="164" t="s">
+      <c r="J173" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K173" s="18">
@@ -36634,15 +36600,15 @@
       <c r="E174" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F174" s="152">
-        <v>1</v>
-      </c>
-      <c r="G174" s="153">
+      <c r="F174" s="136">
+        <v>1</v>
+      </c>
+      <c r="G174" s="137">
         <v>2</v>
       </c>
       <c r="H174" s="57"/>
       <c r="I174" s="9"/>
-      <c r="J174" s="164" t="s">
+      <c r="J174" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K174" s="18">
@@ -36840,15 +36806,15 @@
       <c r="E175" s="56" t="s">
         <v>152</v>
       </c>
-      <c r="F175" s="152">
-        <v>1</v>
-      </c>
-      <c r="G175" s="152">
+      <c r="F175" s="136">
+        <v>1</v>
+      </c>
+      <c r="G175" s="136">
         <v>1</v>
       </c>
       <c r="H175" s="57"/>
       <c r="I175" s="9"/>
-      <c r="J175" s="164" t="s">
+      <c r="J175" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K175" s="18">
@@ -37046,15 +37012,15 @@
       <c r="E176" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F176" s="153">
+      <c r="F176" s="137">
         <v>2</v>
       </c>
-      <c r="G176" s="152">
+      <c r="G176" s="136">
         <v>1</v>
       </c>
       <c r="H176" s="57"/>
       <c r="I176" s="9"/>
-      <c r="J176" s="164" t="s">
+      <c r="J176" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K176" s="18">
@@ -37234,15 +37200,15 @@
       <c r="E177" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F177" s="152">
-        <v>1</v>
-      </c>
-      <c r="G177" s="153">
+      <c r="F177" s="136">
+        <v>1</v>
+      </c>
+      <c r="G177" s="137">
         <v>2</v>
       </c>
       <c r="H177" s="57"/>
       <c r="I177" s="9"/>
-      <c r="J177" s="164" t="s">
+      <c r="J177" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K177" s="18">
@@ -37440,17 +37406,17 @@
       <c r="E178" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F178" s="154">
+      <c r="F178" s="138">
         <v>3</v>
       </c>
-      <c r="G178" s="153">
+      <c r="G178" s="137">
         <v>2</v>
       </c>
       <c r="H178" s="57"/>
       <c r="I178" s="57" t="s">
         <v>624</v>
       </c>
-      <c r="J178" s="164" t="s">
+      <c r="J178" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K178" s="18">
@@ -37612,15 +37578,15 @@
       <c r="E179" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F179" s="154">
+      <c r="F179" s="138">
         <v>3</v>
       </c>
-      <c r="G179" s="153">
+      <c r="G179" s="137">
         <v>2</v>
       </c>
       <c r="H179" s="57"/>
       <c r="I179" s="57"/>
-      <c r="J179" s="164" t="s">
+      <c r="J179" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K179" s="18">
@@ -37782,15 +37748,15 @@
       <c r="E180" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F180" s="154">
+      <c r="F180" s="138">
         <v>3</v>
       </c>
-      <c r="G180" s="153">
+      <c r="G180" s="137">
         <v>2</v>
       </c>
       <c r="H180" s="57"/>
       <c r="I180" s="57"/>
-      <c r="J180" s="164" t="s">
+      <c r="J180" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K180" s="18">
@@ -37952,15 +37918,15 @@
       <c r="E181" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F181" s="154">
+      <c r="F181" s="138">
         <v>3</v>
       </c>
-      <c r="G181" s="153">
+      <c r="G181" s="137">
         <v>2</v>
       </c>
       <c r="H181" s="57"/>
       <c r="I181" s="57"/>
-      <c r="J181" s="164" t="s">
+      <c r="J181" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K181" s="18">
@@ -38122,15 +38088,15 @@
       <c r="E182" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F182" s="154">
+      <c r="F182" s="138">
         <v>3</v>
       </c>
-      <c r="G182" s="153">
+      <c r="G182" s="137">
         <v>2</v>
       </c>
       <c r="H182" s="57"/>
       <c r="I182" s="57"/>
-      <c r="J182" s="164" t="s">
+      <c r="J182" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K182" s="18">
@@ -38292,15 +38258,15 @@
       <c r="E183" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F183" s="154">
+      <c r="F183" s="138">
         <v>3</v>
       </c>
-      <c r="G183" s="153">
+      <c r="G183" s="137">
         <v>2</v>
       </c>
       <c r="H183" s="57"/>
       <c r="I183" s="57"/>
-      <c r="J183" s="164" t="s">
+      <c r="J183" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K183" s="18">
@@ -38462,15 +38428,15 @@
       <c r="E184" s="54" t="s">
         <v>152</v>
       </c>
-      <c r="F184" s="154">
+      <c r="F184" s="138">
         <v>3</v>
       </c>
-      <c r="G184" s="153">
+      <c r="G184" s="137">
         <v>2</v>
       </c>
       <c r="H184" s="57"/>
       <c r="I184" s="57"/>
-      <c r="J184" s="164" t="s">
+      <c r="J184" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K184" s="18">
@@ -38632,17 +38598,17 @@
       <c r="E185" t="s">
         <v>640</v>
       </c>
-      <c r="F185" s="153">
+      <c r="F185" s="137">
         <v>2</v>
       </c>
-      <c r="G185" s="153">
+      <c r="G185" s="137">
         <v>2</v>
       </c>
       <c r="H185" s="10"/>
       <c r="I185" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J185" s="164" t="s">
+      <c r="J185" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K185" s="18">
@@ -38799,15 +38765,15 @@
       <c r="E186" t="s">
         <v>644</v>
       </c>
-      <c r="F186" s="153">
+      <c r="F186" s="137">
         <v>2</v>
       </c>
-      <c r="G186" s="153">
+      <c r="G186" s="137">
         <v>2</v>
       </c>
       <c r="H186" s="59"/>
       <c r="I186" s="60"/>
-      <c r="J186" s="164" t="s">
+      <c r="J186" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K186" s="18">
@@ -38964,15 +38930,15 @@
       <c r="E187" t="s">
         <v>647</v>
       </c>
-      <c r="F187" s="153">
+      <c r="F187" s="137">
         <v>2</v>
       </c>
-      <c r="G187" s="153">
+      <c r="G187" s="137">
         <v>2</v>
       </c>
       <c r="H187" s="59"/>
       <c r="I187" s="60"/>
-      <c r="J187" s="164" t="s">
+      <c r="J187" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K187" s="18">
@@ -39113,7 +39079,7 @@
       <c r="CD187" s="80"/>
       <c r="CE187" s="61"/>
     </row>
-    <row r="188" spans="1:87">
+    <row r="188" spans="1:87" hidden="1">
       <c r="A188" s="53" t="s">
         <v>648</v>
       </c>
@@ -39129,9 +39095,7 @@
       <c r="E188" t="s">
         <v>651</v>
       </c>
-      <c r="F188" s="152">
-        <v>1</v>
-      </c>
+      <c r="F188" s="136"/>
       <c r="G188" s="10">
         <v>2</v>
       </c>
@@ -39141,7 +39105,7 @@
       <c r="I188" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J188" s="152">
+      <c r="J188" s="136">
         <v>1</v>
       </c>
       <c r="K188" s="18">
@@ -39356,7 +39320,7 @@
       <c r="E189" t="s">
         <v>654</v>
       </c>
-      <c r="F189" s="152">
+      <c r="F189" s="136">
         <v>1</v>
       </c>
       <c r="G189" s="10">
@@ -39545,17 +39509,17 @@
       <c r="E190" t="s">
         <v>658</v>
       </c>
-      <c r="F190" s="153">
+      <c r="F190" s="137">
         <v>2</v>
       </c>
-      <c r="G190" s="153">
+      <c r="G190" s="137">
         <v>2</v>
       </c>
       <c r="H190" s="11"/>
       <c r="I190" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J190" s="164" t="s">
+      <c r="J190" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K190" s="18">
@@ -39711,7 +39675,7 @@
       <c r="CE190" s="61"/>
       <c r="CF190" s="33"/>
     </row>
-    <row r="191" spans="1:87">
+    <row r="191" spans="1:87" hidden="1">
       <c r="A191" s="53" t="s">
         <v>659</v>
       </c>
@@ -39727,9 +39691,7 @@
       <c r="E191" t="s">
         <v>660</v>
       </c>
-      <c r="F191" s="152">
-        <v>1</v>
-      </c>
+      <c r="F191" s="136"/>
       <c r="G191" s="10">
         <v>2</v>
       </c>
@@ -39739,7 +39701,7 @@
       <c r="I191" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J191" s="152">
+      <c r="J191" s="136">
         <v>1</v>
       </c>
       <c r="K191" s="18">
@@ -39949,17 +39911,17 @@
       <c r="E192" t="s">
         <v>663</v>
       </c>
-      <c r="F192" s="152">
-        <v>1</v>
-      </c>
-      <c r="G192" s="153">
+      <c r="F192" s="136">
+        <v>1</v>
+      </c>
+      <c r="G192" s="137">
         <v>2</v>
       </c>
       <c r="H192" s="9"/>
       <c r="I192" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J192" s="154">
+      <c r="J192" s="138">
         <v>3</v>
       </c>
       <c r="K192" s="18">
@@ -40178,17 +40140,17 @@
       <c r="E193" t="s">
         <v>666</v>
       </c>
-      <c r="F193" s="153">
+      <c r="F193" s="137">
         <v>2</v>
       </c>
-      <c r="G193" s="153">
+      <c r="G193" s="137">
         <v>2</v>
       </c>
       <c r="H193" s="9"/>
       <c r="I193" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="J193" s="153">
+      <c r="J193" s="137">
         <v>2</v>
       </c>
       <c r="K193" s="18">
@@ -40407,17 +40369,17 @@
       <c r="E194" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="F194" s="155">
-        <v>1</v>
-      </c>
-      <c r="G194" s="156">
+      <c r="F194" s="139">
+        <v>1</v>
+      </c>
+      <c r="G194" s="140">
         <v>2</v>
       </c>
       <c r="H194" s="86"/>
       <c r="I194" s="91" t="s">
         <v>149</v>
       </c>
-      <c r="J194" s="155">
+      <c r="J194" s="139">
         <v>1</v>
       </c>
       <c r="K194" s="18">
@@ -40614,17 +40576,17 @@
       <c r="E195" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="F195" s="155">
-        <v>1</v>
-      </c>
-      <c r="G195" s="156">
+      <c r="F195" s="139">
+        <v>1</v>
+      </c>
+      <c r="G195" s="140">
         <v>2</v>
       </c>
       <c r="H195" s="86"/>
       <c r="I195" s="91" t="s">
         <v>149</v>
       </c>
-      <c r="J195" s="155">
+      <c r="J195" s="139">
         <v>1</v>
       </c>
       <c r="K195" s="18">
@@ -40833,17 +40795,17 @@
       <c r="E196" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="F196" s="155">
-        <v>1</v>
-      </c>
-      <c r="G196" s="156">
+      <c r="F196" s="139">
+        <v>1</v>
+      </c>
+      <c r="G196" s="140">
         <v>2</v>
       </c>
       <c r="H196" s="86"/>
       <c r="I196" s="91" t="s">
         <v>149</v>
       </c>
-      <c r="J196" s="155">
+      <c r="J196" s="139">
         <v>1</v>
       </c>
       <c r="K196" s="18">
@@ -41052,17 +41014,17 @@
       <c r="E197" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="F197" s="156">
+      <c r="F197" s="140">
         <v>2</v>
       </c>
-      <c r="G197" s="156">
+      <c r="G197" s="140">
         <v>2</v>
       </c>
       <c r="H197" s="87"/>
       <c r="I197" s="91" t="s">
         <v>149</v>
       </c>
-      <c r="J197" s="164" t="s">
+      <c r="J197" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K197" s="18">
@@ -41220,15 +41182,15 @@
       <c r="E198" t="s">
         <v>687</v>
       </c>
-      <c r="F198" s="153">
+      <c r="F198" s="137">
         <v>2</v>
       </c>
-      <c r="G198" s="153">
+      <c r="G198" s="137">
         <v>2</v>
       </c>
       <c r="H198" s="9"/>
       <c r="I198" s="92"/>
-      <c r="J198" s="152">
+      <c r="J198" s="136">
         <v>1</v>
       </c>
       <c r="K198" s="18">
@@ -41446,15 +41408,15 @@
       <c r="E199" t="s">
         <v>690</v>
       </c>
-      <c r="F199" s="153">
+      <c r="F199" s="137">
         <v>2</v>
       </c>
-      <c r="G199" s="153">
+      <c r="G199" s="137">
         <v>2</v>
       </c>
       <c r="H199" s="9"/>
       <c r="I199" s="92"/>
-      <c r="J199" s="152">
+      <c r="J199" s="136">
         <v>1</v>
       </c>
       <c r="K199" s="18">
@@ -41672,15 +41634,15 @@
       <c r="E200" t="s">
         <v>687</v>
       </c>
-      <c r="F200" s="153">
+      <c r="F200" s="137">
         <v>2</v>
       </c>
-      <c r="G200" s="153">
+      <c r="G200" s="137">
         <v>2</v>
       </c>
       <c r="H200" s="9"/>
       <c r="I200" s="92"/>
-      <c r="J200" s="152">
+      <c r="J200" s="136">
         <v>1</v>
       </c>
       <c r="K200" s="18">
@@ -41856,15 +41818,15 @@
       <c r="E201" t="s">
         <v>697</v>
       </c>
-      <c r="F201" s="153">
+      <c r="F201" s="137">
         <v>2</v>
       </c>
-      <c r="G201" s="153">
+      <c r="G201" s="137">
         <v>2</v>
       </c>
       <c r="H201" s="59"/>
       <c r="I201" s="60"/>
-      <c r="J201" s="164" t="s">
+      <c r="J201" s="147" t="s">
         <v>150</v>
       </c>
       <c r="K201" s="18">
@@ -42022,15 +41984,15 @@
       <c r="E202" t="s">
         <v>701</v>
       </c>
-      <c r="F202" s="157">
-        <v>1</v>
-      </c>
-      <c r="G202" s="157">
+      <c r="F202" s="141">
+        <v>1</v>
+      </c>
+      <c r="G202" s="141">
         <v>1</v>
       </c>
       <c r="H202" s="88"/>
       <c r="I202" s="88"/>
-      <c r="J202" s="157">
+      <c r="J202" s="141">
         <v>1</v>
       </c>
       <c r="K202" s="72">
@@ -42269,10 +42231,10 @@
       <c r="E203" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="F203" s="158">
+      <c r="F203" s="142">
         <v>2</v>
       </c>
-      <c r="G203" s="158">
+      <c r="G203" s="142">
         <v>2</v>
       </c>
       <c r="H203" s="89" t="s">
@@ -42281,7 +42243,7 @@
       <c r="I203" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="J203" s="166" t="s">
+      <c r="J203" s="149" t="s">
         <v>150</v>
       </c>
       <c r="K203" s="18">
@@ -42521,10 +42483,10 @@
       <c r="E204" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F204" s="157">
-        <v>1</v>
-      </c>
-      <c r="G204" s="158">
+      <c r="F204" s="141">
+        <v>1</v>
+      </c>
+      <c r="G204" s="142">
         <v>2</v>
       </c>
       <c r="H204" s="89" t="s">
@@ -42533,7 +42495,7 @@
       <c r="I204" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="J204" s="166" t="s">
+      <c r="J204" s="149" t="s">
         <v>150</v>
       </c>
       <c r="K204" s="18">
@@ -42773,17 +42735,17 @@
       <c r="E205" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F205" s="157">
-        <v>1</v>
-      </c>
-      <c r="G205" s="158">
+      <c r="F205" s="141">
+        <v>1</v>
+      </c>
+      <c r="G205" s="142">
         <v>2</v>
       </c>
       <c r="H205" s="90"/>
       <c r="I205" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="J205" s="167">
+      <c r="J205" s="150">
         <v>3</v>
       </c>
       <c r="K205" s="18">
@@ -43023,10 +42985,10 @@
       <c r="E206" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F206" s="157">
-        <v>1</v>
-      </c>
-      <c r="G206" s="158">
+      <c r="F206" s="141">
+        <v>1</v>
+      </c>
+      <c r="G206" s="142">
         <v>2</v>
       </c>
       <c r="H206" s="89" t="s">
@@ -43035,7 +42997,7 @@
       <c r="I206" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="J206" s="166" t="s">
+      <c r="J206" s="149" t="s">
         <v>150</v>
       </c>
       <c r="K206" s="18">
@@ -43290,9 +43252,9 @@
       <c r="CE207" s="61"/>
     </row>
     <row r="208" spans="1:84" s="4" customFormat="1">
-      <c r="F208" s="160"/>
-      <c r="G208" s="160"/>
-      <c r="J208" s="160"/>
+      <c r="F208" s="144"/>
+      <c r="G208" s="144"/>
+      <c r="J208" s="144"/>
       <c r="S208" s="103"/>
       <c r="AK208" s="109"/>
       <c r="AN208" s="110"/>
@@ -43326,13 +43288,13 @@
       <c r="C209" s="84" t="s">
         <v>718</v>
       </c>
-      <c r="G209" s="159" t="s">
+      <c r="G209" s="143" t="s">
         <v>719</v>
       </c>
       <c r="H209" t="s">
         <v>720</v>
       </c>
-      <c r="J209" s="168" t="s">
+      <c r="J209" s="151" t="s">
         <v>721</v>
       </c>
       <c r="K209" s="94">
@@ -43383,10 +43345,10 @@
         <f>COUNTIF(D$4:D$207,D210)</f>
         <v>40</v>
       </c>
-      <c r="F210" s="161" t="s">
+      <c r="F210" s="145" t="s">
         <v>722</v>
       </c>
-      <c r="J210" s="168" t="s">
+      <c r="J210" s="151" t="s">
         <v>723</v>
       </c>
       <c r="K210" s="95">
@@ -43477,10 +43439,10 @@
         <f>COUNTIF(D$4:D$207,D211)</f>
         <v>18</v>
       </c>
-      <c r="F211" s="161" t="s">
+      <c r="F211" s="145" t="s">
         <v>725</v>
       </c>
-      <c r="J211" s="169" t="s">
+      <c r="J211" s="152" t="s">
         <v>726</v>
       </c>
       <c r="K211" s="96">
@@ -43571,10 +43533,10 @@
         <f>COUNTIF(D$4:D$207,D212)</f>
         <v>54</v>
       </c>
-      <c r="F212" s="161" t="s">
+      <c r="F212" s="145" t="s">
         <v>728</v>
       </c>
-      <c r="J212" s="168" t="s">
+      <c r="J212" s="151" t="s">
         <v>729</v>
       </c>
       <c r="K212" s="30">
@@ -43665,10 +43627,10 @@
         <f>COUNTIF(D$4:D$207,D213)</f>
         <v>8</v>
       </c>
-      <c r="F213" s="161" t="s">
+      <c r="F213" s="145" t="s">
         <v>731</v>
       </c>
-      <c r="J213" s="168" t="s">
+      <c r="J213" s="151" t="s">
         <v>732</v>
       </c>
       <c r="K213" s="30">
@@ -43759,10 +43721,10 @@
         <f t="shared" ref="E214:E219" si="5">COUNTIF(D$4:D$207,D214)</f>
         <v>15</v>
       </c>
-      <c r="F214" s="161" t="s">
+      <c r="F214" s="145" t="s">
         <v>733</v>
       </c>
-      <c r="J214" s="168" t="s">
+      <c r="J214" s="151" t="s">
         <v>734</v>
       </c>
       <c r="K214" s="97">
@@ -43853,10 +43815,10 @@
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="F215" s="162" t="s">
+      <c r="F215" s="146" t="s">
         <v>735</v>
       </c>
-      <c r="J215" s="168" t="s">
+      <c r="J215" s="151" t="s">
         <v>736</v>
       </c>
       <c r="K215" s="30"/>
@@ -43914,10 +43876,10 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="F216" s="162" t="s">
+      <c r="F216" s="146" t="s">
         <v>737</v>
       </c>
-      <c r="J216" s="168" t="s">
+      <c r="J216" s="151" t="s">
         <v>738</v>
       </c>
       <c r="K216" s="30"/>
@@ -43975,10 +43937,10 @@
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="F217" s="162" t="s">
+      <c r="F217" s="146" t="s">
         <v>739</v>
       </c>
-      <c r="J217" s="168" t="s">
+      <c r="J217" s="151" t="s">
         <v>740</v>
       </c>
       <c r="K217" s="30"/>
@@ -44036,10 +43998,10 @@
         <f t="shared" si="5"/>
         <v>31</v>
       </c>
-      <c r="F218" s="162" t="s">
+      <c r="F218" s="146" t="s">
         <v>741</v>
       </c>
-      <c r="J218" s="168" t="s">
+      <c r="J218" s="151" t="s">
         <v>742</v>
       </c>
       <c r="K218" s="30"/>
@@ -44097,10 +44059,10 @@
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="F219" s="162" t="s">
+      <c r="F219" s="146" t="s">
         <v>743</v>
       </c>
-      <c r="J219" s="168" t="s">
+      <c r="J219" s="151" t="s">
         <v>744</v>
       </c>
       <c r="K219" s="30"/>
@@ -44156,7 +44118,7 @@
       <c r="S223" s="25"/>
     </row>
     <row r="224" spans="3:83">
-      <c r="J224" s="159" t="str">
+      <c r="J224" s="143" t="str">
         <f>D210</f>
         <v>Construction (Civil)</v>
       </c>
@@ -44184,7 +44146,7 @@
       <c r="S224" s="25"/>
     </row>
     <row r="225" spans="10:84">
-      <c r="J225" s="159" t="str">
+      <c r="J225" s="143" t="str">
         <f t="shared" ref="J225:J227" si="7">D211</f>
         <v>Construction (commercial building)</v>
       </c>
@@ -44212,7 +44174,7 @@
       <c r="S225" s="25"/>
     </row>
     <row r="226" spans="10:84">
-      <c r="J226" s="159" t="str">
+      <c r="J226" s="143" t="str">
         <f t="shared" si="7"/>
         <v>Construction (residential building)</v>
       </c>
@@ -44240,7 +44202,7 @@
       <c r="S226" s="25"/>
     </row>
     <row r="227" spans="10:84">
-      <c r="J227" s="159" t="str">
+      <c r="J227" s="143" t="str">
         <f t="shared" si="7"/>
         <v>Construction (institutional building)</v>
       </c>
@@ -44268,7 +44230,7 @@
       <c r="S227" s="25"/>
     </row>
     <row r="228" spans="10:84">
-      <c r="J228" s="159" t="str">
+      <c r="J228" s="143" t="str">
         <f t="shared" ref="J228:K228" si="8">D214</f>
         <v>Construction (Industrial)</v>
       </c>
@@ -44296,7 +44258,7 @@
       <c r="S228" s="25"/>
     </row>
     <row r="229" spans="10:84">
-      <c r="J229" s="151" t="s">
+      <c r="J229" s="135" t="s">
         <v>750</v>
       </c>
       <c r="K229" s="8">
@@ -44323,7 +44285,7 @@
       <c r="S229" s="25"/>
     </row>
     <row r="230" spans="10:84">
-      <c r="J230" s="159" t="str">
+      <c r="J230" s="143" t="str">
         <f>C215</f>
         <v>Engineering</v>
       </c>
@@ -44351,7 +44313,7 @@
       <c r="S230" s="25"/>
     </row>
     <row r="231" spans="10:84">
-      <c r="J231" s="159" t="str">
+      <c r="J231" s="143" t="str">
         <f>C216</f>
         <v>Mobility</v>
       </c>
@@ -44379,7 +44341,7 @@
       <c r="S231" s="25"/>
     </row>
     <row r="232" spans="10:84">
-      <c r="J232" s="159" t="str">
+      <c r="J232" s="143" t="str">
         <f>C217</f>
         <v>Event management</v>
       </c>
@@ -44407,7 +44369,7 @@
       <c r="S232" s="25"/>
     </row>
     <row r="233" spans="10:84">
-      <c r="J233" s="159" t="str">
+      <c r="J233" s="143" t="str">
         <f>C218</f>
         <v>IT</v>
       </c>
@@ -44435,7 +44397,7 @@
       <c r="S233" s="25"/>
     </row>
     <row r="234" spans="10:84">
-      <c r="J234" s="159" t="str">
+      <c r="J234" s="143" t="str">
         <f>C219</f>
         <v>Education</v>
       </c>
@@ -44508,11 +44470,8 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="30">
-    <mergeCell ref="Y1:AP1"/>
-    <mergeCell ref="AQ1:AY1"/>
-    <mergeCell ref="BI2:BK2"/>
-    <mergeCell ref="BL2:BN2"/>
-    <mergeCell ref="BO2:BQ2"/>
+    <mergeCell ref="BX2:BZ2"/>
+    <mergeCell ref="CA2:CC2"/>
     <mergeCell ref="BR2:BT2"/>
     <mergeCell ref="BU2:BW2"/>
     <mergeCell ref="A1:E2"/>
@@ -44529,6 +44488,11 @@
     <mergeCell ref="AE2:AG2"/>
     <mergeCell ref="AH2:AJ2"/>
     <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="Y1:AP1"/>
+    <mergeCell ref="AQ1:AY1"/>
+    <mergeCell ref="BI2:BK2"/>
+    <mergeCell ref="BL2:BN2"/>
+    <mergeCell ref="BO2:BQ2"/>
     <mergeCell ref="AN2:AP2"/>
     <mergeCell ref="AQ2:AS2"/>
     <mergeCell ref="AT2:AV2"/>
@@ -44536,8 +44500,6 @@
     <mergeCell ref="AZ2:BB2"/>
     <mergeCell ref="BC2:BE2"/>
     <mergeCell ref="BF2:BH2"/>
-    <mergeCell ref="BX2:BZ2"/>
-    <mergeCell ref="CA2:CC2"/>
   </mergeCells>
   <conditionalFormatting sqref="Q10 Q15 Q16:R16 Q30:R30 Q35:R38 Q39">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="lessThanOrEqual">

--- a/dataset/DSLIB_Analysis_Scheet.xlsx
+++ b/dataset/DSLIB_Analysis_Scheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/jisantos_ubu_es/Documents/CodeDrive/GitHub/counterEVM-1/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="13_ncr:1_{397A7FD8-BC23-430C-B2C6-E98CFB6549D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92B32219-D8E5-4F52-B320-1AED125380EF}"/>
+  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{397A7FD8-BC23-430C-B2C6-E98CFB6549D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF564D3-DF71-4C57-B8A0-5F19F477967D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3359,7 +3359,7 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3741,16 +3741,10 @@
     <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3771,17 +3765,15 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Bueno" xfId="4" builtinId="26"/>
@@ -6233,232 +6225,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:84" ht="16" customHeight="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="155" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="159" t="s">
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="157" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="159"/>
-      <c r="H1" s="160"/>
-      <c r="I1" s="158" t="s">
+      <c r="G1" s="157"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="161"/>
-      <c r="K1" s="160" t="s">
+      <c r="J1" s="159"/>
+      <c r="K1" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="160"/>
-      <c r="M1" s="160"/>
-      <c r="N1" s="158" t="s">
+      <c r="L1" s="158"/>
+      <c r="M1" s="158"/>
+      <c r="N1" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="158"/>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="162" t="s">
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="160" t="s">
         <v>131</v>
       </c>
-      <c r="R1" s="162"/>
-      <c r="S1" s="158" t="s">
+      <c r="R1" s="160"/>
+      <c r="S1" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="T1" s="158"/>
-      <c r="U1" s="158"/>
-      <c r="V1" s="158"/>
-      <c r="W1" s="158"/>
-      <c r="X1" s="158"/>
-      <c r="Y1" s="153" t="s">
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="161" t="s">
         <v>71</v>
       </c>
-      <c r="Z1" s="153"/>
-      <c r="AA1" s="153"/>
-      <c r="AB1" s="153"/>
-      <c r="AC1" s="153"/>
-      <c r="AD1" s="153"/>
-      <c r="AE1" s="153"/>
-      <c r="AF1" s="153"/>
-      <c r="AG1" s="153"/>
-      <c r="AH1" s="153"/>
-      <c r="AI1" s="153"/>
-      <c r="AJ1" s="153"/>
-      <c r="AK1" s="153"/>
-      <c r="AL1" s="153"/>
-      <c r="AM1" s="153"/>
-      <c r="AN1" s="153"/>
-      <c r="AO1" s="153"/>
-      <c r="AP1" s="153"/>
-      <c r="AQ1" s="154" t="s">
+      <c r="Z1" s="161"/>
+      <c r="AA1" s="161"/>
+      <c r="AB1" s="161"/>
+      <c r="AC1" s="161"/>
+      <c r="AD1" s="161"/>
+      <c r="AE1" s="161"/>
+      <c r="AF1" s="161"/>
+      <c r="AG1" s="161"/>
+      <c r="AH1" s="161"/>
+      <c r="AI1" s="161"/>
+      <c r="AJ1" s="161"/>
+      <c r="AK1" s="161"/>
+      <c r="AL1" s="161"/>
+      <c r="AM1" s="161"/>
+      <c r="AN1" s="161"/>
+      <c r="AO1" s="161"/>
+      <c r="AP1" s="161"/>
+      <c r="AQ1" s="163" t="s">
         <v>86</v>
       </c>
-      <c r="AR1" s="154"/>
-      <c r="AS1" s="154"/>
-      <c r="AT1" s="154"/>
-      <c r="AU1" s="154"/>
-      <c r="AV1" s="154"/>
-      <c r="AW1" s="154"/>
-      <c r="AX1" s="154"/>
-      <c r="AY1" s="154"/>
-      <c r="AZ1" s="153" t="s">
+      <c r="AR1" s="163"/>
+      <c r="AS1" s="163"/>
+      <c r="AT1" s="163"/>
+      <c r="AU1" s="163"/>
+      <c r="AV1" s="163"/>
+      <c r="AW1" s="163"/>
+      <c r="AX1" s="163"/>
+      <c r="AY1" s="163"/>
+      <c r="AZ1" s="161" t="s">
         <v>89</v>
       </c>
-      <c r="BA1" s="153"/>
-      <c r="BB1" s="153"/>
-      <c r="BC1" s="153"/>
-      <c r="BD1" s="153"/>
-      <c r="BE1" s="153"/>
-      <c r="BF1" s="153"/>
-      <c r="BG1" s="153"/>
-      <c r="BH1" s="153"/>
-      <c r="BI1" s="163" t="s">
+      <c r="BA1" s="161"/>
+      <c r="BB1" s="161"/>
+      <c r="BC1" s="161"/>
+      <c r="BD1" s="161"/>
+      <c r="BE1" s="161"/>
+      <c r="BF1" s="161"/>
+      <c r="BG1" s="161"/>
+      <c r="BH1" s="161"/>
+      <c r="BI1" s="162" t="s">
         <v>91</v>
       </c>
-      <c r="BJ1" s="163"/>
-      <c r="BK1" s="163"/>
-      <c r="BL1" s="163"/>
-      <c r="BM1" s="163"/>
-      <c r="BN1" s="163"/>
-      <c r="BO1" s="163"/>
-      <c r="BP1" s="163"/>
-      <c r="BQ1" s="163"/>
-      <c r="BR1" s="163"/>
-      <c r="BS1" s="163"/>
-      <c r="BT1" s="163"/>
-      <c r="BU1" s="163"/>
-      <c r="BV1" s="163"/>
-      <c r="BW1" s="163"/>
-      <c r="BX1" s="163"/>
-      <c r="BY1" s="163"/>
-      <c r="BZ1" s="163"/>
-      <c r="CA1" s="163"/>
-      <c r="CB1" s="163"/>
-      <c r="CC1" s="163"/>
-      <c r="CD1" s="163"/>
-      <c r="CE1" s="163"/>
+      <c r="BJ1" s="162"/>
+      <c r="BK1" s="162"/>
+      <c r="BL1" s="162"/>
+      <c r="BM1" s="162"/>
+      <c r="BN1" s="162"/>
+      <c r="BO1" s="162"/>
+      <c r="BP1" s="162"/>
+      <c r="BQ1" s="162"/>
+      <c r="BR1" s="162"/>
+      <c r="BS1" s="162"/>
+      <c r="BT1" s="162"/>
+      <c r="BU1" s="162"/>
+      <c r="BV1" s="162"/>
+      <c r="BW1" s="162"/>
+      <c r="BX1" s="162"/>
+      <c r="BY1" s="162"/>
+      <c r="BZ1" s="162"/>
+      <c r="CA1" s="162"/>
+      <c r="CB1" s="162"/>
+      <c r="CC1" s="162"/>
+      <c r="CD1" s="162"/>
+      <c r="CE1" s="162"/>
     </row>
     <row r="2" spans="1:84" ht="16" customHeight="1">
-      <c r="A2" s="157"/>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="160"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="160"/>
-      <c r="M2" s="160"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="162"/>
-      <c r="R2" s="162"/>
-      <c r="S2" s="158"/>
-      <c r="T2" s="158"/>
-      <c r="U2" s="158"/>
-      <c r="V2" s="158"/>
-      <c r="W2" s="158"/>
-      <c r="X2" s="158"/>
-      <c r="Y2" s="155" t="s">
+      <c r="A2" s="155"/>
+      <c r="B2" s="155"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="156"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="156"/>
+      <c r="Q2" s="160"/>
+      <c r="R2" s="160"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="156"/>
+      <c r="U2" s="156"/>
+      <c r="V2" s="156"/>
+      <c r="W2" s="156"/>
+      <c r="X2" s="156"/>
+      <c r="Y2" s="154" t="s">
         <v>132</v>
       </c>
-      <c r="Z2" s="155"/>
-      <c r="AA2" s="155"/>
-      <c r="AB2" s="156" t="s">
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="154"/>
+      <c r="AB2" s="153" t="s">
         <v>75</v>
       </c>
-      <c r="AC2" s="156"/>
-      <c r="AD2" s="156"/>
-      <c r="AE2" s="155" t="s">
+      <c r="AC2" s="153"/>
+      <c r="AD2" s="153"/>
+      <c r="AE2" s="154" t="s">
         <v>77</v>
       </c>
-      <c r="AF2" s="155"/>
-      <c r="AG2" s="155"/>
-      <c r="AH2" s="156" t="s">
+      <c r="AF2" s="154"/>
+      <c r="AG2" s="154"/>
+      <c r="AH2" s="153" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" s="156"/>
-      <c r="AJ2" s="156"/>
-      <c r="AK2" s="155" t="s">
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="153"/>
+      <c r="AK2" s="154" t="s">
         <v>81</v>
       </c>
-      <c r="AL2" s="155"/>
-      <c r="AM2" s="155"/>
-      <c r="AN2" s="156" t="s">
+      <c r="AL2" s="154"/>
+      <c r="AM2" s="154"/>
+      <c r="AN2" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="AO2" s="156"/>
-      <c r="AP2" s="156"/>
-      <c r="AQ2" s="155" t="s">
+      <c r="AO2" s="153"/>
+      <c r="AP2" s="153"/>
+      <c r="AQ2" s="154" t="s">
         <v>79</v>
       </c>
-      <c r="AR2" s="155"/>
-      <c r="AS2" s="155"/>
-      <c r="AT2" s="156" t="s">
+      <c r="AR2" s="154"/>
+      <c r="AS2" s="154"/>
+      <c r="AT2" s="153" t="s">
         <v>81</v>
       </c>
-      <c r="AU2" s="156"/>
-      <c r="AV2" s="156"/>
-      <c r="AW2" s="155" t="s">
+      <c r="AU2" s="153"/>
+      <c r="AV2" s="153"/>
+      <c r="AW2" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="AX2" s="155"/>
-      <c r="AY2" s="155"/>
-      <c r="AZ2" s="156" t="s">
+      <c r="AX2" s="154"/>
+      <c r="AY2" s="154"/>
+      <c r="AZ2" s="153" t="s">
         <v>79</v>
       </c>
-      <c r="BA2" s="156"/>
-      <c r="BB2" s="156"/>
-      <c r="BC2" s="155" t="s">
+      <c r="BA2" s="153"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="154" t="s">
         <v>81</v>
       </c>
-      <c r="BD2" s="155"/>
-      <c r="BE2" s="155"/>
-      <c r="BF2" s="156" t="s">
+      <c r="BD2" s="154"/>
+      <c r="BE2" s="154"/>
+      <c r="BF2" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="BG2" s="156"/>
-      <c r="BH2" s="156"/>
-      <c r="BI2" s="155" t="s">
+      <c r="BG2" s="153"/>
+      <c r="BH2" s="153"/>
+      <c r="BI2" s="154" t="s">
         <v>93</v>
       </c>
-      <c r="BJ2" s="155"/>
-      <c r="BK2" s="155"/>
-      <c r="BL2" s="156" t="s">
+      <c r="BJ2" s="154"/>
+      <c r="BK2" s="154"/>
+      <c r="BL2" s="153" t="s">
         <v>95</v>
       </c>
-      <c r="BM2" s="156"/>
-      <c r="BN2" s="156"/>
-      <c r="BO2" s="155" t="s">
+      <c r="BM2" s="153"/>
+      <c r="BN2" s="153"/>
+      <c r="BO2" s="154" t="s">
         <v>97</v>
       </c>
-      <c r="BP2" s="155"/>
-      <c r="BQ2" s="155"/>
-      <c r="BR2" s="156" t="s">
+      <c r="BP2" s="154"/>
+      <c r="BQ2" s="154"/>
+      <c r="BR2" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="BS2" s="156"/>
-      <c r="BT2" s="156"/>
-      <c r="BU2" s="155" t="s">
+      <c r="BS2" s="153"/>
+      <c r="BT2" s="153"/>
+      <c r="BU2" s="154" t="s">
         <v>101</v>
       </c>
-      <c r="BV2" s="155"/>
-      <c r="BW2" s="155"/>
-      <c r="BX2" s="156" t="s">
+      <c r="BV2" s="154"/>
+      <c r="BW2" s="154"/>
+      <c r="BX2" s="153" t="s">
         <v>103</v>
       </c>
-      <c r="BY2" s="156"/>
-      <c r="BZ2" s="156"/>
-      <c r="CA2" s="155" t="s">
+      <c r="BY2" s="153"/>
+      <c r="BZ2" s="153"/>
+      <c r="CA2" s="154" t="s">
         <v>105</v>
       </c>
-      <c r="CB2" s="155"/>
-      <c r="CC2" s="155"/>
+      <c r="CB2" s="154"/>
+      <c r="CC2" s="154"/>
       <c r="CD2" s="41" t="s">
         <v>133</v>
       </c>
@@ -12062,10 +12054,10 @@
       <c r="CF29" s="33"/>
     </row>
     <row r="30" spans="1:84">
-      <c r="A30" s="166" t="s">
+      <c r="A30" t="s">
         <v>261</v>
       </c>
-      <c r="B30" s="167" t="s">
+      <c r="B30" s="6" t="s">
         <v>262</v>
       </c>
       <c r="C30" t="s">
@@ -22117,7 +22109,7 @@
       </c>
       <c r="CF83" s="33"/>
     </row>
-    <row r="84" spans="1:84">
+    <row r="84" spans="1:84" hidden="1">
       <c r="A84" s="6" t="s">
         <v>404</v>
       </c>
@@ -22144,7 +22136,7 @@
         <v>149</v>
       </c>
       <c r="J84" s="148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K84" s="6">
         <v>26</v>
@@ -32486,10 +32478,10 @@
       <c r="CF150" s="18"/>
     </row>
     <row r="151" spans="1:84" hidden="1">
-      <c r="A151" s="164" t="s">
+      <c r="A151" s="53" t="s">
         <v>568</v>
       </c>
-      <c r="B151" s="165" t="s">
+      <c r="B151" s="54" t="s">
         <v>569</v>
       </c>
       <c r="C151" s="53" t="s">
@@ -32732,10 +32724,10 @@
       <c r="CF151" s="18"/>
     </row>
     <row r="152" spans="1:84" hidden="1">
-      <c r="A152" s="164" t="s">
+      <c r="A152" s="53" t="s">
         <v>570</v>
       </c>
-      <c r="B152" s="165" t="s">
+      <c r="B152" s="54" t="s">
         <v>571</v>
       </c>
       <c r="C152" s="53" t="s">
@@ -32938,10 +32930,10 @@
       <c r="CF152" s="18"/>
     </row>
     <row r="153" spans="1:84">
-      <c r="A153" s="164" t="s">
+      <c r="A153" s="53" t="s">
         <v>572</v>
       </c>
-      <c r="B153" s="165" t="s">
+      <c r="B153" s="54" t="s">
         <v>573</v>
       </c>
       <c r="C153" s="53" t="s">
@@ -33180,10 +33172,10 @@
       <c r="CF153" s="18"/>
     </row>
     <row r="154" spans="1:84" hidden="1">
-      <c r="A154" s="164" t="s">
+      <c r="A154" s="53" t="s">
         <v>574</v>
       </c>
-      <c r="B154" s="165" t="s">
+      <c r="B154" s="54" t="s">
         <v>575</v>
       </c>
       <c r="C154" s="53" t="s">
@@ -33350,10 +33342,10 @@
       <c r="CF154" s="18"/>
     </row>
     <row r="155" spans="1:84" hidden="1">
-      <c r="A155" s="164" t="s">
+      <c r="A155" s="53" t="s">
         <v>576</v>
       </c>
-      <c r="B155" s="165" t="s">
+      <c r="B155" s="54" t="s">
         <v>577</v>
       </c>
       <c r="C155" s="53" t="s">
@@ -33550,10 +33542,10 @@
       <c r="CF155" s="18"/>
     </row>
     <row r="156" spans="1:84">
-      <c r="A156" s="164" t="s">
+      <c r="A156" s="53" t="s">
         <v>578</v>
       </c>
-      <c r="B156" s="165" t="s">
+      <c r="B156" s="54" t="s">
         <v>579</v>
       </c>
       <c r="C156" s="53" t="s">
@@ -33792,10 +33784,10 @@
       <c r="CF156" s="18"/>
     </row>
     <row r="157" spans="1:84" hidden="1">
-      <c r="A157" s="165" t="s">
+      <c r="A157" s="54" t="s">
         <v>580</v>
       </c>
-      <c r="B157" s="165" t="s">
+      <c r="B157" s="54" t="s">
         <v>581</v>
       </c>
       <c r="C157" s="53" t="s">
@@ -33956,10 +33948,10 @@
       <c r="CF157" s="18"/>
     </row>
     <row r="158" spans="1:84" hidden="1">
-      <c r="A158" s="165" t="s">
+      <c r="A158" s="54" t="s">
         <v>583</v>
       </c>
-      <c r="B158" s="165" t="s">
+      <c r="B158" s="54" t="s">
         <v>423</v>
       </c>
       <c r="C158" s="53" t="s">
@@ -34080,10 +34072,10 @@
       <c r="CF158" s="18"/>
     </row>
     <row r="159" spans="1:84">
-      <c r="A159" s="165" t="s">
+      <c r="A159" s="54" t="s">
         <v>584</v>
       </c>
-      <c r="B159" s="165" t="s">
+      <c r="B159" s="54" t="s">
         <v>585</v>
       </c>
       <c r="C159" s="53" t="s">
@@ -34206,10 +34198,10 @@
       <c r="CF159" s="18"/>
     </row>
     <row r="160" spans="1:84">
-      <c r="A160" s="165" t="s">
+      <c r="A160" s="54" t="s">
         <v>586</v>
       </c>
-      <c r="B160" s="165" t="s">
+      <c r="B160" s="54" t="s">
         <v>587</v>
       </c>
       <c r="C160" s="53" t="s">
@@ -34332,10 +34324,10 @@
       <c r="CF160" s="18"/>
     </row>
     <row r="161" spans="1:84">
-      <c r="A161" s="165" t="s">
+      <c r="A161" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="B161" s="165" t="s">
+      <c r="B161" s="54" t="s">
         <v>589</v>
       </c>
       <c r="C161" s="53" t="s">
@@ -34458,10 +34450,10 @@
       <c r="CF161" s="18"/>
     </row>
     <row r="162" spans="1:84">
-      <c r="A162" s="165" t="s">
+      <c r="A162" s="54" t="s">
         <v>590</v>
       </c>
-      <c r="B162" s="165" t="s">
+      <c r="B162" s="54" t="s">
         <v>591</v>
       </c>
       <c r="C162" s="53" t="s">
@@ -34584,10 +34576,10 @@
       <c r="CF162" s="18"/>
     </row>
     <row r="163" spans="1:84" hidden="1">
-      <c r="A163" s="165" t="s">
+      <c r="A163" s="54" t="s">
         <v>592</v>
       </c>
-      <c r="B163" s="165" t="s">
+      <c r="B163" s="54" t="s">
         <v>593</v>
       </c>
       <c r="C163" s="53" t="s">
@@ -34708,10 +34700,10 @@
       <c r="CF163" s="18"/>
     </row>
     <row r="164" spans="1:84" hidden="1">
-      <c r="A164" s="165" t="s">
+      <c r="A164" s="54" t="s">
         <v>594</v>
       </c>
-      <c r="B164" s="165" t="s">
+      <c r="B164" s="54" t="s">
         <v>595</v>
       </c>
       <c r="C164" s="53" t="s">
@@ -34832,10 +34824,10 @@
       <c r="CF164" s="18"/>
     </row>
     <row r="165" spans="1:84" hidden="1">
-      <c r="A165" s="164" t="s">
+      <c r="A165" s="53" t="s">
         <v>596</v>
       </c>
-      <c r="B165" s="165" t="s">
+      <c r="B165" s="54" t="s">
         <v>597</v>
       </c>
       <c r="C165" s="53" t="s">
@@ -35232,7 +35224,7 @@
       <c r="CC166" s="80"/>
       <c r="CF166" s="18"/>
     </row>
-    <row r="167" spans="1:84">
+    <row r="167" spans="1:84" hidden="1">
       <c r="A167" s="53" t="s">
         <v>600</v>
       </c>
@@ -35257,7 +35249,7 @@
       <c r="H167" s="58"/>
       <c r="I167" s="9"/>
       <c r="J167" s="136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K167" s="18">
         <v>30</v>
@@ -40353,7 +40345,7 @@
         <v>95509712</v>
       </c>
     </row>
-    <row r="194" spans="1:84" s="2" customFormat="1">
+    <row r="194" spans="1:84" s="2" customFormat="1" hidden="1">
       <c r="A194" s="53" t="s">
         <v>667</v>
       </c>
@@ -40380,7 +40372,7 @@
         <v>149</v>
       </c>
       <c r="J194" s="139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K194" s="18">
         <v>42</v>
@@ -40560,7 +40552,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="195" spans="1:84" s="2" customFormat="1">
+    <row r="195" spans="1:84" s="2" customFormat="1" hidden="1">
       <c r="A195" s="53" t="s">
         <v>671</v>
       </c>
@@ -40587,7 +40579,7 @@
         <v>149</v>
       </c>
       <c r="J195" s="139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K195" s="18">
         <v>49</v>
@@ -40779,7 +40771,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="196" spans="1:84" s="2" customFormat="1">
+    <row r="196" spans="1:84" s="2" customFormat="1" hidden="1">
       <c r="A196" s="53" t="s">
         <v>676</v>
       </c>
@@ -40806,7 +40798,7 @@
         <v>149</v>
       </c>
       <c r="J196" s="139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K196" s="18">
         <v>28</v>
@@ -41968,7 +41960,7 @@
       <c r="CE201" s="61"/>
       <c r="CF201" s="33"/>
     </row>
-    <row r="202" spans="1:84">
+    <row r="202" spans="1:84" hidden="1">
       <c r="A202" t="s">
         <v>698</v>
       </c>
@@ -41993,7 +41985,7 @@
       <c r="H202" s="88"/>
       <c r="I202" s="88"/>
       <c r="J202" s="141">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K202" s="72">
         <v>66</v>
@@ -44470,6 +44462,20 @@
     </filterColumn>
   </autoFilter>
   <mergeCells count="30">
+    <mergeCell ref="BL2:BN2"/>
+    <mergeCell ref="BO2:BQ2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AW2:AY2"/>
+    <mergeCell ref="AZ2:BB2"/>
+    <mergeCell ref="BC2:BE2"/>
+    <mergeCell ref="BF2:BH2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="Y1:AP1"/>
+    <mergeCell ref="AQ1:AY1"/>
+    <mergeCell ref="BI2:BK2"/>
     <mergeCell ref="BX2:BZ2"/>
     <mergeCell ref="CA2:CC2"/>
     <mergeCell ref="BR2:BT2"/>
@@ -44486,20 +44492,6 @@
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="Y1:AP1"/>
-    <mergeCell ref="AQ1:AY1"/>
-    <mergeCell ref="BI2:BK2"/>
-    <mergeCell ref="BL2:BN2"/>
-    <mergeCell ref="BO2:BQ2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AW2:AY2"/>
-    <mergeCell ref="AZ2:BB2"/>
-    <mergeCell ref="BC2:BE2"/>
-    <mergeCell ref="BF2:BH2"/>
   </mergeCells>
   <conditionalFormatting sqref="Q10 Q15 Q16:R16 Q30:R30 Q35:R38 Q39">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="lessThanOrEqual">

--- a/dataset/DSLIB_Analysis_Scheet.xlsx
+++ b/dataset/DSLIB_Analysis_Scheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://universidaddeburgos-my.sharepoint.com/personal/jisantos_ubu_es/Documents/CodeDrive/GitHub/counterEVM-1/dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariapereda/Dropbox/UPM/investigacion/Josema&amp;cia/Counterfactuals/Repo_comun/counterEVM/dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="13_ncr:1_{397A7FD8-BC23-430C-B2C6-E98CFB6549D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCF564D3-DF71-4C57-B8A0-5F19F477967D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F3A7CD-DE37-254C-A7F6-2136452C7704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35080" yWindow="1600" windowWidth="36720" windowHeight="20480" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -2940,12 +2940,19 @@
     <numFmt numFmtId="169" formatCode="_ [$€-2]\ * #,##0.00_ ;_ [$€-2]\ * \-#,##0.00_ ;_ [$€-2]\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3351,25 +3358,25 @@
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3382,34 +3389,34 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3421,10 +3428,10 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
@@ -3442,20 +3449,20 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3465,10 +3472,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3480,43 +3487,43 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3525,31 +3532,31 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="14" fillId="14" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="15" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="15" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3561,55 +3568,55 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -3624,17 +3631,17 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -3647,56 +3654,47 @@
     <xf numFmtId="168" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="5" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3705,40 +3703,49 @@
     <xf numFmtId="0" fontId="34" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3747,42 +3754,48 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
-    <cellStyle name="Bueno" xfId="4" builtinId="26"/>
-    <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
-    <cellStyle name="Incorrecto" xfId="3" builtinId="27"/>
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Comma" xfId="6" builtinId="3"/>
+    <cellStyle name="Good" xfId="4" builtinId="26"/>
+    <cellStyle name="Hyperlink" xfId="5" builtinId="8"/>
     <cellStyle name="Komma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Millares" xfId="6" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="7" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="7" builtinId="5"/>
     <cellStyle name="Standaard 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
   </cellStyles>
   <dxfs count="11">
@@ -3915,7 +3928,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4900,10 +4913,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5227,7 +5236,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M109"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="115" customWidth="1"/>
     <col min="2" max="2" width="48.83203125" style="115" customWidth="1"/>
@@ -5235,7 +5244,7 @@
     <col min="4" max="16384" width="10.83203125" style="115"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="31">
+    <row r="1" spans="1:13" ht="31" x14ac:dyDescent="0.35">
       <c r="A1" s="116" t="s">
         <v>0</v>
       </c>
@@ -5251,7 +5260,7 @@
       <c r="K1" s="117"/>
       <c r="L1" s="117"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="118" t="s">
         <v>1</v>
       </c>
@@ -5270,7 +5279,7 @@
       <c r="L3" s="120"/>
       <c r="M3" s="120"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="118" t="s">
         <v>3</v>
       </c>
@@ -5289,7 +5298,7 @@
       <c r="L4" s="120"/>
       <c r="M4" s="120"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="118" t="s">
         <v>5</v>
       </c>
@@ -5308,7 +5317,7 @@
       <c r="L5" s="121"/>
       <c r="M5" s="121"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="118"/>
       <c r="B6" s="121" t="s">
         <v>753</v>
@@ -5325,7 +5334,7 @@
       <c r="L6" s="121"/>
       <c r="M6" s="121"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="118" t="s">
         <v>7</v>
       </c>
@@ -5344,7 +5353,7 @@
       <c r="L7" s="121"/>
       <c r="M7" s="121"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="123" t="s">
         <v>8</v>
       </c>
@@ -5361,16 +5370,16 @@
       <c r="L9" s="124"/>
       <c r="M9" s="124"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10" s="115" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="125"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="7"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="123" t="s">
         <v>10</v>
       </c>
@@ -5387,7 +5396,7 @@
       <c r="L12" s="124"/>
       <c r="M12" s="124"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B13" s="115" t="s">
         <v>11</v>
       </c>
@@ -5395,7 +5404,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="115" t="s">
         <v>13</v>
       </c>
@@ -5403,7 +5412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15" s="115" t="s">
         <v>15</v>
       </c>
@@ -5411,7 +5420,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B16" s="115" t="s">
         <v>17</v>
       </c>
@@ -5419,7 +5428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="123" t="s">
         <v>19</v>
       </c>
@@ -5436,13 +5445,13 @@
       <c r="L18" s="124"/>
       <c r="M18" s="124"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="126"/>
       <c r="B19" s="132" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B20" s="115" t="s">
         <v>21</v>
       </c>
@@ -5450,7 +5459,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B21" s="115" t="s">
         <v>23</v>
       </c>
@@ -5458,7 +5467,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B22" s="115" t="s">
         <v>25</v>
       </c>
@@ -5466,7 +5475,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="114" customFormat="1">
+    <row r="23" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="128" t="s">
         <v>27</v>
       </c>
@@ -5474,7 +5483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="123" t="s">
         <v>29</v>
       </c>
@@ -5491,13 +5500,13 @@
       <c r="L25" s="124"/>
       <c r="M25" s="124"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="126"/>
       <c r="B26" s="132" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B27" s="115" t="s">
         <v>31</v>
       </c>
@@ -5505,7 +5514,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B28" s="115" t="s">
         <v>33</v>
       </c>
@@ -5513,7 +5522,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="114" customFormat="1">
+    <row r="29" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="128" t="s">
         <v>27</v>
       </c>
@@ -5521,10 +5530,10 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B30" s="129"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="123" t="s">
         <v>35</v>
       </c>
@@ -5541,7 +5550,7 @@
       <c r="L31" s="124"/>
       <c r="M31" s="124"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B32" s="115" t="s">
         <v>36</v>
       </c>
@@ -5549,7 +5558,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B33" s="115" t="s">
         <v>38</v>
       </c>
@@ -5557,7 +5566,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B34" s="115" t="s">
         <v>40</v>
       </c>
@@ -5565,10 +5574,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B35" s="129"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="123" t="s">
         <v>42</v>
       </c>
@@ -5585,7 +5594,7 @@
       <c r="L36" s="124"/>
       <c r="M36" s="124"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B37" s="115" t="s">
         <v>43</v>
       </c>
@@ -5593,7 +5602,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B38" s="115" t="s">
         <v>45</v>
       </c>
@@ -5601,7 +5610,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B39" s="115" t="s">
         <v>47</v>
       </c>
@@ -5609,7 +5618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="114" customFormat="1">
+    <row r="40" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="128" t="s">
         <v>27</v>
       </c>
@@ -5617,10 +5626,10 @@
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B41" s="129"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="123" t="s">
         <v>50</v>
       </c>
@@ -5637,7 +5646,7 @@
       <c r="L42" s="124"/>
       <c r="M42" s="124"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B43" s="115" t="s">
         <v>51</v>
       </c>
@@ -5645,7 +5654,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B44" s="115" t="s">
         <v>53</v>
       </c>
@@ -5653,10 +5662,10 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B45" s="129"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="123" t="s">
         <v>55</v>
       </c>
@@ -5673,7 +5682,7 @@
       <c r="L46" s="124"/>
       <c r="M46" s="124"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B47" s="115" t="s">
         <v>56</v>
       </c>
@@ -5681,7 +5690,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B48" s="115" t="s">
         <v>58</v>
       </c>
@@ -5689,7 +5698,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B49" s="115" t="s">
         <v>60</v>
       </c>
@@ -5697,7 +5706,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B50" s="115" t="s">
         <v>62</v>
       </c>
@@ -5705,7 +5714,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B51" s="115" t="s">
         <v>64</v>
       </c>
@@ -5713,7 +5722,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B52" s="115" t="s">
         <v>66</v>
       </c>
@@ -5721,7 +5730,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="114" customFormat="1">
+    <row r="53" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="128" t="s">
         <v>68</v>
       </c>
@@ -5729,15 +5738,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="114" customFormat="1">
+    <row r="54" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C54" s="114" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B55" s="129"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="123" t="s">
         <v>71</v>
       </c>
@@ -5754,13 +5763,13 @@
       <c r="L56" s="124"/>
       <c r="M56" s="124"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="126"/>
       <c r="B57" s="132" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B58" s="115" t="s">
         <v>73</v>
       </c>
@@ -5768,7 +5777,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B59" s="115" t="s">
         <v>75</v>
       </c>
@@ -5776,7 +5785,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B60" s="115" t="s">
         <v>77</v>
       </c>
@@ -5784,7 +5793,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B61" s="115" t="s">
         <v>79</v>
       </c>
@@ -5792,7 +5801,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B62" s="115" t="s">
         <v>81</v>
       </c>
@@ -5800,7 +5809,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B63" s="115" t="s">
         <v>83</v>
       </c>
@@ -5808,7 +5817,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:13" s="114" customFormat="1">
+    <row r="64" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B64" s="128" t="s">
         <v>27</v>
       </c>
@@ -5816,10 +5825,10 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L65" s="131"/>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66" s="123" t="s">
         <v>86</v>
       </c>
@@ -5836,13 +5845,13 @@
       <c r="L66" s="124"/>
       <c r="M66" s="124"/>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67" s="126"/>
       <c r="B67" s="132" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B68" s="115" t="s">
         <v>79</v>
       </c>
@@ -5850,7 +5859,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B69" s="115" t="s">
         <v>81</v>
       </c>
@@ -5858,7 +5867,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B70" s="115" t="s">
         <v>83</v>
       </c>
@@ -5866,7 +5875,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:13" s="114" customFormat="1">
+    <row r="71" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B71" s="128" t="s">
         <v>27</v>
       </c>
@@ -5874,7 +5883,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73" s="123" t="s">
         <v>89</v>
       </c>
@@ -5891,13 +5900,13 @@
       <c r="L73" s="124"/>
       <c r="M73" s="124"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74" s="126"/>
       <c r="B74" s="132" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B75" s="115" t="s">
         <v>79</v>
       </c>
@@ -5905,7 +5914,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B76" s="115" t="s">
         <v>81</v>
       </c>
@@ -5913,7 +5922,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B77" s="115" t="s">
         <v>83</v>
       </c>
@@ -5921,7 +5930,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:13" s="114" customFormat="1">
+    <row r="78" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B78" s="128" t="s">
         <v>27</v>
       </c>
@@ -5929,7 +5938,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80" s="123" t="s">
         <v>91</v>
       </c>
@@ -5946,13 +5955,13 @@
       <c r="L80" s="124"/>
       <c r="M80" s="124"/>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81" s="126"/>
       <c r="B81" s="132" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B82" s="115" t="s">
         <v>93</v>
       </c>
@@ -5960,7 +5969,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B83" s="115" t="s">
         <v>95</v>
       </c>
@@ -5968,7 +5977,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B84" s="115" t="s">
         <v>97</v>
       </c>
@@ -5977,7 +5986,7 @@
       </c>
       <c r="D84" s="131"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B85" s="115" t="s">
         <v>99</v>
       </c>
@@ -5985,7 +5994,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B86" s="115" t="s">
         <v>101</v>
       </c>
@@ -5993,7 +6002,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B87" s="115" t="s">
         <v>103</v>
       </c>
@@ -6001,7 +6010,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B88" s="115" t="s">
         <v>105</v>
       </c>
@@ -6009,7 +6018,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B89" s="115" t="s">
         <v>107</v>
       </c>
@@ -6017,7 +6026,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B90" s="115" t="s">
         <v>109</v>
       </c>
@@ -6025,7 +6034,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="91" spans="1:13" s="114" customFormat="1">
+    <row r="91" spans="1:13" s="114" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B91" s="128" t="s">
         <v>27</v>
       </c>
@@ -6033,7 +6042,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93" s="123" t="s">
         <v>111</v>
       </c>
@@ -6050,7 +6059,7 @@
       <c r="L93" s="124"/>
       <c r="M93" s="124"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B94" s="115" t="s">
         <v>112</v>
       </c>
@@ -6058,7 +6067,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B95" s="115" t="s">
         <v>114</v>
       </c>
@@ -6066,7 +6075,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B96" s="115" t="s">
         <v>116</v>
       </c>
@@ -6074,7 +6083,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B97" s="115" t="s">
         <v>118</v>
       </c>
@@ -6082,7 +6091,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B98" s="115" t="s">
         <v>120</v>
       </c>
@@ -6090,7 +6099,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B99" s="115" t="s">
         <v>122</v>
       </c>
@@ -6098,7 +6107,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B100" s="115" t="s">
         <v>124</v>
       </c>
@@ -6106,7 +6115,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B101" s="115" t="s">
         <v>126</v>
       </c>
@@ -6114,10 +6123,10 @@
         <v>127</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C102" s="131"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103" s="123" t="s">
         <v>754</v>
       </c>
@@ -6134,7 +6143,7 @@
       <c r="L103" s="124"/>
       <c r="M103" s="124"/>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B104" s="133" t="s">
         <v>757</v>
       </c>
@@ -6142,7 +6151,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B105" s="133" t="s">
         <v>758</v>
       </c>
@@ -6150,7 +6159,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107" s="123" t="s">
         <v>128</v>
       </c>
@@ -6167,7 +6176,7 @@
       <c r="L107" s="124"/>
       <c r="M107" s="124"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B108" s="115" t="s">
         <v>129</v>
       </c>
@@ -6175,7 +6184,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B109" s="115" t="s">
         <v>351</v>
       </c>
@@ -6198,11 +6207,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:CI258"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.1640625" customWidth="1"/>
     <col min="3" max="3" width="23.1640625" customWidth="1"/>
-    <col min="4" max="4" width="14.9140625" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" customWidth="1"/>
     <col min="6" max="6" width="17.5" style="143" customWidth="1"/>
     <col min="7" max="7" width="17" style="143" customWidth="1"/>
@@ -6224,138 +6233,138 @@
     <col min="84" max="84" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" ht="16" customHeight="1">
-      <c r="A1" s="155" t="s">
+    <row r="1" spans="1:84" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="157" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="157" t="s">
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="159" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="157"/>
-      <c r="H1" s="158"/>
-      <c r="I1" s="156" t="s">
+      <c r="G1" s="159"/>
+      <c r="H1" s="160"/>
+      <c r="I1" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="159"/>
-      <c r="K1" s="158" t="s">
+      <c r="J1" s="161"/>
+      <c r="K1" s="160" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="158"/>
-      <c r="M1" s="158"/>
-      <c r="N1" s="156" t="s">
+      <c r="L1" s="160"/>
+      <c r="M1" s="160"/>
+      <c r="N1" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="160" t="s">
+      <c r="O1" s="158"/>
+      <c r="P1" s="158"/>
+      <c r="Q1" s="162" t="s">
         <v>131</v>
       </c>
-      <c r="R1" s="160"/>
-      <c r="S1" s="156" t="s">
+      <c r="R1" s="162"/>
+      <c r="S1" s="158" t="s">
         <v>55</v>
       </c>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="161" t="s">
+      <c r="T1" s="158"/>
+      <c r="U1" s="158"/>
+      <c r="V1" s="158"/>
+      <c r="W1" s="158"/>
+      <c r="X1" s="158"/>
+      <c r="Y1" s="155" t="s">
         <v>71</v>
       </c>
-      <c r="Z1" s="161"/>
-      <c r="AA1" s="161"/>
-      <c r="AB1" s="161"/>
-      <c r="AC1" s="161"/>
-      <c r="AD1" s="161"/>
-      <c r="AE1" s="161"/>
-      <c r="AF1" s="161"/>
-      <c r="AG1" s="161"/>
-      <c r="AH1" s="161"/>
-      <c r="AI1" s="161"/>
-      <c r="AJ1" s="161"/>
-      <c r="AK1" s="161"/>
-      <c r="AL1" s="161"/>
-      <c r="AM1" s="161"/>
-      <c r="AN1" s="161"/>
-      <c r="AO1" s="161"/>
-      <c r="AP1" s="161"/>
-      <c r="AQ1" s="163" t="s">
+      <c r="Z1" s="155"/>
+      <c r="AA1" s="155"/>
+      <c r="AB1" s="155"/>
+      <c r="AC1" s="155"/>
+      <c r="AD1" s="155"/>
+      <c r="AE1" s="155"/>
+      <c r="AF1" s="155"/>
+      <c r="AG1" s="155"/>
+      <c r="AH1" s="155"/>
+      <c r="AI1" s="155"/>
+      <c r="AJ1" s="155"/>
+      <c r="AK1" s="155"/>
+      <c r="AL1" s="155"/>
+      <c r="AM1" s="155"/>
+      <c r="AN1" s="155"/>
+      <c r="AO1" s="155"/>
+      <c r="AP1" s="155"/>
+      <c r="AQ1" s="156" t="s">
         <v>86</v>
       </c>
-      <c r="AR1" s="163"/>
-      <c r="AS1" s="163"/>
-      <c r="AT1" s="163"/>
-      <c r="AU1" s="163"/>
-      <c r="AV1" s="163"/>
-      <c r="AW1" s="163"/>
-      <c r="AX1" s="163"/>
-      <c r="AY1" s="163"/>
-      <c r="AZ1" s="161" t="s">
+      <c r="AR1" s="156"/>
+      <c r="AS1" s="156"/>
+      <c r="AT1" s="156"/>
+      <c r="AU1" s="156"/>
+      <c r="AV1" s="156"/>
+      <c r="AW1" s="156"/>
+      <c r="AX1" s="156"/>
+      <c r="AY1" s="156"/>
+      <c r="AZ1" s="155" t="s">
         <v>89</v>
       </c>
-      <c r="BA1" s="161"/>
-      <c r="BB1" s="161"/>
-      <c r="BC1" s="161"/>
-      <c r="BD1" s="161"/>
-      <c r="BE1" s="161"/>
-      <c r="BF1" s="161"/>
-      <c r="BG1" s="161"/>
-      <c r="BH1" s="161"/>
-      <c r="BI1" s="162" t="s">
+      <c r="BA1" s="155"/>
+      <c r="BB1" s="155"/>
+      <c r="BC1" s="155"/>
+      <c r="BD1" s="155"/>
+      <c r="BE1" s="155"/>
+      <c r="BF1" s="155"/>
+      <c r="BG1" s="155"/>
+      <c r="BH1" s="155"/>
+      <c r="BI1" s="163" t="s">
         <v>91</v>
       </c>
-      <c r="BJ1" s="162"/>
-      <c r="BK1" s="162"/>
-      <c r="BL1" s="162"/>
-      <c r="BM1" s="162"/>
-      <c r="BN1" s="162"/>
-      <c r="BO1" s="162"/>
-      <c r="BP1" s="162"/>
-      <c r="BQ1" s="162"/>
-      <c r="BR1" s="162"/>
-      <c r="BS1" s="162"/>
-      <c r="BT1" s="162"/>
-      <c r="BU1" s="162"/>
-      <c r="BV1" s="162"/>
-      <c r="BW1" s="162"/>
-      <c r="BX1" s="162"/>
-      <c r="BY1" s="162"/>
-      <c r="BZ1" s="162"/>
-      <c r="CA1" s="162"/>
-      <c r="CB1" s="162"/>
-      <c r="CC1" s="162"/>
-      <c r="CD1" s="162"/>
-      <c r="CE1" s="162"/>
+      <c r="BJ1" s="163"/>
+      <c r="BK1" s="163"/>
+      <c r="BL1" s="163"/>
+      <c r="BM1" s="163"/>
+      <c r="BN1" s="163"/>
+      <c r="BO1" s="163"/>
+      <c r="BP1" s="163"/>
+      <c r="BQ1" s="163"/>
+      <c r="BR1" s="163"/>
+      <c r="BS1" s="163"/>
+      <c r="BT1" s="163"/>
+      <c r="BU1" s="163"/>
+      <c r="BV1" s="163"/>
+      <c r="BW1" s="163"/>
+      <c r="BX1" s="163"/>
+      <c r="BY1" s="163"/>
+      <c r="BZ1" s="163"/>
+      <c r="CA1" s="163"/>
+      <c r="CB1" s="163"/>
+      <c r="CC1" s="163"/>
+      <c r="CD1" s="163"/>
+      <c r="CE1" s="163"/>
     </row>
-    <row r="2" spans="1:84" ht="16" customHeight="1">
-      <c r="A2" s="155"/>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="156"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="158"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="156"/>
-      <c r="O2" s="156"/>
-      <c r="P2" s="156"/>
-      <c r="Q2" s="160"/>
-      <c r="R2" s="160"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="156"/>
-      <c r="U2" s="156"/>
-      <c r="V2" s="156"/>
-      <c r="W2" s="156"/>
-      <c r="X2" s="156"/>
+    <row r="2" spans="1:84" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="157"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="162"/>
+      <c r="R2" s="162"/>
+      <c r="S2" s="158"/>
+      <c r="T2" s="158"/>
+      <c r="U2" s="158"/>
+      <c r="V2" s="158"/>
+      <c r="W2" s="158"/>
+      <c r="X2" s="158"/>
       <c r="Y2" s="154" t="s">
         <v>132</v>
       </c>
@@ -6458,7 +6467,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:84">
+    <row r="3" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -6709,7 +6718,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="4" spans="1:84" hidden="1">
+    <row r="4" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>144</v>
       </c>
@@ -6916,7 +6925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:84" hidden="1">
+    <row r="5" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>154</v>
       </c>
@@ -7117,7 +7126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:84" hidden="1">
+    <row r="6" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>159</v>
       </c>
@@ -7318,7 +7327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:84" hidden="1">
+    <row r="7" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>166</v>
       </c>
@@ -7519,7 +7528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:84" hidden="1">
+    <row r="8" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>171</v>
       </c>
@@ -7769,7 +7778,7 @@
       </c>
       <c r="CF8" s="33"/>
     </row>
-    <row r="9" spans="1:84" hidden="1">
+    <row r="9" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>176</v>
       </c>
@@ -7965,7 +7974,7 @@
       </c>
       <c r="CF9" s="33"/>
     </row>
-    <row r="10" spans="1:84" hidden="1">
+    <row r="10" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>179</v>
       </c>
@@ -8215,7 +8224,7 @@
       </c>
       <c r="CF10" s="33"/>
     </row>
-    <row r="11" spans="1:84" hidden="1">
+    <row r="11" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>183</v>
       </c>
@@ -8417,7 +8426,7 @@
       </c>
       <c r="CF11" s="33"/>
     </row>
-    <row r="12" spans="1:84" hidden="1">
+    <row r="12" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>187</v>
       </c>
@@ -8625,7 +8634,7 @@
       </c>
       <c r="CF12" s="33"/>
     </row>
-    <row r="13" spans="1:84" hidden="1">
+    <row r="13" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>191</v>
       </c>
@@ -8869,7 +8878,7 @@
       </c>
       <c r="CF13" s="33"/>
     </row>
-    <row r="14" spans="1:84" hidden="1">
+    <row r="14" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>195</v>
       </c>
@@ -9071,7 +9080,7 @@
       </c>
       <c r="CF14" s="33"/>
     </row>
-    <row r="15" spans="1:84" hidden="1">
+    <row r="15" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>198</v>
       </c>
@@ -9321,7 +9330,7 @@
       </c>
       <c r="CF15" s="33"/>
     </row>
-    <row r="16" spans="1:84" hidden="1">
+    <row r="16" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>202</v>
       </c>
@@ -9553,7 +9562,7 @@
       </c>
       <c r="CF16" s="33"/>
     </row>
-    <row r="17" spans="1:84" hidden="1">
+    <row r="17" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>208</v>
       </c>
@@ -9725,7 +9734,7 @@
       </c>
       <c r="CF17" s="33"/>
     </row>
-    <row r="18" spans="1:84" hidden="1">
+    <row r="18" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>212</v>
       </c>
@@ -9921,7 +9930,7 @@
       </c>
       <c r="CF18" s="33"/>
     </row>
-    <row r="19" spans="1:84" hidden="1">
+    <row r="19" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>216</v>
       </c>
@@ -10129,7 +10138,7 @@
       </c>
       <c r="CF19" s="33"/>
     </row>
-    <row r="20" spans="1:84" hidden="1">
+    <row r="20" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>220</v>
       </c>
@@ -10301,7 +10310,7 @@
       </c>
       <c r="CF20" s="33"/>
     </row>
-    <row r="21" spans="1:84" hidden="1">
+    <row r="21" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>225</v>
       </c>
@@ -10509,7 +10518,7 @@
       </c>
       <c r="CF21" s="33"/>
     </row>
-    <row r="22" spans="1:84" hidden="1">
+    <row r="22" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>229</v>
       </c>
@@ -10717,7 +10726,7 @@
       </c>
       <c r="CF22" s="33"/>
     </row>
-    <row r="23" spans="1:84" hidden="1">
+    <row r="23" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>233</v>
       </c>
@@ -10889,7 +10898,7 @@
       </c>
       <c r="CF23" s="33"/>
     </row>
-    <row r="24" spans="1:84" hidden="1">
+    <row r="24" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>237</v>
       </c>
@@ -11061,7 +11070,7 @@
       </c>
       <c r="CF24" s="33"/>
     </row>
-    <row r="25" spans="1:84" hidden="1">
+    <row r="25" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>241</v>
       </c>
@@ -11269,7 +11278,7 @@
       </c>
       <c r="CF25" s="33"/>
     </row>
-    <row r="26" spans="1:84" hidden="1">
+    <row r="26" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>245</v>
       </c>
@@ -11471,7 +11480,7 @@
       </c>
       <c r="CF26" s="33"/>
     </row>
-    <row r="27" spans="1:84" hidden="1">
+    <row r="27" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>249</v>
       </c>
@@ -11679,7 +11688,7 @@
       </c>
       <c r="CF27" s="33"/>
     </row>
-    <row r="28" spans="1:84" hidden="1">
+    <row r="28" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>253</v>
       </c>
@@ -11881,7 +11890,7 @@
       </c>
       <c r="CF28" s="33"/>
     </row>
-    <row r="29" spans="1:84" hidden="1">
+    <row r="29" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>257</v>
       </c>
@@ -12053,7 +12062,7 @@
       </c>
       <c r="CF29" s="33"/>
     </row>
-    <row r="30" spans="1:84">
+    <row r="30" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>261</v>
       </c>
@@ -12297,7 +12306,7 @@
       </c>
       <c r="CF30" s="33"/>
     </row>
-    <row r="31" spans="1:84" hidden="1">
+    <row r="31" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>265</v>
       </c>
@@ -12505,7 +12514,7 @@
       </c>
       <c r="CF31" s="33"/>
     </row>
-    <row r="32" spans="1:84" hidden="1">
+    <row r="32" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>269</v>
       </c>
@@ -12735,7 +12744,7 @@
       </c>
       <c r="CF32" s="33"/>
     </row>
-    <row r="33" spans="1:84" hidden="1">
+    <row r="33" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>273</v>
       </c>
@@ -12907,7 +12916,7 @@
       </c>
       <c r="CF33" s="33"/>
     </row>
-    <row r="34" spans="1:84" hidden="1">
+    <row r="34" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>276</v>
       </c>
@@ -13157,7 +13166,7 @@
       </c>
       <c r="CF34" s="33"/>
     </row>
-    <row r="35" spans="1:84" hidden="1">
+    <row r="35" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>279</v>
       </c>
@@ -13389,7 +13398,7 @@
       </c>
       <c r="CF35" s="33"/>
     </row>
-    <row r="36" spans="1:84" hidden="1">
+    <row r="36" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>283</v>
       </c>
@@ -13621,7 +13630,7 @@
       </c>
       <c r="CF36" s="33"/>
     </row>
-    <row r="37" spans="1:84" hidden="1">
+    <row r="37" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>287</v>
       </c>
@@ -13853,7 +13862,7 @@
       </c>
       <c r="CF37" s="33"/>
     </row>
-    <row r="38" spans="1:84" hidden="1">
+    <row r="38" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>290</v>
       </c>
@@ -14085,7 +14094,7 @@
       </c>
       <c r="CF38" s="33"/>
     </row>
-    <row r="39" spans="1:84" hidden="1">
+    <row r="39" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>293</v>
       </c>
@@ -14311,7 +14320,7 @@
       </c>
       <c r="CF39" s="33"/>
     </row>
-    <row r="40" spans="1:84" hidden="1">
+    <row r="40" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>297</v>
       </c>
@@ -14539,7 +14548,7 @@
       </c>
       <c r="CF40" s="33"/>
     </row>
-    <row r="41" spans="1:84" hidden="1">
+    <row r="41" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>301</v>
       </c>
@@ -14765,7 +14774,7 @@
       </c>
       <c r="CF41" s="33"/>
     </row>
-    <row r="42" spans="1:84" hidden="1">
+    <row r="42" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>303</v>
       </c>
@@ -14991,7 +15000,7 @@
       </c>
       <c r="CF42" s="33"/>
     </row>
-    <row r="43" spans="1:84" hidden="1">
+    <row r="43" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>305</v>
       </c>
@@ -15217,7 +15226,7 @@
       </c>
       <c r="CF43" s="33"/>
     </row>
-    <row r="44" spans="1:84" hidden="1">
+    <row r="44" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>308</v>
       </c>
@@ -15445,7 +15454,7 @@
       </c>
       <c r="CF44" s="33"/>
     </row>
-    <row r="45" spans="1:84" hidden="1">
+    <row r="45" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>311</v>
       </c>
@@ -15673,7 +15682,7 @@
       </c>
       <c r="CF45" s="33"/>
     </row>
-    <row r="46" spans="1:84" hidden="1">
+    <row r="46" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>313</v>
       </c>
@@ -15899,7 +15908,7 @@
       </c>
       <c r="CF46" s="33"/>
     </row>
-    <row r="47" spans="1:84" hidden="1">
+    <row r="47" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>316</v>
       </c>
@@ -16131,7 +16140,7 @@
       </c>
       <c r="CF47" s="33"/>
     </row>
-    <row r="48" spans="1:84" hidden="1">
+    <row r="48" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>319</v>
       </c>
@@ -16357,7 +16366,7 @@
       </c>
       <c r="CF48" s="33"/>
     </row>
-    <row r="49" spans="1:84" hidden="1">
+    <row r="49" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>321</v>
       </c>
@@ -16589,7 +16598,7 @@
       </c>
       <c r="CF49" s="33"/>
     </row>
-    <row r="50" spans="1:84" hidden="1">
+    <row r="50" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>323</v>
       </c>
@@ -16821,7 +16830,7 @@
       </c>
       <c r="CF50" s="33"/>
     </row>
-    <row r="51" spans="1:84" hidden="1">
+    <row r="51" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
         <v>325</v>
       </c>
@@ -17053,7 +17062,7 @@
       </c>
       <c r="CF51" s="33"/>
     </row>
-    <row r="52" spans="1:84" hidden="1">
+    <row r="52" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="s">
         <v>327</v>
       </c>
@@ -17281,7 +17290,7 @@
       </c>
       <c r="CF52" s="33"/>
     </row>
-    <row r="53" spans="1:84" hidden="1">
+    <row r="53" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="7" t="s">
         <v>330</v>
       </c>
@@ -17507,7 +17516,7 @@
       </c>
       <c r="CF53" s="33"/>
     </row>
-    <row r="54" spans="1:84">
+    <row r="54" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
         <v>333</v>
       </c>
@@ -17751,7 +17760,7 @@
       </c>
       <c r="CF54" s="33"/>
     </row>
-    <row r="55" spans="1:84" hidden="1">
+    <row r="55" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
         <v>335</v>
       </c>
@@ -17929,7 +17938,7 @@
       </c>
       <c r="CF55" s="33"/>
     </row>
-    <row r="56" spans="1:84" hidden="1">
+    <row r="56" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
         <v>338</v>
       </c>
@@ -18161,7 +18170,7 @@
       </c>
       <c r="CF56" s="33"/>
     </row>
-    <row r="57" spans="1:84" hidden="1">
+    <row r="57" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
         <v>342</v>
       </c>
@@ -18393,7 +18402,7 @@
       </c>
       <c r="CF57" s="33"/>
     </row>
-    <row r="58" spans="1:84" hidden="1">
+    <row r="58" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
         <v>344</v>
       </c>
@@ -18625,7 +18634,7 @@
       </c>
       <c r="CF58" s="33"/>
     </row>
-    <row r="59" spans="1:84" hidden="1">
+    <row r="59" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
         <v>346</v>
       </c>
@@ -18857,7 +18866,7 @@
       </c>
       <c r="CF59" s="33"/>
     </row>
-    <row r="60" spans="1:84" hidden="1">
+    <row r="60" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
         <v>349</v>
       </c>
@@ -18993,7 +19002,7 @@
       </c>
       <c r="CF60" s="33"/>
     </row>
-    <row r="61" spans="1:84" hidden="1">
+    <row r="61" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
         <v>352</v>
       </c>
@@ -19129,7 +19138,7 @@
       </c>
       <c r="CF61" s="33"/>
     </row>
-    <row r="62" spans="1:84" hidden="1">
+    <row r="62" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
         <v>354</v>
       </c>
@@ -19265,7 +19274,7 @@
       </c>
       <c r="CF62" s="33"/>
     </row>
-    <row r="63" spans="1:84" hidden="1">
+    <row r="63" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
         <v>357</v>
       </c>
@@ -19401,7 +19410,7 @@
       </c>
       <c r="CF63" s="33"/>
     </row>
-    <row r="64" spans="1:84" hidden="1">
+    <row r="64" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
         <v>360</v>
       </c>
@@ -19537,7 +19546,7 @@
       </c>
       <c r="CF64" s="33"/>
     </row>
-    <row r="65" spans="1:84" hidden="1">
+    <row r="65" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
         <v>362</v>
       </c>
@@ -19673,7 +19682,7 @@
       </c>
       <c r="CF65" s="33"/>
     </row>
-    <row r="66" spans="1:84" hidden="1">
+    <row r="66" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
         <v>364</v>
       </c>
@@ -19809,7 +19818,7 @@
       </c>
       <c r="CF66" s="33"/>
     </row>
-    <row r="67" spans="1:84" hidden="1">
+    <row r="67" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
         <v>367</v>
       </c>
@@ -19945,7 +19954,7 @@
       </c>
       <c r="CF67" s="33"/>
     </row>
-    <row r="68" spans="1:84" hidden="1">
+    <row r="68" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
         <v>370</v>
       </c>
@@ -20081,7 +20090,7 @@
       </c>
       <c r="CF68" s="33"/>
     </row>
-    <row r="69" spans="1:84" hidden="1">
+    <row r="69" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
         <v>372</v>
       </c>
@@ -20215,7 +20224,7 @@
       </c>
       <c r="CF69" s="33"/>
     </row>
-    <row r="70" spans="1:84" hidden="1">
+    <row r="70" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
         <v>376</v>
       </c>
@@ -20349,7 +20358,7 @@
       </c>
       <c r="CF70" s="33"/>
     </row>
-    <row r="71" spans="1:84">
+    <row r="71" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
         <v>378</v>
       </c>
@@ -20485,7 +20494,7 @@
       </c>
       <c r="CF71" s="33"/>
     </row>
-    <row r="72" spans="1:84" hidden="1">
+    <row r="72" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
         <v>380</v>
       </c>
@@ -20619,7 +20628,7 @@
       </c>
       <c r="CF72" s="33"/>
     </row>
-    <row r="73" spans="1:84" hidden="1">
+    <row r="73" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
         <v>382</v>
       </c>
@@ -20753,7 +20762,7 @@
       </c>
       <c r="CF73" s="33"/>
     </row>
-    <row r="74" spans="1:84">
+    <row r="74" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
         <v>384</v>
       </c>
@@ -20889,7 +20898,7 @@
       </c>
       <c r="CF74" s="33"/>
     </row>
-    <row r="75" spans="1:84">
+    <row r="75" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
         <v>386</v>
       </c>
@@ -21025,7 +21034,7 @@
       </c>
       <c r="CF75" s="33"/>
     </row>
-    <row r="76" spans="1:84">
+    <row r="76" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
         <v>388</v>
       </c>
@@ -21161,7 +21170,7 @@
       </c>
       <c r="CF76" s="33"/>
     </row>
-    <row r="77" spans="1:84">
+    <row r="77" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
         <v>390</v>
       </c>
@@ -21297,7 +21306,7 @@
       </c>
       <c r="CF77" s="33"/>
     </row>
-    <row r="78" spans="1:84">
+    <row r="78" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
         <v>392</v>
       </c>
@@ -21433,7 +21442,7 @@
       </c>
       <c r="CF78" s="33"/>
     </row>
-    <row r="79" spans="1:84" hidden="1">
+    <row r="79" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
         <v>394</v>
       </c>
@@ -21567,7 +21576,7 @@
       </c>
       <c r="CF79" s="33"/>
     </row>
-    <row r="80" spans="1:84">
+    <row r="80" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
         <v>396</v>
       </c>
@@ -21703,7 +21712,7 @@
       </c>
       <c r="CF80" s="33"/>
     </row>
-    <row r="81" spans="1:84">
+    <row r="81" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
         <v>398</v>
       </c>
@@ -21839,7 +21848,7 @@
       </c>
       <c r="CF81" s="33"/>
     </row>
-    <row r="82" spans="1:84">
+    <row r="82" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
         <v>400</v>
       </c>
@@ -21975,7 +21984,7 @@
       </c>
       <c r="CF82" s="33"/>
     </row>
-    <row r="83" spans="1:84" hidden="1">
+    <row r="83" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
         <v>402</v>
       </c>
@@ -22109,7 +22118,7 @@
       </c>
       <c r="CF83" s="33"/>
     </row>
-    <row r="84" spans="1:84" hidden="1">
+    <row r="84" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
         <v>404</v>
       </c>
@@ -22245,7 +22254,7 @@
       </c>
       <c r="CF84" s="33"/>
     </row>
-    <row r="85" spans="1:84">
+    <row r="85" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
         <v>407</v>
       </c>
@@ -22381,7 +22390,7 @@
       </c>
       <c r="CF85" s="33"/>
     </row>
-    <row r="86" spans="1:84" hidden="1">
+    <row r="86" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
         <v>410</v>
       </c>
@@ -22515,7 +22524,7 @@
       </c>
       <c r="CF86" s="33"/>
     </row>
-    <row r="87" spans="1:84" hidden="1">
+    <row r="87" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
         <v>413</v>
       </c>
@@ -22649,7 +22658,7 @@
       </c>
       <c r="CF87" s="33"/>
     </row>
-    <row r="88" spans="1:84" hidden="1">
+    <row r="88" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
         <v>416</v>
       </c>
@@ -22785,7 +22794,7 @@
       </c>
       <c r="CF88" s="33"/>
     </row>
-    <row r="89" spans="1:84" hidden="1">
+    <row r="89" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
         <v>420</v>
       </c>
@@ -22921,7 +22930,7 @@
       </c>
       <c r="CF89" s="33"/>
     </row>
-    <row r="90" spans="1:84" hidden="1">
+    <row r="90" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
         <v>424</v>
       </c>
@@ -23057,7 +23066,7 @@
       </c>
       <c r="CF90" s="33"/>
     </row>
-    <row r="91" spans="1:84" hidden="1">
+    <row r="91" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
         <v>426</v>
       </c>
@@ -23193,7 +23202,7 @@
       </c>
       <c r="CF91" s="33"/>
     </row>
-    <row r="92" spans="1:84" hidden="1">
+    <row r="92" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
         <v>428</v>
       </c>
@@ -23329,7 +23338,7 @@
       </c>
       <c r="CF92" s="33"/>
     </row>
-    <row r="93" spans="1:84" hidden="1">
+    <row r="93" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
         <v>431</v>
       </c>
@@ -23465,7 +23474,7 @@
       </c>
       <c r="CF93" s="33"/>
     </row>
-    <row r="94" spans="1:84" hidden="1">
+    <row r="94" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
         <v>434</v>
       </c>
@@ -23601,7 +23610,7 @@
       </c>
       <c r="CF94" s="33"/>
     </row>
-    <row r="95" spans="1:84" hidden="1">
+    <row r="95" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
         <v>437</v>
       </c>
@@ -23737,7 +23746,7 @@
       </c>
       <c r="CF95" s="33"/>
     </row>
-    <row r="96" spans="1:84" hidden="1">
+    <row r="96" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
         <v>441</v>
       </c>
@@ -23873,7 +23882,7 @@
       </c>
       <c r="CF96" s="33"/>
     </row>
-    <row r="97" spans="1:84" hidden="1">
+    <row r="97" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
         <v>443</v>
       </c>
@@ -24009,7 +24018,7 @@
       </c>
       <c r="CF97" s="33"/>
     </row>
-    <row r="98" spans="1:84" hidden="1">
+    <row r="98" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
         <v>445</v>
       </c>
@@ -24145,7 +24154,7 @@
       </c>
       <c r="CF98" s="33"/>
     </row>
-    <row r="99" spans="1:84" hidden="1">
+    <row r="99" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
         <v>447</v>
       </c>
@@ -24281,7 +24290,7 @@
       </c>
       <c r="CF99" s="33"/>
     </row>
-    <row r="100" spans="1:84" hidden="1">
+    <row r="100" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
         <v>449</v>
       </c>
@@ -24417,7 +24426,7 @@
       </c>
       <c r="CF100" s="33"/>
     </row>
-    <row r="101" spans="1:84" hidden="1">
+    <row r="101" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
         <v>452</v>
       </c>
@@ -24553,7 +24562,7 @@
       </c>
       <c r="CF101" s="33"/>
     </row>
-    <row r="102" spans="1:84" hidden="1">
+    <row r="102" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
         <v>455</v>
       </c>
@@ -24689,7 +24698,7 @@
       </c>
       <c r="CF102" s="33"/>
     </row>
-    <row r="103" spans="1:84" hidden="1">
+    <row r="103" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
         <v>458</v>
       </c>
@@ -24825,7 +24834,7 @@
       </c>
       <c r="CF103" s="33"/>
     </row>
-    <row r="104" spans="1:84" hidden="1">
+    <row r="104" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
         <v>461</v>
       </c>
@@ -24961,7 +24970,7 @@
       </c>
       <c r="CF104" s="33"/>
     </row>
-    <row r="105" spans="1:84" hidden="1">
+    <row r="105" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
         <v>465</v>
       </c>
@@ -25100,7 +25109,7 @@
       </c>
       <c r="CF105" s="33"/>
     </row>
-    <row r="106" spans="1:84" hidden="1">
+    <row r="106" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
         <v>468</v>
       </c>
@@ -25239,7 +25248,7 @@
       </c>
       <c r="CF106" s="33"/>
     </row>
-    <row r="107" spans="1:84" hidden="1">
+    <row r="107" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
         <v>470</v>
       </c>
@@ -25378,7 +25387,7 @@
       </c>
       <c r="CF107" s="33"/>
     </row>
-    <row r="108" spans="1:84" hidden="1">
+    <row r="108" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
         <v>472</v>
       </c>
@@ -25517,7 +25526,7 @@
       </c>
       <c r="CF108" s="33"/>
     </row>
-    <row r="109" spans="1:84" hidden="1">
+    <row r="109" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
         <v>474</v>
       </c>
@@ -25656,7 +25665,7 @@
       </c>
       <c r="CF109" s="33"/>
     </row>
-    <row r="110" spans="1:84" hidden="1">
+    <row r="110" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
         <v>477</v>
       </c>
@@ -25795,7 +25804,7 @@
       </c>
       <c r="CF110" s="33"/>
     </row>
-    <row r="111" spans="1:84" hidden="1">
+    <row r="111" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
         <v>480</v>
       </c>
@@ -25934,7 +25943,7 @@
       </c>
       <c r="CF111" s="33"/>
     </row>
-    <row r="112" spans="1:84" hidden="1">
+    <row r="112" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
         <v>482</v>
       </c>
@@ -26073,7 +26082,7 @@
       </c>
       <c r="CF112" s="33"/>
     </row>
-    <row r="113" spans="1:84" hidden="1">
+    <row r="113" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
         <v>484</v>
       </c>
@@ -26212,7 +26221,7 @@
       </c>
       <c r="CF113" s="33"/>
     </row>
-    <row r="114" spans="1:84" hidden="1">
+    <row r="114" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
         <v>486</v>
       </c>
@@ -26351,7 +26360,7 @@
       </c>
       <c r="CF114" s="33"/>
     </row>
-    <row r="115" spans="1:84" hidden="1">
+    <row r="115" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
         <v>488</v>
       </c>
@@ -26490,7 +26499,7 @@
       </c>
       <c r="CF115" s="33"/>
     </row>
-    <row r="116" spans="1:84" hidden="1">
+    <row r="116" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
         <v>490</v>
       </c>
@@ -26629,7 +26638,7 @@
       </c>
       <c r="CF116" s="33"/>
     </row>
-    <row r="117" spans="1:84" hidden="1">
+    <row r="117" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
         <v>492</v>
       </c>
@@ -26768,7 +26777,7 @@
       </c>
       <c r="CF117" s="33"/>
     </row>
-    <row r="118" spans="1:84" hidden="1">
+    <row r="118" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
         <v>494</v>
       </c>
@@ -26907,7 +26916,7 @@
       </c>
       <c r="CF118" s="33"/>
     </row>
-    <row r="119" spans="1:84" hidden="1">
+    <row r="119" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
         <v>496</v>
       </c>
@@ -27046,7 +27055,7 @@
       </c>
       <c r="CF119" s="33"/>
     </row>
-    <row r="120" spans="1:84" hidden="1">
+    <row r="120" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
         <v>498</v>
       </c>
@@ -27185,7 +27194,7 @@
       </c>
       <c r="CF120" s="33"/>
     </row>
-    <row r="121" spans="1:84" hidden="1">
+    <row r="121" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
         <v>500</v>
       </c>
@@ -27324,7 +27333,7 @@
       </c>
       <c r="CF121" s="33"/>
     </row>
-    <row r="122" spans="1:84" hidden="1">
+    <row r="122" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6" t="s">
         <v>503</v>
       </c>
@@ -27463,7 +27472,7 @@
       </c>
       <c r="CF122" s="33"/>
     </row>
-    <row r="123" spans="1:84" hidden="1">
+    <row r="123" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
         <v>505</v>
       </c>
@@ -27602,7 +27611,7 @@
       </c>
       <c r="CF123" s="33"/>
     </row>
-    <row r="124" spans="1:84" hidden="1">
+    <row r="124" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6" t="s">
         <v>507</v>
       </c>
@@ -27741,7 +27750,7 @@
       </c>
       <c r="CF124" s="33"/>
     </row>
-    <row r="125" spans="1:84" hidden="1">
+    <row r="125" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
         <v>509</v>
       </c>
@@ -27880,7 +27889,7 @@
       </c>
       <c r="CF125" s="33"/>
     </row>
-    <row r="126" spans="1:84" hidden="1">
+    <row r="126" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
         <v>511</v>
       </c>
@@ -28019,7 +28028,7 @@
       </c>
       <c r="CF126" s="33"/>
     </row>
-    <row r="127" spans="1:84" hidden="1">
+    <row r="127" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
         <v>513</v>
       </c>
@@ -28158,7 +28167,7 @@
       </c>
       <c r="CF127" s="33"/>
     </row>
-    <row r="128" spans="1:84" hidden="1">
+    <row r="128" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
         <v>515</v>
       </c>
@@ -28297,7 +28306,7 @@
       </c>
       <c r="CF128" s="33"/>
     </row>
-    <row r="129" spans="1:84" hidden="1">
+    <row r="129" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="53" t="s">
         <v>517</v>
       </c>
@@ -28469,7 +28478,7 @@
       </c>
       <c r="CF129" s="18"/>
     </row>
-    <row r="130" spans="1:84" hidden="1">
+    <row r="130" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="53" t="s">
         <v>521</v>
       </c>
@@ -28640,7 +28649,7 @@
       </c>
       <c r="CF130" s="18"/>
     </row>
-    <row r="131" spans="1:84" hidden="1">
+    <row r="131" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="53" t="s">
         <v>523</v>
       </c>
@@ -28824,7 +28833,7 @@
       </c>
       <c r="CF131" s="18"/>
     </row>
-    <row r="132" spans="1:84" hidden="1">
+    <row r="132" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="53" t="s">
         <v>527</v>
       </c>
@@ -29014,7 +29023,7 @@
       </c>
       <c r="CF132" s="18"/>
     </row>
-    <row r="133" spans="1:84" hidden="1">
+    <row r="133" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="53" t="s">
         <v>530</v>
       </c>
@@ -29198,7 +29207,7 @@
       </c>
       <c r="CF133" s="18"/>
     </row>
-    <row r="134" spans="1:84" hidden="1">
+    <row r="134" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="53" t="s">
         <v>532</v>
       </c>
@@ -29364,7 +29373,7 @@
       </c>
       <c r="CF134" s="18"/>
     </row>
-    <row r="135" spans="1:84" hidden="1">
+    <row r="135" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="53" t="s">
         <v>534</v>
       </c>
@@ -29536,7 +29545,7 @@
       </c>
       <c r="CF135" s="18"/>
     </row>
-    <row r="136" spans="1:84">
+    <row r="136" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="53" t="s">
         <v>536</v>
       </c>
@@ -29784,7 +29793,7 @@
       </c>
       <c r="CF136" s="18"/>
     </row>
-    <row r="137" spans="1:84" hidden="1">
+    <row r="137" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="53" t="s">
         <v>539</v>
       </c>
@@ -29956,7 +29965,7 @@
       </c>
       <c r="CF137" s="18"/>
     </row>
-    <row r="138" spans="1:84" hidden="1">
+    <row r="138" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="53" t="s">
         <v>541</v>
       </c>
@@ -30142,7 +30151,7 @@
       </c>
       <c r="CF138" s="18"/>
     </row>
-    <row r="139" spans="1:84" hidden="1">
+    <row r="139" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="53" t="s">
         <v>543</v>
       </c>
@@ -30314,7 +30323,7 @@
       </c>
       <c r="CF139" s="18"/>
     </row>
-    <row r="140" spans="1:84" hidden="1">
+    <row r="140" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="53" t="s">
         <v>545</v>
       </c>
@@ -30486,7 +30495,7 @@
       </c>
       <c r="CF140" s="18"/>
     </row>
-    <row r="141" spans="1:84" hidden="1">
+    <row r="141" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="53" t="s">
         <v>548</v>
       </c>
@@ -30682,7 +30691,7 @@
       </c>
       <c r="CF141" s="18"/>
     </row>
-    <row r="142" spans="1:84" s="1" customFormat="1" hidden="1">
+    <row r="142" spans="1:84" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="55" t="s">
         <v>550</v>
       </c>
@@ -30883,7 +30892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:84">
+    <row r="143" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="53" t="s">
         <v>552</v>
       </c>
@@ -31133,7 +31142,7 @@
       </c>
       <c r="CF143" s="18"/>
     </row>
-    <row r="144" spans="1:84" hidden="1">
+    <row r="144" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="53" t="s">
         <v>554</v>
       </c>
@@ -31303,7 +31312,7 @@
       </c>
       <c r="CF144" s="18"/>
     </row>
-    <row r="145" spans="1:84" hidden="1">
+    <row r="145" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="53" t="s">
         <v>556</v>
       </c>
@@ -31509,7 +31518,7 @@
       </c>
       <c r="CF145" s="18"/>
     </row>
-    <row r="146" spans="1:84" hidden="1">
+    <row r="146" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="53" t="s">
         <v>558</v>
       </c>
@@ -31713,7 +31722,7 @@
       </c>
       <c r="CF146" s="18"/>
     </row>
-    <row r="147" spans="1:84" hidden="1">
+    <row r="147" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="53" t="s">
         <v>560</v>
       </c>
@@ -31895,7 +31904,7 @@
       </c>
       <c r="CF147" s="18"/>
     </row>
-    <row r="148" spans="1:84" hidden="1">
+    <row r="148" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="53" t="s">
         <v>562</v>
       </c>
@@ -32083,7 +32092,7 @@
       </c>
       <c r="CF148" s="18"/>
     </row>
-    <row r="149" spans="1:84" hidden="1">
+    <row r="149" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="53" t="s">
         <v>564</v>
       </c>
@@ -32277,7 +32286,7 @@
       </c>
       <c r="CF149" s="18"/>
     </row>
-    <row r="150" spans="1:84" hidden="1">
+    <row r="150" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="53" t="s">
         <v>566</v>
       </c>
@@ -32477,7 +32486,7 @@
       </c>
       <c r="CF150" s="18"/>
     </row>
-    <row r="151" spans="1:84" hidden="1">
+    <row r="151" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="53" t="s">
         <v>568</v>
       </c>
@@ -32723,7 +32732,7 @@
       </c>
       <c r="CF151" s="18"/>
     </row>
-    <row r="152" spans="1:84" hidden="1">
+    <row r="152" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="53" t="s">
         <v>570</v>
       </c>
@@ -32929,7 +32938,7 @@
       </c>
       <c r="CF152" s="18"/>
     </row>
-    <row r="153" spans="1:84">
+    <row r="153" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="53" t="s">
         <v>572</v>
       </c>
@@ -33171,7 +33180,7 @@
       </c>
       <c r="CF153" s="18"/>
     </row>
-    <row r="154" spans="1:84" hidden="1">
+    <row r="154" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="53" t="s">
         <v>574</v>
       </c>
@@ -33341,7 +33350,7 @@
       </c>
       <c r="CF154" s="18"/>
     </row>
-    <row r="155" spans="1:84" hidden="1">
+    <row r="155" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="53" t="s">
         <v>576</v>
       </c>
@@ -33541,7 +33550,7 @@
       </c>
       <c r="CF155" s="18"/>
     </row>
-    <row r="156" spans="1:84">
+    <row r="156" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A156" s="53" t="s">
         <v>578</v>
       </c>
@@ -33783,7 +33792,7 @@
       </c>
       <c r="CF156" s="18"/>
     </row>
-    <row r="157" spans="1:84" hidden="1">
+    <row r="157" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="54" t="s">
         <v>580</v>
       </c>
@@ -33947,7 +33956,7 @@
       <c r="CE157" s="61"/>
       <c r="CF157" s="18"/>
     </row>
-    <row r="158" spans="1:84" hidden="1">
+    <row r="158" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="54" t="s">
         <v>583</v>
       </c>
@@ -34071,7 +34080,7 @@
       <c r="CE158" s="61"/>
       <c r="CF158" s="18"/>
     </row>
-    <row r="159" spans="1:84">
+    <row r="159" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A159" s="54" t="s">
         <v>584</v>
       </c>
@@ -34197,7 +34206,7 @@
       <c r="CE159" s="61"/>
       <c r="CF159" s="18"/>
     </row>
-    <row r="160" spans="1:84">
+    <row r="160" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="54" t="s">
         <v>586</v>
       </c>
@@ -34323,14 +34332,14 @@
       <c r="CE160" s="61"/>
       <c r="CF160" s="18"/>
     </row>
-    <row r="161" spans="1:84">
-      <c r="A161" s="54" t="s">
+    <row r="161" spans="1:84" x14ac:dyDescent="0.2">
+      <c r="A161" s="165" t="s">
         <v>588</v>
       </c>
       <c r="B161" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="C161" s="53" t="s">
+      <c r="C161" s="164" t="s">
         <v>582</v>
       </c>
       <c r="D161" s="54" t="s">
@@ -34449,7 +34458,7 @@
       <c r="CE161" s="61"/>
       <c r="CF161" s="18"/>
     </row>
-    <row r="162" spans="1:84">
+    <row r="162" spans="1:84" x14ac:dyDescent="0.2">
       <c r="A162" s="54" t="s">
         <v>590</v>
       </c>
@@ -34575,7 +34584,7 @@
       <c r="CE162" s="61"/>
       <c r="CF162" s="18"/>
     </row>
-    <row r="163" spans="1:84" hidden="1">
+    <row r="163" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="54" t="s">
         <v>592</v>
       </c>
@@ -34699,7 +34708,7 @@
       <c r="CE163" s="61"/>
       <c r="CF163" s="18"/>
     </row>
-    <row r="164" spans="1:84" hidden="1">
+    <row r="164" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="54" t="s">
         <v>594</v>
       </c>
@@ -34823,7 +34832,7 @@
       <c r="CE164" s="61"/>
       <c r="CF164" s="18"/>
     </row>
-    <row r="165" spans="1:84" hidden="1">
+    <row r="165" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="53" t="s">
         <v>596</v>
       </c>
@@ -35048,7 +35057,7 @@
       </c>
       <c r="CF165" s="18"/>
     </row>
-    <row r="166" spans="1:84" hidden="1">
+    <row r="166" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="53" t="s">
         <v>598</v>
       </c>
@@ -35224,7 +35233,7 @@
       <c r="CC166" s="80"/>
       <c r="CF166" s="18"/>
     </row>
-    <row r="167" spans="1:84" hidden="1">
+    <row r="167" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="53" t="s">
         <v>600</v>
       </c>
@@ -35466,7 +35475,7 @@
       </c>
       <c r="CF167" s="18"/>
     </row>
-    <row r="168" spans="1:84" hidden="1">
+    <row r="168" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="53" t="s">
         <v>602</v>
       </c>
@@ -35644,7 +35653,7 @@
       </c>
       <c r="CF168" s="18"/>
     </row>
-    <row r="169" spans="1:84" hidden="1">
+    <row r="169" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="53" t="s">
         <v>604</v>
       </c>
@@ -35830,7 +35839,7 @@
       </c>
       <c r="CF169" s="18"/>
     </row>
-    <row r="170" spans="1:84" hidden="1">
+    <row r="170" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="53" t="s">
         <v>606</v>
       </c>
@@ -36024,7 +36033,7 @@
       </c>
       <c r="CF170" s="18"/>
     </row>
-    <row r="171" spans="1:84" hidden="1">
+    <row r="171" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="53" t="s">
         <v>608</v>
       </c>
@@ -36206,7 +36215,7 @@
       </c>
       <c r="CF171" s="18"/>
     </row>
-    <row r="172" spans="1:84" hidden="1">
+    <row r="172" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="53" t="s">
         <v>610</v>
       </c>
@@ -36406,7 +36415,7 @@
       </c>
       <c r="CF172" s="18"/>
     </row>
-    <row r="173" spans="1:84" hidden="1">
+    <row r="173" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="53" t="s">
         <v>612</v>
       </c>
@@ -36576,7 +36585,7 @@
       </c>
       <c r="CF173" s="18"/>
     </row>
-    <row r="174" spans="1:84" hidden="1">
+    <row r="174" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="53" t="s">
         <v>614</v>
       </c>
@@ -36782,7 +36791,7 @@
       </c>
       <c r="CF174" s="18"/>
     </row>
-    <row r="175" spans="1:84" hidden="1">
+    <row r="175" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="53" t="s">
         <v>616</v>
       </c>
@@ -36988,7 +36997,7 @@
       </c>
       <c r="CF175" s="18"/>
     </row>
-    <row r="176" spans="1:84" hidden="1">
+    <row r="176" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="53" t="s">
         <v>618</v>
       </c>
@@ -37176,7 +37185,7 @@
       </c>
       <c r="CF176" s="18"/>
     </row>
-    <row r="177" spans="1:87" hidden="1">
+    <row r="177" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="53" t="s">
         <v>620</v>
       </c>
@@ -37382,7 +37391,7 @@
       </c>
       <c r="CF177" s="18"/>
     </row>
-    <row r="178" spans="1:87" hidden="1">
+    <row r="178" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="53" t="s">
         <v>622</v>
       </c>
@@ -37554,7 +37563,7 @@
       </c>
       <c r="CF178" s="18"/>
     </row>
-    <row r="179" spans="1:87" hidden="1">
+    <row r="179" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="53" t="s">
         <v>625</v>
       </c>
@@ -37724,7 +37733,7 @@
       </c>
       <c r="CF179" s="18"/>
     </row>
-    <row r="180" spans="1:87" hidden="1">
+    <row r="180" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="53" t="s">
         <v>627</v>
       </c>
@@ -37894,7 +37903,7 @@
       </c>
       <c r="CF180" s="18"/>
     </row>
-    <row r="181" spans="1:87" hidden="1">
+    <row r="181" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="53" t="s">
         <v>629</v>
       </c>
@@ -38064,7 +38073,7 @@
       </c>
       <c r="CF181" s="18"/>
     </row>
-    <row r="182" spans="1:87" hidden="1">
+    <row r="182" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="53" t="s">
         <v>631</v>
       </c>
@@ -38234,7 +38243,7 @@
       </c>
       <c r="CF182" s="18"/>
     </row>
-    <row r="183" spans="1:87" hidden="1">
+    <row r="183" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="53" t="s">
         <v>633</v>
       </c>
@@ -38404,7 +38413,7 @@
       </c>
       <c r="CF183" s="18"/>
     </row>
-    <row r="184" spans="1:87" hidden="1">
+    <row r="184" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="53" t="s">
         <v>635</v>
       </c>
@@ -38574,7 +38583,7 @@
       </c>
       <c r="CF184" s="18"/>
     </row>
-    <row r="185" spans="1:87" hidden="1">
+    <row r="185" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="53" t="s">
         <v>637</v>
       </c>
@@ -38741,7 +38750,7 @@
       <c r="CD185" s="80"/>
       <c r="CE185" s="61"/>
     </row>
-    <row r="186" spans="1:87" hidden="1">
+    <row r="186" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="53" t="s">
         <v>641</v>
       </c>
@@ -38906,7 +38915,7 @@
       <c r="CD186" s="80"/>
       <c r="CE186" s="61"/>
     </row>
-    <row r="187" spans="1:87" hidden="1">
+    <row r="187" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="53" t="s">
         <v>645</v>
       </c>
@@ -39071,7 +39080,7 @@
       <c r="CD187" s="80"/>
       <c r="CE187" s="61"/>
     </row>
-    <row r="188" spans="1:87" hidden="1">
+    <row r="188" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="53" t="s">
         <v>648</v>
       </c>
@@ -39296,7 +39305,7 @@
         <v>756647</v>
       </c>
     </row>
-    <row r="189" spans="1:87" hidden="1">
+    <row r="189" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="53" t="s">
         <v>652</v>
       </c>
@@ -39485,7 +39494,7 @@
       <c r="CH189" s="81"/>
       <c r="CI189" s="81"/>
     </row>
-    <row r="190" spans="1:87" hidden="1">
+    <row r="190" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="53" t="s">
         <v>655</v>
       </c>
@@ -39667,7 +39676,7 @@
       <c r="CE190" s="61"/>
       <c r="CF190" s="33"/>
     </row>
-    <row r="191" spans="1:87" hidden="1">
+    <row r="191" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="53" t="s">
         <v>659</v>
       </c>
@@ -39887,7 +39896,7 @@
       </c>
       <c r="CF191" s="33"/>
     </row>
-    <row r="192" spans="1:87" hidden="1">
+    <row r="192" spans="1:87" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="53" t="s">
         <v>661</v>
       </c>
@@ -40116,7 +40125,7 @@
         <v>217800</v>
       </c>
     </row>
-    <row r="193" spans="1:84" hidden="1">
+    <row r="193" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="53" t="s">
         <v>664</v>
       </c>
@@ -40345,7 +40354,7 @@
         <v>95509712</v>
       </c>
     </row>
-    <row r="194" spans="1:84" s="2" customFormat="1" hidden="1">
+    <row r="194" spans="1:84" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="53" t="s">
         <v>667</v>
       </c>
@@ -40552,7 +40561,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="195" spans="1:84" s="2" customFormat="1" hidden="1">
+    <row r="195" spans="1:84" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="53" t="s">
         <v>671</v>
       </c>
@@ -40771,7 +40780,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="196" spans="1:84" s="2" customFormat="1" hidden="1">
+    <row r="196" spans="1:84" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="53" t="s">
         <v>676</v>
       </c>
@@ -40990,7 +40999,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="197" spans="1:84" s="2" customFormat="1" hidden="1">
+    <row r="197" spans="1:84" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="53" t="s">
         <v>681</v>
       </c>
@@ -41158,7 +41167,7 @@
       <c r="CE197" s="61"/>
       <c r="CF197" s="111"/>
     </row>
-    <row r="198" spans="1:84" hidden="1">
+    <row r="198" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="53" t="s">
         <v>685</v>
       </c>
@@ -41384,7 +41393,7 @@
       </c>
       <c r="CF198" s="33"/>
     </row>
-    <row r="199" spans="1:84" hidden="1">
+    <row r="199" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="53" t="s">
         <v>688</v>
       </c>
@@ -41610,7 +41619,7 @@
       </c>
       <c r="CF199" s="33"/>
     </row>
-    <row r="200" spans="1:84" hidden="1">
+    <row r="200" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="53" t="s">
         <v>691</v>
       </c>
@@ -41794,7 +41803,7 @@
       </c>
       <c r="CF200" s="33"/>
     </row>
-    <row r="201" spans="1:84" hidden="1">
+    <row r="201" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="53" t="s">
         <v>694</v>
       </c>
@@ -41960,7 +41969,7 @@
       <c r="CE201" s="61"/>
       <c r="CF201" s="33"/>
     </row>
-    <row r="202" spans="1:84" hidden="1">
+    <row r="202" spans="1:84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>698</v>
       </c>
@@ -42207,7 +42216,7 @@
         <v>174816.3</v>
       </c>
     </row>
-    <row r="203" spans="1:84" s="3" customFormat="1" hidden="1">
+    <row r="203" spans="1:84" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>706</v>
       </c>
@@ -42459,7 +42468,7 @@
       </c>
       <c r="CF203" s="112"/>
     </row>
-    <row r="204" spans="1:84" s="3" customFormat="1" hidden="1">
+    <row r="204" spans="1:84" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>710</v>
       </c>
@@ -42711,7 +42720,7 @@
       </c>
       <c r="CF204" s="112"/>
     </row>
-    <row r="205" spans="1:84" s="3" customFormat="1" hidden="1">
+    <row r="205" spans="1:84" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>713</v>
       </c>
@@ -42961,7 +42970,7 @@
       </c>
       <c r="CF205" s="112"/>
     </row>
-    <row r="206" spans="1:84" s="3" customFormat="1" hidden="1">
+    <row r="206" spans="1:84" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>716</v>
       </c>
@@ -43213,7 +43222,7 @@
       </c>
       <c r="CF206" s="112"/>
     </row>
-    <row r="207" spans="1:84">
+    <row r="207" spans="1:84" x14ac:dyDescent="0.2">
       <c r="S207" s="25"/>
       <c r="AK207" s="108"/>
       <c r="AN207" s="7"/>
@@ -43243,7 +43252,7 @@
       <c r="CD207" s="80"/>
       <c r="CE207" s="61"/>
     </row>
-    <row r="208" spans="1:84" s="4" customFormat="1">
+    <row r="208" spans="1:84" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F208" s="144"/>
       <c r="G208" s="144"/>
       <c r="J208" s="144"/>
@@ -43276,7 +43285,7 @@
       <c r="CD208" s="110"/>
       <c r="CE208" s="110"/>
     </row>
-    <row r="209" spans="3:83">
+    <row r="209" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C209" s="84" t="s">
         <v>718</v>
       </c>
@@ -43325,7 +43334,7 @@
       <c r="CD209" s="7"/>
       <c r="CE209" s="7"/>
     </row>
-    <row r="210" spans="3:83">
+    <row r="210" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C210" s="85" t="s">
         <v>169</v>
       </c>
@@ -43419,7 +43428,7 @@
       <c r="CD210" s="7"/>
       <c r="CE210" s="7"/>
     </row>
-    <row r="211" spans="3:83">
+    <row r="211" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C211" s="85" t="s">
         <v>724</v>
       </c>
@@ -43513,7 +43522,7 @@
       <c r="CD211" s="7"/>
       <c r="CE211" s="7"/>
     </row>
-    <row r="212" spans="3:83">
+    <row r="212" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C212" s="85" t="s">
         <v>727</v>
       </c>
@@ -43607,7 +43616,7 @@
       <c r="CD212" s="7"/>
       <c r="CE212" s="7"/>
     </row>
-    <row r="213" spans="3:83">
+    <row r="213" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C213" s="85" t="s">
         <v>730</v>
       </c>
@@ -43701,7 +43710,7 @@
       <c r="CD213" s="7"/>
       <c r="CE213" s="7"/>
     </row>
-    <row r="214" spans="3:83">
+    <row r="214" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C214" s="85" t="s">
         <v>205</v>
       </c>
@@ -43795,7 +43804,7 @@
       <c r="CD214" s="7"/>
       <c r="CE214" s="7"/>
     </row>
-    <row r="215" spans="3:83">
+    <row r="215" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C215" s="85" t="s">
         <v>295</v>
       </c>
@@ -43856,7 +43865,7 @@
       <c r="CD215" s="7"/>
       <c r="CE215" s="7"/>
     </row>
-    <row r="216" spans="3:83">
+    <row r="216" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C216" s="85" t="s">
         <v>538</v>
       </c>
@@ -43917,7 +43926,7 @@
       <c r="CD216" s="7"/>
       <c r="CE216" s="7"/>
     </row>
-    <row r="217" spans="3:83">
+    <row r="217" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C217" s="85" t="s">
         <v>525</v>
       </c>
@@ -43978,7 +43987,7 @@
       <c r="CD217" s="7"/>
       <c r="CE217" s="7"/>
     </row>
-    <row r="218" spans="3:83">
+    <row r="218" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C218" s="85" t="s">
         <v>174</v>
       </c>
@@ -44039,7 +44048,7 @@
       <c r="CD218" s="7"/>
       <c r="CE218" s="7"/>
     </row>
-    <row r="219" spans="3:83">
+    <row r="219" spans="3:83" x14ac:dyDescent="0.2">
       <c r="C219" s="85" t="s">
         <v>272</v>
       </c>
@@ -44077,16 +44086,16 @@
       <c r="V219" s="30"/>
       <c r="W219" s="30"/>
     </row>
-    <row r="220" spans="3:83">
+    <row r="220" spans="3:83" x14ac:dyDescent="0.2">
       <c r="S220" s="25"/>
     </row>
-    <row r="221" spans="3:83">
+    <row r="221" spans="3:83" x14ac:dyDescent="0.2">
       <c r="S221" s="107"/>
     </row>
-    <row r="222" spans="3:83">
+    <row r="222" spans="3:83" x14ac:dyDescent="0.2">
       <c r="S222" s="25"/>
     </row>
-    <row r="223" spans="3:83">
+    <row r="223" spans="3:83" x14ac:dyDescent="0.2">
       <c r="E223">
         <f>SUM(E210:E219)</f>
         <v>203</v>
@@ -44109,7 +44118,7 @@
       </c>
       <c r="S223" s="25"/>
     </row>
-    <row r="224" spans="3:83">
+    <row r="224" spans="3:83" x14ac:dyDescent="0.2">
       <c r="J224" s="143" t="str">
         <f>D210</f>
         <v>Construction (Civil)</v>
@@ -44137,7 +44146,7 @@
       </c>
       <c r="S224" s="25"/>
     </row>
-    <row r="225" spans="10:84">
+    <row r="225" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J225" s="143" t="str">
         <f t="shared" ref="J225:J227" si="7">D211</f>
         <v>Construction (commercial building)</v>
@@ -44165,7 +44174,7 @@
       </c>
       <c r="S225" s="25"/>
     </row>
-    <row r="226" spans="10:84">
+    <row r="226" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J226" s="143" t="str">
         <f t="shared" si="7"/>
         <v>Construction (residential building)</v>
@@ -44193,7 +44202,7 @@
       </c>
       <c r="S226" s="25"/>
     </row>
-    <row r="227" spans="10:84">
+    <row r="227" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J227" s="143" t="str">
         <f t="shared" si="7"/>
         <v>Construction (institutional building)</v>
@@ -44221,7 +44230,7 @@
       </c>
       <c r="S227" s="25"/>
     </row>
-    <row r="228" spans="10:84">
+    <row r="228" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J228" s="143" t="str">
         <f t="shared" ref="J228:K228" si="8">D214</f>
         <v>Construction (Industrial)</v>
@@ -44249,7 +44258,7 @@
       </c>
       <c r="S228" s="25"/>
     </row>
-    <row r="229" spans="10:84">
+    <row r="229" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J229" s="135" t="s">
         <v>750</v>
       </c>
@@ -44276,7 +44285,7 @@
       </c>
       <c r="S229" s="25"/>
     </row>
-    <row r="230" spans="10:84">
+    <row r="230" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J230" s="143" t="str">
         <f>C215</f>
         <v>Engineering</v>
@@ -44304,7 +44313,7 @@
       </c>
       <c r="S230" s="25"/>
     </row>
-    <row r="231" spans="10:84">
+    <row r="231" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J231" s="143" t="str">
         <f>C216</f>
         <v>Mobility</v>
@@ -44332,7 +44341,7 @@
       </c>
       <c r="S231" s="25"/>
     </row>
-    <row r="232" spans="10:84">
+    <row r="232" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J232" s="143" t="str">
         <f>C217</f>
         <v>Event management</v>
@@ -44360,7 +44369,7 @@
       </c>
       <c r="S232" s="25"/>
     </row>
-    <row r="233" spans="10:84">
+    <row r="233" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J233" s="143" t="str">
         <f>C218</f>
         <v>IT</v>
@@ -44388,7 +44397,7 @@
       </c>
       <c r="S233" s="25"/>
     </row>
-    <row r="234" spans="10:84">
+    <row r="234" spans="10:84" x14ac:dyDescent="0.2">
       <c r="J234" s="143" t="str">
         <f>C219</f>
         <v>Education</v>
@@ -44416,35 +44425,35 @@
       </c>
       <c r="S234" s="25"/>
     </row>
-    <row r="235" spans="10:84">
+    <row r="235" spans="10:84" x14ac:dyDescent="0.2">
       <c r="S235" s="25"/>
     </row>
-    <row r="236" spans="10:84">
+    <row r="236" spans="10:84" x14ac:dyDescent="0.2">
       <c r="K236">
         <f>SUM(K229:K234)</f>
         <v>203</v>
       </c>
       <c r="S236" s="25"/>
     </row>
-    <row r="237" spans="10:84">
+    <row r="237" spans="10:84" x14ac:dyDescent="0.2">
       <c r="S237" s="25"/>
     </row>
-    <row r="238" spans="10:84">
+    <row r="238" spans="10:84" x14ac:dyDescent="0.2">
       <c r="S238" s="25"/>
     </row>
-    <row r="239" spans="10:84">
+    <row r="239" spans="10:84" x14ac:dyDescent="0.2">
       <c r="S239" s="25"/>
     </row>
-    <row r="240" spans="10:84">
+    <row r="240" spans="10:84" x14ac:dyDescent="0.2">
       <c r="S240" s="25"/>
       <c r="CE240" s="113"/>
       <c r="CF240" s="113"/>
     </row>
-    <row r="249" spans="83:84">
+    <row r="249" spans="83:84" x14ac:dyDescent="0.2">
       <c r="CE249" s="113"/>
       <c r="CF249" s="113"/>
     </row>
-    <row r="258" spans="83:84">
+    <row r="258" spans="83:84" x14ac:dyDescent="0.2">
       <c r="CE258" s="113"/>
       <c r="CF258" s="113"/>
     </row>
@@ -44460,22 +44469,31 @@
         <filter val="1"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="16">
+      <filters>
+        <filter val="1.0%"/>
+        <filter val="12.0%"/>
+        <filter val="13.5%"/>
+        <filter val="26.2%"/>
+        <filter val="4.4%"/>
+        <filter val="40.3%"/>
+        <filter val="5.4%"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="17">
+      <filters>
+        <filter val="0.31€"/>
+        <filter val="0.7%"/>
+        <filter val="1.4%"/>
+        <filter val="1.5%"/>
+        <filter val="11.9%"/>
+        <filter val="4.2%"/>
+        <filter val="42.5%"/>
+        <filter val="93.9%"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <mergeCells count="30">
-    <mergeCell ref="BL2:BN2"/>
-    <mergeCell ref="BO2:BQ2"/>
-    <mergeCell ref="AN2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AV2"/>
-    <mergeCell ref="AW2:AY2"/>
-    <mergeCell ref="AZ2:BB2"/>
-    <mergeCell ref="BC2:BE2"/>
-    <mergeCell ref="BF2:BH2"/>
-    <mergeCell ref="AH2:AJ2"/>
-    <mergeCell ref="AK2:AM2"/>
-    <mergeCell ref="Y1:AP1"/>
-    <mergeCell ref="AQ1:AY1"/>
-    <mergeCell ref="BI2:BK2"/>
     <mergeCell ref="BX2:BZ2"/>
     <mergeCell ref="CA2:CC2"/>
     <mergeCell ref="BR2:BT2"/>
@@ -44492,6 +44510,20 @@
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AG2"/>
+    <mergeCell ref="AH2:AJ2"/>
+    <mergeCell ref="AK2:AM2"/>
+    <mergeCell ref="Y1:AP1"/>
+    <mergeCell ref="AQ1:AY1"/>
+    <mergeCell ref="BI2:BK2"/>
+    <mergeCell ref="BL2:BN2"/>
+    <mergeCell ref="BO2:BQ2"/>
+    <mergeCell ref="AN2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AV2"/>
+    <mergeCell ref="AW2:AY2"/>
+    <mergeCell ref="AZ2:BB2"/>
+    <mergeCell ref="BC2:BE2"/>
+    <mergeCell ref="BF2:BH2"/>
   </mergeCells>
   <conditionalFormatting sqref="Q10 Q15 Q16:R16 Q30:R30 Q35:R38 Q39">
     <cfRule type="cellIs" dxfId="10" priority="12" operator="lessThanOrEqual">
